--- a/research/traditional_assets/database/data/norway/norway_air_transport.xlsx
+++ b/research/traditional_assets/database/data/norway/norway_air_transport.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ4"/>
+  <dimension ref="A1:AQ5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,43 +588,43 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.339</v>
+        <v>-0.108</v>
       </c>
       <c r="G2">
-        <v>-2.395238095238096</v>
+        <v>-0.2638162888722946</v>
       </c>
       <c r="H2">
-        <v>-2.395238095238096</v>
+        <v>-0.2638162888722946</v>
       </c>
       <c r="I2">
-        <v>-0.9240010946907499</v>
+        <v>-0.1707634676030783</v>
       </c>
       <c r="J2">
-        <v>-0.9240010946907499</v>
+        <v>-0.170406529699908</v>
       </c>
       <c r="K2">
-        <v>-1706.85</v>
+        <v>-64.2</v>
       </c>
       <c r="L2">
-        <v>-4.671182266009853</v>
+        <v>-0.03962058048470411</v>
       </c>
       <c r="M2">
-        <v>42.4</v>
+        <v>1.4</v>
       </c>
       <c r="N2">
-        <v>0.03647311827956989</v>
+        <v>0.001868909357896142</v>
       </c>
       <c r="O2">
-        <v>-0.02484108152444561</v>
+        <v>-0.02180685358255452</v>
       </c>
       <c r="P2">
-        <v>42.4</v>
+        <v>1.4</v>
       </c>
       <c r="Q2">
-        <v>0.03647311827956989</v>
+        <v>0.001868909357896142</v>
       </c>
       <c r="R2">
-        <v>-0.02484108152444561</v>
+        <v>-0.02180685358255452</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -633,61 +633,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>916.7</v>
+        <v>844.3</v>
       </c>
       <c r="V2">
-        <v>0.7885591397849463</v>
+        <v>1.127085836336938</v>
+      </c>
+      <c r="W2">
+        <v>-2.933002481389579</v>
       </c>
       <c r="X2">
-        <v>0.08538647425198548</v>
+        <v>0.6108015419859167</v>
+      </c>
+      <c r="Y2">
+        <v>-3.543804023375495</v>
       </c>
       <c r="Z2">
-        <v>0.05738515901060071</v>
+        <v>4.023764589024088</v>
+      </c>
+      <c r="AA2">
+        <v>-2.108585858585859</v>
       </c>
       <c r="AB2">
-        <v>0.05415776567461978</v>
+        <v>0.08147465100316451</v>
+      </c>
+      <c r="AC2">
+        <v>-2.190060509589024</v>
       </c>
       <c r="AD2">
-        <v>989.6</v>
+        <v>2116.1</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>989.6</v>
+        <v>2116.1</v>
       </c>
       <c r="AG2">
-        <v>72.89999999999998</v>
+        <v>1271.8</v>
       </c>
       <c r="AH2">
-        <v>0.4598299335532736</v>
+        <v>0.7385522825631718</v>
       </c>
       <c r="AI2">
-        <v>0.7500378960133394</v>
+        <v>0.8054889421795897</v>
       </c>
       <c r="AJ2">
-        <v>0.05900922778047594</v>
+        <v>0.6293235687070117</v>
       </c>
       <c r="AK2">
-        <v>0.1810280605910106</v>
+        <v>0.7133722234687009</v>
       </c>
       <c r="AL2">
-        <v>128.224</v>
+        <v>92.71000000000001</v>
       </c>
       <c r="AM2">
-        <v>128.224</v>
+        <v>87.7</v>
       </c>
       <c r="AN2">
-        <v>-1.546926780466454</v>
+        <v>-12.0850942318675</v>
       </c>
       <c r="AO2">
-        <v>-2.633126403793362</v>
+        <v>-2.984575558192212</v>
       </c>
       <c r="AP2">
-        <v>-0.1139561057962858</v>
+        <v>-7.263278126784694</v>
       </c>
       <c r="AQ2">
-        <v>-2.633126403793362</v>
+        <v>-3.155074116305587</v>
       </c>
     </row>
     <row r="3">
@@ -707,43 +719,43 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.339</v>
+        <v>-0.108</v>
       </c>
       <c r="G3">
-        <v>-2.388067870826492</v>
+        <v>-0.2452954770551337</v>
       </c>
       <c r="H3">
-        <v>-2.388067870826492</v>
+        <v>-0.2452954770551337</v>
       </c>
       <c r="I3">
-        <v>-0.9168035030103996</v>
+        <v>-0.09442060085836911</v>
       </c>
       <c r="J3">
-        <v>-0.9168035030103996</v>
+        <v>-0.0938285135970913</v>
       </c>
       <c r="K3">
-        <v>-1704.2</v>
+        <v>113.8</v>
       </c>
       <c r="L3">
-        <v>-4.663929939792009</v>
+        <v>0.07514031033344337</v>
       </c>
       <c r="M3">
-        <v>42.4</v>
+        <v>1.4</v>
       </c>
       <c r="N3">
-        <v>0.03742277140335393</v>
+        <v>0.002019619157530294</v>
       </c>
       <c r="O3">
-        <v>-0.02487970895434808</v>
+        <v>0.01230228471001757</v>
       </c>
       <c r="P3">
-        <v>42.4</v>
+        <v>1.4</v>
       </c>
       <c r="Q3">
-        <v>0.03742277140335393</v>
+        <v>0.002019619157530294</v>
       </c>
       <c r="R3">
-        <v>-0.02487970895434808</v>
+        <v>0.01230228471001757</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -752,73 +764,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>875.1</v>
+        <v>754</v>
       </c>
       <c r="V3">
-        <v>0.7723742277140335</v>
+        <v>1.087709174841315</v>
       </c>
       <c r="W3">
-        <v>-1.436567478715334</v>
+        <v>0.3930915371329879</v>
       </c>
       <c r="X3">
-        <v>0.07732554652509753</v>
+        <v>0.1353283169483657</v>
       </c>
       <c r="Y3">
-        <v>-1.513893025240431</v>
+        <v>0.2577632201846222</v>
       </c>
       <c r="Z3">
-        <v>0.05738515901060071</v>
+        <v>4.171027265216193</v>
       </c>
       <c r="AA3">
-        <v>-0.05261091480172752</v>
+        <v>-0.3913612884681761</v>
       </c>
       <c r="AB3">
-        <v>0.05510529880289118</v>
+        <v>0.08248873543294578</v>
       </c>
       <c r="AC3">
-        <v>-0.1077162136046187</v>
+        <v>-0.4738500239011219</v>
       </c>
       <c r="AD3">
-        <v>948.7</v>
+        <v>1000.1</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>948.7</v>
+        <v>1000.1</v>
       </c>
       <c r="AG3">
-        <v>73.60000000000002</v>
+        <v>246.1</v>
       </c>
       <c r="AH3">
-        <v>0.4557332949032042</v>
+        <v>0.5906218626350912</v>
       </c>
       <c r="AI3">
-        <v>0.7661928606041027</v>
+        <v>0.6909153713298791</v>
       </c>
       <c r="AJ3">
-        <v>0.06099784518481687</v>
+        <v>0.2620036197168104</v>
       </c>
       <c r="AK3">
-        <v>0.2026989809969706</v>
+        <v>0.3548666186012978</v>
       </c>
       <c r="AL3">
-        <v>128.2</v>
+        <v>55.7</v>
       </c>
       <c r="AM3">
-        <v>128.2</v>
+        <v>50.90000000000001</v>
       </c>
       <c r="AN3">
-        <v>-1.489091194474965</v>
+        <v>-11.01431718061674</v>
       </c>
       <c r="AO3">
-        <v>-2.613104524180967</v>
+        <v>-2.567324955116697</v>
       </c>
       <c r="AP3">
-        <v>-0.1155234657039712</v>
+        <v>-2.710352422907489</v>
       </c>
       <c r="AQ3">
-        <v>-2.613104524180967</v>
+        <v>-2.80943025540275</v>
       </c>
     </row>
     <row r="4">
@@ -837,8 +849,23 @@
           <t>Air Transport</t>
         </is>
       </c>
+      <c r="G4">
+        <v>-0.4596695821185617</v>
+      </c>
+      <c r="H4">
+        <v>-0.4596695821185617</v>
+      </c>
+      <c r="I4">
+        <v>-0.8114674441205053</v>
+      </c>
+      <c r="J4">
+        <v>-0.8114674441205053</v>
+      </c>
       <c r="K4">
-        <v>-2.65</v>
+        <v>-118.2</v>
+      </c>
+      <c r="L4">
+        <v>-1.14868804664723</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -862,58 +889,177 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>41.6</v>
+        <v>14.2</v>
       </c>
       <c r="V4">
-        <v>1.410169491525424</v>
+        <v>1.014285714285714</v>
+      </c>
+      <c r="W4">
+        <v>-2.933002481389579</v>
       </c>
       <c r="X4">
-        <v>0.09344740197887343</v>
+        <v>0.6108015419859167</v>
+      </c>
+      <c r="Y4">
+        <v>-3.543804023375495</v>
+      </c>
+      <c r="Z4">
+        <v>2.59848484848485</v>
+      </c>
+      <c r="AA4">
+        <v>-2.108585858585859</v>
       </c>
       <c r="AB4">
-        <v>0.05321023254634838</v>
+        <v>0.08147465100316451</v>
+      </c>
+      <c r="AC4">
+        <v>-2.190060509589024</v>
       </c>
       <c r="AD4">
-        <v>40.9</v>
+        <v>208.1</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>40.9</v>
+        <v>208.1</v>
       </c>
       <c r="AG4">
-        <v>-0.7000000000000028</v>
+        <v>193.9</v>
       </c>
       <c r="AH4">
-        <v>0.5809659090909091</v>
+        <v>0.9369653309320126</v>
       </c>
       <c r="AI4">
-        <v>0.5036945812807883</v>
+        <v>1.249099639855942</v>
       </c>
       <c r="AJ4">
-        <v>-0.02430555555555566</v>
+        <v>0.9326599326599326</v>
       </c>
       <c r="AK4">
-        <v>-0.01767676767676775</v>
+        <v>1.272309711286089</v>
       </c>
       <c r="AL4">
-        <v>0.024</v>
+        <v>33.7</v>
       </c>
       <c r="AM4">
-        <v>0.024</v>
+        <v>33.558</v>
       </c>
       <c r="AN4">
-        <v>-15.61068702290076</v>
+        <v>-2.468564650059312</v>
       </c>
       <c r="AO4">
-        <v>-109.5833333333333</v>
+        <v>-2.477744807121661</v>
       </c>
       <c r="AP4">
-        <v>0.267175572519085</v>
+        <v>-2.300118623962041</v>
       </c>
       <c r="AQ4">
-        <v>-109.5833333333333</v>
+        <v>-2.488229334286906</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Norse Atlantic ASA (OB:NORSE)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Air Transport</t>
+        </is>
+      </c>
+      <c r="G5">
+        <v>-2.922558922558922</v>
+      </c>
+      <c r="H5">
+        <v>-2.922558922558922</v>
+      </c>
+      <c r="I5">
+        <v>-16.9023569023569</v>
+      </c>
+      <c r="J5">
+        <v>-16.9023569023569</v>
+      </c>
+      <c r="K5">
+        <v>-59.8</v>
+      </c>
+      <c r="L5">
+        <v>-20.13468013468013</v>
+      </c>
+      <c r="M5">
+        <v>-0</v>
+      </c>
+      <c r="N5">
+        <v>-0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>-0</v>
+      </c>
+      <c r="Q5">
+        <v>-0</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>76.09999999999999</v>
+      </c>
+      <c r="V5">
+        <v>1.816229116945107</v>
+      </c>
+      <c r="X5">
+        <v>0.8518396486905357</v>
+      </c>
+      <c r="AB5">
+        <v>0.07858600892833588</v>
+      </c>
+      <c r="AD5">
+        <v>907.9</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>907.9</v>
+      </c>
+      <c r="AG5">
+        <v>831.8</v>
+      </c>
+      <c r="AH5">
+        <v>0.9558854495683302</v>
+      </c>
+      <c r="AI5">
+        <v>0.896248766041461</v>
+      </c>
+      <c r="AJ5">
+        <v>0.9520430353668308</v>
+      </c>
+      <c r="AK5">
+        <v>0.887821539118369</v>
+      </c>
+      <c r="AL5">
+        <v>3.31</v>
+      </c>
+      <c r="AM5">
+        <v>3.242</v>
+      </c>
+      <c r="AO5">
+        <v>-15.16616314199396</v>
+      </c>
+      <c r="AQ5">
+        <v>-15.48426896977175</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/norway/norway_air_transport.xlsx
+++ b/research/traditional_assets/database/data/norway/norway_air_transport.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="ob_nas" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -351,7 +353,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ5"/>
+  <dimension ref="A1:AQ4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +581,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,43 +590,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.108</v>
+        <v>-0.0946</v>
+      </c>
+      <c r="E2">
+        <v>0.121</v>
       </c>
       <c r="G2">
-        <v>-0.2638162888722946</v>
+        <v>-0.07702005279123823</v>
       </c>
       <c r="H2">
-        <v>-0.2638162888722946</v>
+        <v>-0.07702005279123823</v>
       </c>
       <c r="I2">
-        <v>-0.1707634676030783</v>
+        <v>0.03774179569002876</v>
       </c>
       <c r="J2">
-        <v>-0.170406529699908</v>
+        <v>0.03711232309477634</v>
       </c>
       <c r="K2">
-        <v>-64.2</v>
+        <v>33</v>
       </c>
       <c r="L2">
-        <v>-0.03962058048470411</v>
+        <v>0.01300082732537525</v>
       </c>
       <c r="M2">
-        <v>1.4</v>
+        <v>0.019</v>
       </c>
       <c r="N2">
-        <v>0.001868909357896142</v>
+        <v>1.634408602150538e-05</v>
       </c>
       <c r="O2">
-        <v>-0.02180685358255452</v>
+        <v>0.0005757575757575757</v>
       </c>
       <c r="P2">
-        <v>1.4</v>
+        <v>0.019</v>
       </c>
       <c r="Q2">
-        <v>0.001868909357896142</v>
+        <v>1.634408602150538e-05</v>
       </c>
       <c r="R2">
-        <v>-0.02180685358255452</v>
+        <v>0.0005757575757575757</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -633,73 +638,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>844.3</v>
+        <v>923.2</v>
       </c>
       <c r="V2">
-        <v>1.127085836336938</v>
+        <v>0.7941505376344087</v>
       </c>
       <c r="W2">
-        <v>-2.933002481389579</v>
+        <v>-0.3431159714634125</v>
       </c>
       <c r="X2">
-        <v>0.6108015419859167</v>
+        <v>0.1892510133375045</v>
       </c>
       <c r="Y2">
-        <v>-3.543804023375495</v>
+        <v>-0.5323669848009169</v>
       </c>
       <c r="Z2">
-        <v>4.023764589024088</v>
+        <v>1.556857212953876</v>
       </c>
       <c r="AA2">
-        <v>-2.108585858585859</v>
+        <v>0.0795652581442529</v>
       </c>
       <c r="AB2">
-        <v>0.08147465100316451</v>
+        <v>0.07151033890015474</v>
       </c>
       <c r="AC2">
-        <v>-2.190060509589024</v>
+        <v>0.008054919244098166</v>
       </c>
       <c r="AD2">
-        <v>2116.1</v>
+        <v>2247.7</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>2116.1</v>
+        <v>2247.7</v>
       </c>
       <c r="AG2">
-        <v>1271.8</v>
+        <v>1324.5</v>
       </c>
       <c r="AH2">
-        <v>0.7385522825631718</v>
+        <v>0.6591109025863585</v>
       </c>
       <c r="AI2">
-        <v>0.8054889421795897</v>
+        <v>0.8183274474824335</v>
       </c>
       <c r="AJ2">
-        <v>0.6293235687070117</v>
+        <v>0.5325693606755125</v>
       </c>
       <c r="AK2">
-        <v>0.7133722234687009</v>
+        <v>0.7263504250068549</v>
       </c>
       <c r="AL2">
-        <v>92.71000000000001</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="AM2">
-        <v>87.7</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="AN2">
-        <v>-12.0850942318675</v>
+        <v>15.35314207650273</v>
       </c>
       <c r="AO2">
-        <v>-2.984575558192212</v>
+        <v>0.9765545361875636</v>
       </c>
       <c r="AP2">
-        <v>-7.263278126784694</v>
+        <v>9.047131147540982</v>
       </c>
       <c r="AQ2">
-        <v>-3.155074116305587</v>
+        <v>1.301630434782609</v>
       </c>
     </row>
     <row r="3">
@@ -719,43 +724,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.108</v>
+        <v>-0.0946</v>
+      </c>
+      <c r="E3">
+        <v>0.121</v>
       </c>
       <c r="G3">
-        <v>-0.2452954770551337</v>
+        <v>-0.02265681983953319</v>
       </c>
       <c r="H3">
-        <v>-0.2452954770551337</v>
+        <v>-0.02265681983953319</v>
       </c>
       <c r="I3">
-        <v>-0.09442060085836911</v>
+        <v>0.07941283734500365</v>
       </c>
       <c r="J3">
-        <v>-0.0938285135970913</v>
+        <v>0.0767638799275841</v>
       </c>
       <c r="K3">
-        <v>113.8</v>
+        <v>137.4</v>
       </c>
       <c r="L3">
-        <v>0.07514031033344337</v>
+        <v>0.062636761487965</v>
       </c>
       <c r="M3">
-        <v>1.4</v>
+        <v>0.019</v>
       </c>
       <c r="N3">
-        <v>0.002019619157530294</v>
+        <v>1.868791187174191e-05</v>
       </c>
       <c r="O3">
-        <v>0.01230228471001757</v>
+        <v>0.0001382823871906841</v>
       </c>
       <c r="P3">
-        <v>1.4</v>
+        <v>0.019</v>
       </c>
       <c r="Q3">
-        <v>0.002019619157530294</v>
+        <v>1.868791187174191e-05</v>
       </c>
       <c r="R3">
-        <v>0.01230228471001757</v>
+        <v>0.0001382823871906841</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -764,73 +772,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>754</v>
+        <v>880.6</v>
       </c>
       <c r="V3">
-        <v>1.087709174841315</v>
+        <v>0.8661355365397856</v>
       </c>
       <c r="W3">
-        <v>0.3930915371329879</v>
+        <v>0.3071077335717479</v>
       </c>
       <c r="X3">
-        <v>0.1353283169483657</v>
+        <v>0.1122783543023493</v>
       </c>
       <c r="Y3">
-        <v>0.2577632201846222</v>
+        <v>0.1948293792693986</v>
       </c>
       <c r="Z3">
-        <v>4.171027265216193</v>
+        <v>3.16308579668349</v>
       </c>
       <c r="AA3">
-        <v>-0.3913612884681761</v>
+        <v>0.2428107382972581</v>
       </c>
       <c r="AB3">
-        <v>0.08248873543294578</v>
+        <v>0.07173364728051365</v>
       </c>
       <c r="AC3">
-        <v>-0.4738500239011219</v>
+        <v>0.1710770910167444</v>
       </c>
       <c r="AD3">
-        <v>1000.1</v>
+        <v>1285.5</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>1000.1</v>
+        <v>1285.5</v>
       </c>
       <c r="AG3">
-        <v>246.1</v>
+        <v>404.9</v>
       </c>
       <c r="AH3">
-        <v>0.5906218626350912</v>
+        <v>0.5583789418816785</v>
       </c>
       <c r="AI3">
-        <v>0.6909153713298791</v>
+        <v>0.6893130998981178</v>
       </c>
       <c r="AJ3">
-        <v>0.2620036197168104</v>
+        <v>0.2848199212155318</v>
       </c>
       <c r="AK3">
-        <v>0.3548666186012978</v>
+        <v>0.4113583257137052</v>
       </c>
       <c r="AL3">
-        <v>55.7</v>
+        <v>72.2</v>
       </c>
       <c r="AM3">
-        <v>50.90000000000001</v>
+        <v>47.7</v>
       </c>
       <c r="AN3">
-        <v>-11.01431718061674</v>
+        <v>5.751677852348993</v>
       </c>
       <c r="AO3">
-        <v>-2.567324955116697</v>
+        <v>2.412742382271468</v>
       </c>
       <c r="AP3">
-        <v>-2.710352422907489</v>
+        <v>1.811633109619687</v>
       </c>
       <c r="AQ3">
-        <v>-2.80943025540275</v>
+        <v>3.651991614255765</v>
       </c>
     </row>
     <row r="4">
@@ -841,7 +849,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Flyr AS (OB:FLYR)</t>
+          <t>Norse Atlantic ASA (OB:NORSE)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -850,22 +858,22 @@
         </is>
       </c>
       <c r="G4">
-        <v>-0.4596695821185617</v>
+        <v>-0.4229765013054831</v>
       </c>
       <c r="H4">
-        <v>-0.4596695821185617</v>
+        <v>-0.4229765013054831</v>
       </c>
       <c r="I4">
-        <v>-0.8114674441205053</v>
+        <v>-0.2274441543371047</v>
       </c>
       <c r="J4">
-        <v>-0.8114674441205053</v>
+        <v>-0.2274441543371047</v>
       </c>
       <c r="K4">
-        <v>-118.2</v>
+        <v>-104.4</v>
       </c>
       <c r="L4">
-        <v>-1.14868804664723</v>
+        <v>-0.3028720626631854</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -889,177 +897,8845 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>14.2</v>
+        <v>42.6</v>
       </c>
       <c r="V4">
-        <v>1.014285714285714</v>
+        <v>0.2921810699588477</v>
       </c>
       <c r="W4">
-        <v>-2.933002481389579</v>
+        <v>-0.9933396764985729</v>
       </c>
       <c r="X4">
-        <v>0.6108015419859167</v>
+        <v>0.2662236723726597</v>
       </c>
       <c r="Y4">
-        <v>-3.543804023375495</v>
+        <v>-1.259563348871233</v>
       </c>
       <c r="Z4">
-        <v>2.59848484848485</v>
+        <v>0.3679154658981748</v>
       </c>
       <c r="AA4">
-        <v>-2.108585858585859</v>
+        <v>-0.08368022200875228</v>
       </c>
       <c r="AB4">
-        <v>0.08147465100316451</v>
+        <v>0.07128703051979583</v>
       </c>
       <c r="AC4">
-        <v>-2.190060509589024</v>
+        <v>-0.1549672525285481</v>
       </c>
       <c r="AD4">
-        <v>208.1</v>
+        <v>962.2</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>208.1</v>
+        <v>962.2</v>
       </c>
       <c r="AG4">
-        <v>193.9</v>
+        <v>919.6</v>
       </c>
       <c r="AH4">
-        <v>0.9369653309320126</v>
+        <v>0.8684115523465704</v>
       </c>
       <c r="AI4">
-        <v>1.249099639855942</v>
+        <v>1.091177137672942</v>
       </c>
       <c r="AJ4">
-        <v>0.9326599326599326</v>
+        <v>0.8631499906138539</v>
       </c>
       <c r="AK4">
-        <v>1.272309711286089</v>
+        <v>1.09580552907531</v>
       </c>
       <c r="AL4">
-        <v>33.7</v>
+        <v>25.9</v>
       </c>
       <c r="AM4">
-        <v>33.558</v>
+        <v>25.9</v>
       </c>
       <c r="AN4">
-        <v>-2.468564650059312</v>
+        <v>-12.4798962386511</v>
       </c>
       <c r="AO4">
-        <v>-2.477744807121661</v>
+        <v>-3.027027027027027</v>
       </c>
       <c r="AP4">
-        <v>-2.300118623962041</v>
+        <v>-11.92736705577173</v>
       </c>
       <c r="AQ4">
-        <v>-2.488229334286906</v>
+        <v>-3.027027027027027</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AY2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>current_interest_coverage</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_interest_coverage</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_capital</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>current_equity_value</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>current_enterprise_value</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_capital</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_rating</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_equity</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>current_beta</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_coverage_ratio</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_interest_expense</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_debt_rating</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_drop_ebitda</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_ev_implied_growth</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio_limit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Norwegian Air Shuttle ASA (OB:NAS)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>OB:NAS</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Air Transport</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>2.41274238227147</v>
+      </c>
+      <c r="F2">
+        <v>4.56604453632618</v>
+      </c>
+      <c r="G2">
+        <v>5.75167785234899</v>
+      </c>
+      <c r="H2">
+        <v>4.42928859060403</v>
+      </c>
+      <c r="I2">
+        <v>0.558378941881678</v>
+      </c>
+      <c r="J2">
+        <v>0.43</v>
+      </c>
+      <c r="K2">
+        <v>1016.7</v>
+      </c>
+      <c r="L2">
+        <v>1293.94713364851</v>
+      </c>
+      <c r="M2">
+        <v>1421.6</v>
+      </c>
+      <c r="N2">
+        <v>1403.29313364851</v>
+      </c>
+      <c r="O2">
+        <v>1285.5</v>
+      </c>
+      <c r="P2">
+        <v>989.946</v>
+      </c>
+      <c r="Q2">
+        <v>0.07173364728051369</v>
+      </c>
+      <c r="R2">
+        <v>0.072682285508942</v>
+      </c>
+      <c r="S2">
+        <v>0.0396669</v>
+      </c>
+      <c r="T2">
+        <v>0.039702</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="W2">
+        <v>0.112278354302349</v>
+      </c>
+      <c r="X2">
+        <v>0.0975621500156877</v>
+      </c>
+      <c r="Y2">
+        <v>1.59735552831194</v>
+      </c>
+      <c r="Z2">
+        <v>1.2774380438193</v>
+      </c>
+      <c r="AA2">
+        <v>1285.5</v>
+      </c>
+      <c r="AB2">
+        <v>0.050855</v>
+      </c>
+      <c r="AC2">
+        <v>2.412742382271468</v>
+      </c>
+      <c r="AD2">
+        <v>1285.5</v>
+      </c>
+      <c r="AE2">
+        <v>72.2</v>
+      </c>
+      <c r="AF2">
+        <v>49.30000000000001</v>
+      </c>
+      <c r="AG2">
+        <v>223.5</v>
+      </c>
+      <c r="AH2">
+        <v>0</v>
+      </c>
+      <c r="AI2">
+        <v>0.0388</v>
+      </c>
+      <c r="AJ2">
+        <v>1016.7</v>
+      </c>
+      <c r="AK2">
+        <v>0.046</v>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="AM2">
+        <v>0.22</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>2</v>
+      </c>
+      <c r="AQ2">
+        <v>81.7</v>
+      </c>
+      <c r="AR2">
+        <v>72.2</v>
+      </c>
+      <c r="AS2">
+        <v>1285.5</v>
+      </c>
+      <c r="AT2">
+        <v>880.6</v>
+      </c>
+      <c r="AV2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AX2">
+        <v>1</v>
+      </c>
+      <c r="AY2">
+        <v>10000000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.0757940639595118</v>
+      </c>
+      <c r="C2">
+        <v>2227.017733367543</v>
+      </c>
+      <c r="D2">
+        <v>1346.417733367543</v>
+      </c>
+      <c r="E2">
+        <v>-1285.5</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>880.6</v>
+      </c>
+      <c r="H2">
+        <v>1016.7</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>279.375</v>
+      </c>
+      <c r="K2">
+        <v>49.30000000000001</v>
+      </c>
+      <c r="L2">
+        <v>230.075</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>230.075</v>
+      </c>
+      <c r="O2">
+        <v>50.61649999999999</v>
+      </c>
+      <c r="P2">
+        <v>179.4585</v>
+      </c>
+      <c r="Q2">
+        <v>228.7585</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.0757940639595118</v>
+      </c>
+      <c r="T2">
+        <v>0.8042187817285175</v>
+      </c>
+      <c r="U2">
+        <v>0.0447</v>
+      </c>
+      <c r="V2">
+        <v>0.22</v>
+      </c>
+      <c r="W2">
+        <v>0.034866</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.07567333701880087</v>
+      </c>
+      <c r="C3">
+        <v>2206.116216641276</v>
+      </c>
+      <c r="D3">
+        <v>1348.538216641276</v>
+      </c>
+      <c r="E3">
+        <v>-1262.478</v>
+      </c>
+      <c r="F3">
+        <v>23.022</v>
+      </c>
+      <c r="G3">
+        <v>880.6</v>
+      </c>
+      <c r="H3">
+        <v>1016.7</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>279.375</v>
+      </c>
+      <c r="K3">
+        <v>49.30000000000001</v>
+      </c>
+      <c r="L3">
+        <v>230.075</v>
+      </c>
+      <c r="M3">
+        <v>1.0290834</v>
+      </c>
+      <c r="N3">
+        <v>229.0459166</v>
+      </c>
+      <c r="O3">
+        <v>50.390101652</v>
+      </c>
+      <c r="P3">
+        <v>178.655814948</v>
+      </c>
+      <c r="Q3">
+        <v>227.955814948</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.07608553234222311</v>
+      </c>
+      <c r="T3">
+        <v>0.8105550509178936</v>
+      </c>
+      <c r="U3">
+        <v>0.0447</v>
+      </c>
+      <c r="V3">
+        <v>0.22</v>
+      </c>
+      <c r="W3">
+        <v>0.034866</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>223.5727444442307</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.07555261007808994</v>
+      </c>
+      <c r="C4">
+        <v>2185.22138958028</v>
+      </c>
+      <c r="D4">
+        <v>1350.66538958028</v>
+      </c>
+      <c r="E4">
+        <v>-1239.456</v>
+      </c>
+      <c r="F4">
+        <v>46.044</v>
+      </c>
+      <c r="G4">
+        <v>880.6</v>
+      </c>
+      <c r="H4">
+        <v>1016.7</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>279.375</v>
+      </c>
+      <c r="K4">
+        <v>49.30000000000001</v>
+      </c>
+      <c r="L4">
+        <v>230.075</v>
+      </c>
+      <c r="M4">
+        <v>2.0581668</v>
+      </c>
+      <c r="N4">
+        <v>228.0168332</v>
+      </c>
+      <c r="O4">
+        <v>50.16370330399999</v>
+      </c>
+      <c r="P4">
+        <v>177.853129896</v>
+      </c>
+      <c r="Q4">
+        <v>227.153129896</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.07638294905927545</v>
+      </c>
+      <c r="T4">
+        <v>0.8170206317233796</v>
+      </c>
+      <c r="U4">
+        <v>0.0447</v>
+      </c>
+      <c r="V4">
+        <v>0.22</v>
+      </c>
+      <c r="W4">
+        <v>0.034866</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>111.7863722221153</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Norway</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Norse Atlantic ASA (OB:NORSE)</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Air Transport</t>
-        </is>
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.07543188313737902</v>
+      </c>
+      <c r="C5">
+        <v>2164.333283891236</v>
+      </c>
+      <c r="D5">
+        <v>1352.799283891236</v>
+      </c>
+      <c r="E5">
+        <v>-1216.434</v>
+      </c>
+      <c r="F5">
+        <v>69.06599999999999</v>
       </c>
       <c r="G5">
-        <v>-2.922558922558922</v>
+        <v>880.6</v>
       </c>
       <c r="H5">
-        <v>-2.922558922558922</v>
+        <v>1016.7</v>
       </c>
       <c r="I5">
-        <v>-16.9023569023569</v>
+        <v>0</v>
       </c>
       <c r="J5">
-        <v>-16.9023569023569</v>
+        <v>279.375</v>
       </c>
       <c r="K5">
-        <v>-59.8</v>
+        <v>49.30000000000001</v>
       </c>
       <c r="L5">
-        <v>-20.13468013468013</v>
+        <v>230.075</v>
       </c>
       <c r="M5">
-        <v>-0</v>
+        <v>3.0872502</v>
       </c>
       <c r="N5">
-        <v>-0</v>
+        <v>226.9877498</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>49.937304956</v>
       </c>
       <c r="P5">
-        <v>-0</v>
+        <v>177.050444844</v>
       </c>
       <c r="Q5">
-        <v>-0</v>
+        <v>226.350444844</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>0.07668649807977218</v>
+      </c>
+      <c r="T5">
+        <v>0.8236195234733085</v>
       </c>
       <c r="U5">
-        <v>76.09999999999999</v>
+        <v>0.0447</v>
       </c>
       <c r="V5">
-        <v>1.816229116945107</v>
-      </c>
-      <c r="X5">
-        <v>0.8518396486905357</v>
-      </c>
-      <c r="AB5">
-        <v>0.07858600892833588</v>
-      </c>
-      <c r="AD5">
-        <v>907.9</v>
-      </c>
-      <c r="AE5">
-        <v>0</v>
-      </c>
-      <c r="AF5">
-        <v>907.9</v>
-      </c>
-      <c r="AG5">
-        <v>831.8</v>
-      </c>
-      <c r="AH5">
-        <v>0.9558854495683302</v>
-      </c>
-      <c r="AI5">
-        <v>0.896248766041461</v>
-      </c>
-      <c r="AJ5">
-        <v>0.9520430353668308</v>
-      </c>
-      <c r="AK5">
-        <v>0.887821539118369</v>
-      </c>
-      <c r="AL5">
-        <v>3.31</v>
-      </c>
-      <c r="AM5">
-        <v>3.242</v>
-      </c>
-      <c r="AO5">
-        <v>-15.16616314199396</v>
-      </c>
-      <c r="AQ5">
-        <v>-15.48426896977175</v>
+        <v>0.22</v>
+      </c>
+      <c r="W5">
+        <v>0.034866</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>74.52424814807689</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.0753111561966681</v>
+      </c>
+      <c r="C6">
+        <v>2143.451931481512</v>
+      </c>
+      <c r="D6">
+        <v>1354.939931481513</v>
+      </c>
+      <c r="E6">
+        <v>-1193.412</v>
+      </c>
+      <c r="F6">
+        <v>92.08799999999999</v>
+      </c>
+      <c r="G6">
+        <v>880.6</v>
+      </c>
+      <c r="H6">
+        <v>1016.7</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>279.375</v>
+      </c>
+      <c r="K6">
+        <v>49.30000000000001</v>
+      </c>
+      <c r="L6">
+        <v>230.075</v>
+      </c>
+      <c r="M6">
+        <v>4.1163336</v>
+      </c>
+      <c r="N6">
+        <v>225.9586664</v>
+      </c>
+      <c r="O6">
+        <v>49.710906608</v>
+      </c>
+      <c r="P6">
+        <v>176.247759792</v>
+      </c>
+      <c r="Q6">
+        <v>225.547759792</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.07699637103819594</v>
+      </c>
+      <c r="T6">
+        <v>0.8303558921346943</v>
+      </c>
+      <c r="U6">
+        <v>0.0447</v>
+      </c>
+      <c r="V6">
+        <v>0.22</v>
+      </c>
+      <c r="W6">
+        <v>0.034866</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>55.89318611105767</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.07519042925595719</v>
+      </c>
+      <c r="C7">
+        <v>2122.577364460758</v>
+      </c>
+      <c r="D7">
+        <v>1357.087364460758</v>
+      </c>
+      <c r="E7">
+        <v>-1170.39</v>
+      </c>
+      <c r="F7">
+        <v>115.11</v>
+      </c>
+      <c r="G7">
+        <v>880.6</v>
+      </c>
+      <c r="H7">
+        <v>1016.7</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>279.375</v>
+      </c>
+      <c r="K7">
+        <v>49.30000000000001</v>
+      </c>
+      <c r="L7">
+        <v>230.075</v>
+      </c>
+      <c r="M7">
+        <v>5.145417</v>
+      </c>
+      <c r="N7">
+        <v>224.929583</v>
+      </c>
+      <c r="O7">
+        <v>49.48450826</v>
+      </c>
+      <c r="P7">
+        <v>175.44507474</v>
+      </c>
+      <c r="Q7">
+        <v>224.74507474</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.07731276763784967</v>
+      </c>
+      <c r="T7">
+        <v>0.8372340790836883</v>
+      </c>
+      <c r="U7">
+        <v>0.0447</v>
+      </c>
+      <c r="V7">
+        <v>0.22</v>
+      </c>
+      <c r="W7">
+        <v>0.034866</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>44.71454888884612</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.07506970231524625</v>
+      </c>
+      <c r="C8">
+        <v>2101.709615142506</v>
+      </c>
+      <c r="D8">
+        <v>1359.241615142506</v>
+      </c>
+      <c r="E8">
+        <v>-1147.368</v>
+      </c>
+      <c r="F8">
+        <v>138.132</v>
+      </c>
+      <c r="G8">
+        <v>880.6</v>
+      </c>
+      <c r="H8">
+        <v>1016.7</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>279.375</v>
+      </c>
+      <c r="K8">
+        <v>49.30000000000001</v>
+      </c>
+      <c r="L8">
+        <v>230.075</v>
+      </c>
+      <c r="M8">
+        <v>6.174500399999999</v>
+      </c>
+      <c r="N8">
+        <v>223.9004996</v>
+      </c>
+      <c r="O8">
+        <v>49.25810991199999</v>
+      </c>
+      <c r="P8">
+        <v>174.642389688</v>
+      </c>
+      <c r="Q8">
+        <v>223.942389688</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.0776358960800492</v>
+      </c>
+      <c r="T8">
+        <v>0.8442586104358522</v>
+      </c>
+      <c r="U8">
+        <v>0.0447</v>
+      </c>
+      <c r="V8">
+        <v>0.22</v>
+      </c>
+      <c r="W8">
+        <v>0.034866</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>37.26212407403845</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.07494897537453533</v>
+      </c>
+      <c r="C9">
+        <v>2080.848716045792</v>
+      </c>
+      <c r="D9">
+        <v>1361.402716045792</v>
+      </c>
+      <c r="E9">
+        <v>-1124.346</v>
+      </c>
+      <c r="F9">
+        <v>161.154</v>
+      </c>
+      <c r="G9">
+        <v>880.6</v>
+      </c>
+      <c r="H9">
+        <v>1016.7</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>279.375</v>
+      </c>
+      <c r="K9">
+        <v>49.30000000000001</v>
+      </c>
+      <c r="L9">
+        <v>230.075</v>
+      </c>
+      <c r="M9">
+        <v>7.203583800000001</v>
+      </c>
+      <c r="N9">
+        <v>222.8714162</v>
+      </c>
+      <c r="O9">
+        <v>49.031711564</v>
+      </c>
+      <c r="P9">
+        <v>173.839704636</v>
+      </c>
+      <c r="Q9">
+        <v>223.139704636</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.07796597352100573</v>
+      </c>
+      <c r="T9">
+        <v>0.8514342069783853</v>
+      </c>
+      <c r="U9">
+        <v>0.0447</v>
+      </c>
+      <c r="V9">
+        <v>0.22</v>
+      </c>
+      <c r="W9">
+        <v>0.034866</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>31.93896349203295</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.07482824843382441</v>
+      </c>
+      <c r="C10">
+        <v>2059.994699896796</v>
+      </c>
+      <c r="D10">
+        <v>1363.570699896796</v>
+      </c>
+      <c r="E10">
+        <v>-1101.324</v>
+      </c>
+      <c r="F10">
+        <v>184.176</v>
+      </c>
+      <c r="G10">
+        <v>880.6</v>
+      </c>
+      <c r="H10">
+        <v>1016.7</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>279.375</v>
+      </c>
+      <c r="K10">
+        <v>49.30000000000001</v>
+      </c>
+      <c r="L10">
+        <v>230.075</v>
+      </c>
+      <c r="M10">
+        <v>8.2326672</v>
+      </c>
+      <c r="N10">
+        <v>221.8423328</v>
+      </c>
+      <c r="O10">
+        <v>48.80531321599999</v>
+      </c>
+      <c r="P10">
+        <v>173.037019584</v>
+      </c>
+      <c r="Q10">
+        <v>222.337019584</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.07830322655850477</v>
+      </c>
+      <c r="T10">
+        <v>0.8587657947501038</v>
+      </c>
+      <c r="U10">
+        <v>0.0447</v>
+      </c>
+      <c r="V10">
+        <v>0.22</v>
+      </c>
+      <c r="W10">
+        <v>0.034866</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>27.94659305552883</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.07470752149311348</v>
+      </c>
+      <c r="C11">
+        <v>2039.14759963049</v>
+      </c>
+      <c r="D11">
+        <v>1365.74559963049</v>
+      </c>
+      <c r="E11">
+        <v>-1078.302</v>
+      </c>
+      <c r="F11">
+        <v>207.198</v>
+      </c>
+      <c r="G11">
+        <v>880.6</v>
+      </c>
+      <c r="H11">
+        <v>1016.7</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>279.375</v>
+      </c>
+      <c r="K11">
+        <v>49.30000000000001</v>
+      </c>
+      <c r="L11">
+        <v>230.075</v>
+      </c>
+      <c r="M11">
+        <v>9.261750599999999</v>
+      </c>
+      <c r="N11">
+        <v>220.8132494</v>
+      </c>
+      <c r="O11">
+        <v>48.578914868</v>
+      </c>
+      <c r="P11">
+        <v>172.234334532</v>
+      </c>
+      <c r="Q11">
+        <v>221.534334532</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.07864789175067415</v>
+      </c>
+      <c r="T11">
+        <v>0.8662585163190031</v>
+      </c>
+      <c r="U11">
+        <v>0.0447</v>
+      </c>
+      <c r="V11">
+        <v>0.22</v>
+      </c>
+      <c r="W11">
+        <v>0.034866</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>24.84141604935896</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.07458679455240257</v>
+      </c>
+      <c r="C12">
+        <v>2018.307448392308</v>
+      </c>
+      <c r="D12">
+        <v>1367.927448392307</v>
+      </c>
+      <c r="E12">
+        <v>-1055.28</v>
+      </c>
+      <c r="F12">
+        <v>230.22</v>
+      </c>
+      <c r="G12">
+        <v>880.6</v>
+      </c>
+      <c r="H12">
+        <v>1016.7</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>279.375</v>
+      </c>
+      <c r="K12">
+        <v>49.30000000000001</v>
+      </c>
+      <c r="L12">
+        <v>230.075</v>
+      </c>
+      <c r="M12">
+        <v>10.290834</v>
+      </c>
+      <c r="N12">
+        <v>219.784166</v>
+      </c>
+      <c r="O12">
+        <v>48.35251652</v>
+      </c>
+      <c r="P12">
+        <v>171.43164948</v>
+      </c>
+      <c r="Q12">
+        <v>220.73164948</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.07900021616933617</v>
+      </c>
+      <c r="T12">
+        <v>0.8739177428116557</v>
+      </c>
+      <c r="U12">
+        <v>0.0447</v>
+      </c>
+      <c r="V12">
+        <v>0.22</v>
+      </c>
+      <c r="W12">
+        <v>0.034866</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>22.35727444442307</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.07446606761169161</v>
+      </c>
+      <c r="C13">
+        <v>1997.474279539829</v>
+      </c>
+      <c r="D13">
+        <v>1370.116279539829</v>
+      </c>
+      <c r="E13">
+        <v>-1032.258</v>
+      </c>
+      <c r="F13">
+        <v>253.242</v>
+      </c>
+      <c r="G13">
+        <v>880.6</v>
+      </c>
+      <c r="H13">
+        <v>1016.7</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>279.375</v>
+      </c>
+      <c r="K13">
+        <v>49.30000000000001</v>
+      </c>
+      <c r="L13">
+        <v>230.075</v>
+      </c>
+      <c r="M13">
+        <v>11.3199174</v>
+      </c>
+      <c r="N13">
+        <v>218.7550826</v>
+      </c>
+      <c r="O13">
+        <v>48.126118172</v>
+      </c>
+      <c r="P13">
+        <v>170.628964428</v>
+      </c>
+      <c r="Q13">
+        <v>219.928964428</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.07936045799066474</v>
+      </c>
+      <c r="T13">
+        <v>0.8817490867535813</v>
+      </c>
+      <c r="U13">
+        <v>0.0447</v>
+      </c>
+      <c r="V13">
+        <v>0.22</v>
+      </c>
+      <c r="W13">
+        <v>0.034866</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>20.32479494947551</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.07434534067098068</v>
+      </c>
+      <c r="C14">
+        <v>1976.648126644476</v>
+      </c>
+      <c r="D14">
+        <v>1372.312126644476</v>
+      </c>
+      <c r="E14">
+        <v>-1009.236</v>
+      </c>
+      <c r="F14">
+        <v>276.264</v>
+      </c>
+      <c r="G14">
+        <v>880.6</v>
+      </c>
+      <c r="H14">
+        <v>1016.7</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>279.375</v>
+      </c>
+      <c r="K14">
+        <v>49.30000000000001</v>
+      </c>
+      <c r="L14">
+        <v>230.075</v>
+      </c>
+      <c r="M14">
+        <v>12.3490008</v>
+      </c>
+      <c r="N14">
+        <v>217.7259992</v>
+      </c>
+      <c r="O14">
+        <v>47.89971982399999</v>
+      </c>
+      <c r="P14">
+        <v>169.826279376</v>
+      </c>
+      <c r="Q14">
+        <v>219.126279376</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.07972888712611442</v>
+      </c>
+      <c r="T14">
+        <v>0.8897584157850962</v>
+      </c>
+      <c r="U14">
+        <v>0.0447</v>
+      </c>
+      <c r="V14">
+        <v>0.22</v>
+      </c>
+      <c r="W14">
+        <v>0.034866</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>18.63106203701922</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.07422461373026976</v>
+      </c>
+      <c r="C15">
+        <v>1955.829023493236</v>
+      </c>
+      <c r="D15">
+        <v>1374.515023493236</v>
+      </c>
+      <c r="E15">
+        <v>-986.2139999999999</v>
+      </c>
+      <c r="F15">
+        <v>299.286</v>
+      </c>
+      <c r="G15">
+        <v>880.6</v>
+      </c>
+      <c r="H15">
+        <v>1016.7</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>279.375</v>
+      </c>
+      <c r="K15">
+        <v>49.30000000000001</v>
+      </c>
+      <c r="L15">
+        <v>230.075</v>
+      </c>
+      <c r="M15">
+        <v>13.3780842</v>
+      </c>
+      <c r="N15">
+        <v>216.6969158</v>
+      </c>
+      <c r="O15">
+        <v>47.673321476</v>
+      </c>
+      <c r="P15">
+        <v>169.023594324</v>
+      </c>
+      <c r="Q15">
+        <v>218.323594324</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.08010578589686179</v>
+      </c>
+      <c r="T15">
+        <v>0.8979518673230826</v>
+      </c>
+      <c r="U15">
+        <v>0.0447</v>
+      </c>
+      <c r="V15">
+        <v>0.22</v>
+      </c>
+      <c r="W15">
+        <v>0.034866</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>17.19790341878697</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.07410388678955884</v>
+      </c>
+      <c r="C16">
+        <v>1935.017004090386</v>
+      </c>
+      <c r="D16">
+        <v>1376.725004090386</v>
+      </c>
+      <c r="E16">
+        <v>-963.192</v>
+      </c>
+      <c r="F16">
+        <v>322.308</v>
+      </c>
+      <c r="G16">
+        <v>880.6</v>
+      </c>
+      <c r="H16">
+        <v>1016.7</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>279.375</v>
+      </c>
+      <c r="K16">
+        <v>49.30000000000001</v>
+      </c>
+      <c r="L16">
+        <v>230.075</v>
+      </c>
+      <c r="M16">
+        <v>14.4071676</v>
+      </c>
+      <c r="N16">
+        <v>215.6678324</v>
+      </c>
+      <c r="O16">
+        <v>47.44692312799999</v>
+      </c>
+      <c r="P16">
+        <v>168.220909272</v>
+      </c>
+      <c r="Q16">
+        <v>217.520909272</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.08049144975530098</v>
+      </c>
+      <c r="T16">
+        <v>0.9063358642456735</v>
+      </c>
+      <c r="U16">
+        <v>0.0447</v>
+      </c>
+      <c r="V16">
+        <v>0.22</v>
+      </c>
+      <c r="W16">
+        <v>0.034866</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>15.96948174601647</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.07398315984884792</v>
+      </c>
+      <c r="C17">
+        <v>1914.212102659252</v>
+      </c>
+      <c r="D17">
+        <v>1378.942102659252</v>
+      </c>
+      <c r="E17">
+        <v>-940.1700000000001</v>
+      </c>
+      <c r="F17">
+        <v>345.33</v>
+      </c>
+      <c r="G17">
+        <v>880.6</v>
+      </c>
+      <c r="H17">
+        <v>1016.7</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>279.375</v>
+      </c>
+      <c r="K17">
+        <v>49.30000000000001</v>
+      </c>
+      <c r="L17">
+        <v>230.075</v>
+      </c>
+      <c r="M17">
+        <v>15.436251</v>
+      </c>
+      <c r="N17">
+        <v>214.638749</v>
+      </c>
+      <c r="O17">
+        <v>47.22052478</v>
+      </c>
+      <c r="P17">
+        <v>167.41822422</v>
+      </c>
+      <c r="Q17">
+        <v>216.71822422</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.08088618805746814</v>
+      </c>
+      <c r="T17">
+        <v>0.9149171316840899</v>
+      </c>
+      <c r="U17">
+        <v>0.0447</v>
+      </c>
+      <c r="V17">
+        <v>0.22</v>
+      </c>
+      <c r="W17">
+        <v>0.034866</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>14.90484962961538</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.07386243290813699</v>
+      </c>
+      <c r="C18">
+        <v>1893.414353643966</v>
+      </c>
+      <c r="D18">
+        <v>1381.166353643966</v>
+      </c>
+      <c r="E18">
+        <v>-917.148</v>
+      </c>
+      <c r="F18">
+        <v>368.352</v>
+      </c>
+      <c r="G18">
+        <v>880.6</v>
+      </c>
+      <c r="H18">
+        <v>1016.7</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>279.375</v>
+      </c>
+      <c r="K18">
+        <v>49.30000000000001</v>
+      </c>
+      <c r="L18">
+        <v>230.075</v>
+      </c>
+      <c r="M18">
+        <v>16.4653344</v>
+      </c>
+      <c r="N18">
+        <v>213.6096656</v>
+      </c>
+      <c r="O18">
+        <v>46.994126432</v>
+      </c>
+      <c r="P18">
+        <v>166.615539168</v>
+      </c>
+      <c r="Q18">
+        <v>215.915539168</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.08129032489063928</v>
+      </c>
+      <c r="T18">
+        <v>0.9237027150138972</v>
+      </c>
+      <c r="U18">
+        <v>0.0447</v>
+      </c>
+      <c r="V18">
+        <v>0.22</v>
+      </c>
+      <c r="W18">
+        <v>0.034866</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>13.97329652776442</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.07374170596742606</v>
+      </c>
+      <c r="C19">
+        <v>1872.623791711259</v>
+      </c>
+      <c r="D19">
+        <v>1383.397791711259</v>
+      </c>
+      <c r="E19">
+        <v>-894.126</v>
+      </c>
+      <c r="F19">
+        <v>391.374</v>
+      </c>
+      <c r="G19">
+        <v>880.6</v>
+      </c>
+      <c r="H19">
+        <v>1016.7</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>279.375</v>
+      </c>
+      <c r="K19">
+        <v>49.30000000000001</v>
+      </c>
+      <c r="L19">
+        <v>230.075</v>
+      </c>
+      <c r="M19">
+        <v>17.4944178</v>
+      </c>
+      <c r="N19">
+        <v>212.5805822</v>
+      </c>
+      <c r="O19">
+        <v>46.767728084</v>
+      </c>
+      <c r="P19">
+        <v>165.812854116</v>
+      </c>
+      <c r="Q19">
+        <v>215.112854116</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.0817041999607543</v>
+      </c>
+      <c r="T19">
+        <v>0.9326999991468325</v>
+      </c>
+      <c r="U19">
+        <v>0.0447</v>
+      </c>
+      <c r="V19">
+        <v>0.22</v>
+      </c>
+      <c r="W19">
+        <v>0.034866</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>13.15133790848416</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.07377541902671515</v>
+      </c>
+      <c r="C20">
+        <v>1848.977936221039</v>
+      </c>
+      <c r="D20">
+        <v>1382.77393622104</v>
+      </c>
+      <c r="E20">
+        <v>-871.104</v>
+      </c>
+      <c r="F20">
+        <v>414.396</v>
+      </c>
+      <c r="G20">
+        <v>880.6</v>
+      </c>
+      <c r="H20">
+        <v>1016.7</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>279.375</v>
+      </c>
+      <c r="K20">
+        <v>49.30000000000001</v>
+      </c>
+      <c r="L20">
+        <v>230.075</v>
+      </c>
+      <c r="M20">
+        <v>18.9793368</v>
+      </c>
+      <c r="N20">
+        <v>211.0956632</v>
+      </c>
+      <c r="O20">
+        <v>46.441045904</v>
+      </c>
+      <c r="P20">
+        <v>164.654617296</v>
+      </c>
+      <c r="Q20">
+        <v>213.954617296</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.08212816954477456</v>
+      </c>
+      <c r="T20">
+        <v>0.9419167292342294</v>
+      </c>
+      <c r="U20">
+        <v>0.0458</v>
+      </c>
+      <c r="V20">
+        <v>0.22</v>
+      </c>
+      <c r="W20">
+        <v>0.035724</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>12.12239407648849</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.07366327208600422</v>
+      </c>
+      <c r="C21">
+        <v>1828.033380376047</v>
+      </c>
+      <c r="D21">
+        <v>1384.851380376047</v>
+      </c>
+      <c r="E21">
+        <v>-848.0820000000001</v>
+      </c>
+      <c r="F21">
+        <v>437.4179999999999</v>
+      </c>
+      <c r="G21">
+        <v>880.6</v>
+      </c>
+      <c r="H21">
+        <v>1016.7</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>279.375</v>
+      </c>
+      <c r="K21">
+        <v>49.30000000000001</v>
+      </c>
+      <c r="L21">
+        <v>230.075</v>
+      </c>
+      <c r="M21">
+        <v>20.0337444</v>
+      </c>
+      <c r="N21">
+        <v>210.0412556</v>
+      </c>
+      <c r="O21">
+        <v>46.209076232</v>
+      </c>
+      <c r="P21">
+        <v>163.832179368</v>
+      </c>
+      <c r="Q21">
+        <v>213.132179368</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.08256260751358545</v>
+      </c>
+      <c r="T21">
+        <v>0.9513610329040314</v>
+      </c>
+      <c r="U21">
+        <v>0.0458</v>
+      </c>
+      <c r="V21">
+        <v>0.22</v>
+      </c>
+      <c r="W21">
+        <v>0.035724</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>11.48437333562068</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.0735511251452933</v>
+      </c>
+      <c r="C22">
+        <v>1807.095076121092</v>
+      </c>
+      <c r="D22">
+        <v>1386.935076121092</v>
+      </c>
+      <c r="E22">
+        <v>-825.0599999999999</v>
+      </c>
+      <c r="F22">
+        <v>460.44</v>
+      </c>
+      <c r="G22">
+        <v>880.6</v>
+      </c>
+      <c r="H22">
+        <v>1016.7</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>279.375</v>
+      </c>
+      <c r="K22">
+        <v>49.30000000000001</v>
+      </c>
+      <c r="L22">
+        <v>230.075</v>
+      </c>
+      <c r="M22">
+        <v>21.088152</v>
+      </c>
+      <c r="N22">
+        <v>208.986848</v>
+      </c>
+      <c r="O22">
+        <v>45.97710656</v>
+      </c>
+      <c r="P22">
+        <v>163.00974144</v>
+      </c>
+      <c r="Q22">
+        <v>212.30974144</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.08300790643161661</v>
+      </c>
+      <c r="T22">
+        <v>0.9610414441655785</v>
+      </c>
+      <c r="U22">
+        <v>0.0458</v>
+      </c>
+      <c r="V22">
+        <v>0.22</v>
+      </c>
+      <c r="W22">
+        <v>0.035724</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>10.91015466883964</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.07343897820458237</v>
+      </c>
+      <c r="C23">
+        <v>1786.16305171778</v>
+      </c>
+      <c r="D23">
+        <v>1389.02505171778</v>
+      </c>
+      <c r="E23">
+        <v>-802.038</v>
+      </c>
+      <c r="F23">
+        <v>483.4619999999999</v>
+      </c>
+      <c r="G23">
+        <v>880.6</v>
+      </c>
+      <c r="H23">
+        <v>1016.7</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>279.375</v>
+      </c>
+      <c r="K23">
+        <v>49.30000000000001</v>
+      </c>
+      <c r="L23">
+        <v>230.075</v>
+      </c>
+      <c r="M23">
+        <v>22.1425596</v>
+      </c>
+      <c r="N23">
+        <v>207.9324404</v>
+      </c>
+      <c r="O23">
+        <v>45.745136888</v>
+      </c>
+      <c r="P23">
+        <v>162.187303512</v>
+      </c>
+      <c r="Q23">
+        <v>211.487303512</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.08346447873997767</v>
+      </c>
+      <c r="T23">
+        <v>0.9709669291299492</v>
+      </c>
+      <c r="U23">
+        <v>0.0458</v>
+      </c>
+      <c r="V23">
+        <v>0.22</v>
+      </c>
+      <c r="W23">
+        <v>0.035724</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>10.39062349413299</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.07370435126387144</v>
+      </c>
+      <c r="C24">
+        <v>1758.205693065971</v>
+      </c>
+      <c r="D24">
+        <v>1384.08969306597</v>
+      </c>
+      <c r="E24">
+        <v>-779.0160000000001</v>
+      </c>
+      <c r="F24">
+        <v>506.484</v>
+      </c>
+      <c r="G24">
+        <v>880.6</v>
+      </c>
+      <c r="H24">
+        <v>1016.7</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>279.375</v>
+      </c>
+      <c r="K24">
+        <v>49.30000000000001</v>
+      </c>
+      <c r="L24">
+        <v>230.075</v>
+      </c>
+      <c r="M24">
+        <v>24.311232</v>
+      </c>
+      <c r="N24">
+        <v>205.763768</v>
+      </c>
+      <c r="O24">
+        <v>45.26802896</v>
+      </c>
+      <c r="P24">
+        <v>160.49573904</v>
+      </c>
+      <c r="Q24">
+        <v>209.79573904</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.0839327580306044</v>
+      </c>
+      <c r="T24">
+        <v>0.9811469137087913</v>
+      </c>
+      <c r="U24">
+        <v>0.048</v>
+      </c>
+      <c r="V24">
+        <v>0.22</v>
+      </c>
+      <c r="W24">
+        <v>0.03744</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>9.463732648349536</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.07360936432316051</v>
+      </c>
+      <c r="C25">
+        <v>1736.946207275025</v>
+      </c>
+      <c r="D25">
+        <v>1385.852207275025</v>
+      </c>
+      <c r="E25">
+        <v>-755.994</v>
+      </c>
+      <c r="F25">
+        <v>529.506</v>
+      </c>
+      <c r="G25">
+        <v>880.6</v>
+      </c>
+      <c r="H25">
+        <v>1016.7</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>279.375</v>
+      </c>
+      <c r="K25">
+        <v>49.30000000000001</v>
+      </c>
+      <c r="L25">
+        <v>230.075</v>
+      </c>
+      <c r="M25">
+        <v>25.416288</v>
+      </c>
+      <c r="N25">
+        <v>204.658712</v>
+      </c>
+      <c r="O25">
+        <v>45.02491663999999</v>
+      </c>
+      <c r="P25">
+        <v>159.63379536</v>
+      </c>
+      <c r="Q25">
+        <v>208.93379536</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.08441320041968897</v>
+      </c>
+      <c r="T25">
+        <v>0.9915913134714994</v>
+      </c>
+      <c r="U25">
+        <v>0.048</v>
+      </c>
+      <c r="V25">
+        <v>0.22</v>
+      </c>
+      <c r="W25">
+        <v>0.03744</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>9.052266011464773</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.07351437738244958</v>
+      </c>
+      <c r="C26">
+        <v>1715.691216015309</v>
+      </c>
+      <c r="D26">
+        <v>1387.619216015309</v>
+      </c>
+      <c r="E26">
+        <v>-732.9720000000001</v>
+      </c>
+      <c r="F26">
+        <v>552.5279999999999</v>
+      </c>
+      <c r="G26">
+        <v>880.6</v>
+      </c>
+      <c r="H26">
+        <v>1016.7</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>279.375</v>
+      </c>
+      <c r="K26">
+        <v>49.30000000000001</v>
+      </c>
+      <c r="L26">
+        <v>230.075</v>
+      </c>
+      <c r="M26">
+        <v>26.521344</v>
+      </c>
+      <c r="N26">
+        <v>203.553656</v>
+      </c>
+      <c r="O26">
+        <v>44.78180432</v>
+      </c>
+      <c r="P26">
+        <v>158.77185168</v>
+      </c>
+      <c r="Q26">
+        <v>208.07185168</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.08490628602953892</v>
+      </c>
+      <c r="T26">
+        <v>1.002310565859542</v>
+      </c>
+      <c r="U26">
+        <v>0.048</v>
+      </c>
+      <c r="V26">
+        <v>0.22</v>
+      </c>
+      <c r="W26">
+        <v>0.03744</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>8.675088260987076</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.07341939044173867</v>
+      </c>
+      <c r="C27">
+        <v>1694.440736500811</v>
+      </c>
+      <c r="D27">
+        <v>1389.390736500811</v>
+      </c>
+      <c r="E27">
+        <v>-709.95</v>
+      </c>
+      <c r="F27">
+        <v>575.55</v>
+      </c>
+      <c r="G27">
+        <v>880.6</v>
+      </c>
+      <c r="H27">
+        <v>1016.7</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>279.375</v>
+      </c>
+      <c r="K27">
+        <v>49.30000000000001</v>
+      </c>
+      <c r="L27">
+        <v>230.075</v>
+      </c>
+      <c r="M27">
+        <v>27.6264</v>
+      </c>
+      <c r="N27">
+        <v>202.4486</v>
+      </c>
+      <c r="O27">
+        <v>44.538692</v>
+      </c>
+      <c r="P27">
+        <v>157.909908</v>
+      </c>
+      <c r="Q27">
+        <v>207.209908</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.08541252058898488</v>
+      </c>
+      <c r="T27">
+        <v>1.013315664977932</v>
+      </c>
+      <c r="U27">
+        <v>0.048</v>
+      </c>
+      <c r="V27">
+        <v>0.22</v>
+      </c>
+      <c r="W27">
+        <v>0.03744</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>8.328084730547593</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.07332440350102774</v>
+      </c>
+      <c r="C28">
+        <v>1673.19478603354</v>
+      </c>
+      <c r="D28">
+        <v>1391.16678603354</v>
+      </c>
+      <c r="E28">
+        <v>-686.928</v>
+      </c>
+      <c r="F28">
+        <v>598.572</v>
+      </c>
+      <c r="G28">
+        <v>880.6</v>
+      </c>
+      <c r="H28">
+        <v>1016.7</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>279.375</v>
+      </c>
+      <c r="K28">
+        <v>49.30000000000001</v>
+      </c>
+      <c r="L28">
+        <v>230.075</v>
+      </c>
+      <c r="M28">
+        <v>28.731456</v>
+      </c>
+      <c r="N28">
+        <v>201.343544</v>
+      </c>
+      <c r="O28">
+        <v>44.29557968</v>
+      </c>
+      <c r="P28">
+        <v>157.04796432</v>
+      </c>
+      <c r="Q28">
+        <v>206.34796432</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.08593243716355099</v>
+      </c>
+      <c r="T28">
+        <v>1.02461819920763</v>
+      </c>
+      <c r="U28">
+        <v>0.048</v>
+      </c>
+      <c r="V28">
+        <v>0.22</v>
+      </c>
+      <c r="W28">
+        <v>0.03744</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>8.007773779372684</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.07354531656031682</v>
+      </c>
+      <c r="C29">
+        <v>1646.049170729222</v>
+      </c>
+      <c r="D29">
+        <v>1387.043170729222</v>
+      </c>
+      <c r="E29">
+        <v>-663.9060000000001</v>
+      </c>
+      <c r="F29">
+        <v>621.5939999999999</v>
+      </c>
+      <c r="G29">
+        <v>880.6</v>
+      </c>
+      <c r="H29">
+        <v>1016.7</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>279.375</v>
+      </c>
+      <c r="K29">
+        <v>49.30000000000001</v>
+      </c>
+      <c r="L29">
+        <v>230.075</v>
+      </c>
+      <c r="M29">
+        <v>30.768903</v>
+      </c>
+      <c r="N29">
+        <v>199.306097</v>
+      </c>
+      <c r="O29">
+        <v>43.84734134</v>
+      </c>
+      <c r="P29">
+        <v>155.45875566</v>
+      </c>
+      <c r="Q29">
+        <v>204.75875566</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.08646659802783124</v>
+      </c>
+      <c r="T29">
+        <v>1.036230391909375</v>
+      </c>
+      <c r="U29">
+        <v>0.0495</v>
+      </c>
+      <c r="V29">
+        <v>0.22</v>
+      </c>
+      <c r="W29">
+        <v>0.03861000000000001</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>7.477517154251486</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.07346202961960588</v>
+      </c>
+      <c r="C30">
+        <v>1624.578950349572</v>
+      </c>
+      <c r="D30">
+        <v>1388.594950349572</v>
+      </c>
+      <c r="E30">
+        <v>-640.884</v>
+      </c>
+      <c r="F30">
+        <v>644.616</v>
+      </c>
+      <c r="G30">
+        <v>880.6</v>
+      </c>
+      <c r="H30">
+        <v>1016.7</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>279.375</v>
+      </c>
+      <c r="K30">
+        <v>49.30000000000001</v>
+      </c>
+      <c r="L30">
+        <v>230.075</v>
+      </c>
+      <c r="M30">
+        <v>31.908492</v>
+      </c>
+      <c r="N30">
+        <v>198.166508</v>
+      </c>
+      <c r="O30">
+        <v>43.59663176</v>
+      </c>
+      <c r="P30">
+        <v>154.56987624</v>
+      </c>
+      <c r="Q30">
+        <v>203.86987624</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.08701559669389705</v>
+      </c>
+      <c r="T30">
+        <v>1.048165145519501</v>
+      </c>
+      <c r="U30">
+        <v>0.0495</v>
+      </c>
+      <c r="V30">
+        <v>0.22</v>
+      </c>
+      <c r="W30">
+        <v>0.03861000000000001</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>7.210462970171075</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.07337874267889495</v>
+      </c>
+      <c r="C31">
+        <v>1603.112206021821</v>
+      </c>
+      <c r="D31">
+        <v>1390.150206021821</v>
+      </c>
+      <c r="E31">
+        <v>-617.8620000000001</v>
+      </c>
+      <c r="F31">
+        <v>667.6379999999999</v>
+      </c>
+      <c r="G31">
+        <v>880.6</v>
+      </c>
+      <c r="H31">
+        <v>1016.7</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>279.375</v>
+      </c>
+      <c r="K31">
+        <v>49.30000000000001</v>
+      </c>
+      <c r="L31">
+        <v>230.075</v>
+      </c>
+      <c r="M31">
+        <v>33.048081</v>
+      </c>
+      <c r="N31">
+        <v>197.026919</v>
+      </c>
+      <c r="O31">
+        <v>43.34592218</v>
+      </c>
+      <c r="P31">
+        <v>153.68099682</v>
+      </c>
+      <c r="Q31">
+        <v>202.98099682</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.08758006011111966</v>
+      </c>
+      <c r="T31">
+        <v>1.060436089372166</v>
+      </c>
+      <c r="U31">
+        <v>0.0495</v>
+      </c>
+      <c r="V31">
+        <v>0.22</v>
+      </c>
+      <c r="W31">
+        <v>0.03861000000000001</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>6.961826316027246</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.07329545573818402</v>
+      </c>
+      <c r="C32">
+        <v>1581.648949438818</v>
+      </c>
+      <c r="D32">
+        <v>1391.708949438818</v>
+      </c>
+      <c r="E32">
+        <v>-594.84</v>
+      </c>
+      <c r="F32">
+        <v>690.66</v>
+      </c>
+      <c r="G32">
+        <v>880.6</v>
+      </c>
+      <c r="H32">
+        <v>1016.7</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>279.375</v>
+      </c>
+      <c r="K32">
+        <v>49.30000000000001</v>
+      </c>
+      <c r="L32">
+        <v>230.075</v>
+      </c>
+      <c r="M32">
+        <v>34.18767</v>
+      </c>
+      <c r="N32">
+        <v>195.88733</v>
+      </c>
+      <c r="O32">
+        <v>43.0952126</v>
+      </c>
+      <c r="P32">
+        <v>152.7921174</v>
+      </c>
+      <c r="Q32">
+        <v>202.0921174</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.08816065105454861</v>
+      </c>
+      <c r="T32">
+        <v>1.073057631620622</v>
+      </c>
+      <c r="U32">
+        <v>0.0495</v>
+      </c>
+      <c r="V32">
+        <v>0.22</v>
+      </c>
+      <c r="W32">
+        <v>0.03861000000000001</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>6.729765438826337</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.07321216879747308</v>
+      </c>
+      <c r="C33">
+        <v>1560.189192345919</v>
+      </c>
+      <c r="D33">
+        <v>1393.271192345919</v>
+      </c>
+      <c r="E33">
+        <v>-571.8180000000001</v>
+      </c>
+      <c r="F33">
+        <v>713.6819999999999</v>
+      </c>
+      <c r="G33">
+        <v>880.6</v>
+      </c>
+      <c r="H33">
+        <v>1016.7</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>279.375</v>
+      </c>
+      <c r="K33">
+        <v>49.30000000000001</v>
+      </c>
+      <c r="L33">
+        <v>230.075</v>
+      </c>
+      <c r="M33">
+        <v>35.327259</v>
+      </c>
+      <c r="N33">
+        <v>194.747741</v>
+      </c>
+      <c r="O33">
+        <v>42.84450302</v>
+      </c>
+      <c r="P33">
+        <v>151.90323798</v>
+      </c>
+      <c r="Q33">
+        <v>201.20323798</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.0887580707209755</v>
+      </c>
+      <c r="T33">
+        <v>1.086045015673381</v>
+      </c>
+      <c r="U33">
+        <v>0.0495</v>
+      </c>
+      <c r="V33">
+        <v>0.22</v>
+      </c>
+      <c r="W33">
+        <v>0.03861000000000001</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>6.512676231122262</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.07312888185676217</v>
+      </c>
+      <c r="C34">
+        <v>1538.732946541272</v>
+      </c>
+      <c r="D34">
+        <v>1394.836946541272</v>
+      </c>
+      <c r="E34">
+        <v>-548.796</v>
+      </c>
+      <c r="F34">
+        <v>736.704</v>
+      </c>
+      <c r="G34">
+        <v>880.6</v>
+      </c>
+      <c r="H34">
+        <v>1016.7</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>279.375</v>
+      </c>
+      <c r="K34">
+        <v>49.30000000000001</v>
+      </c>
+      <c r="L34">
+        <v>230.075</v>
+      </c>
+      <c r="M34">
+        <v>36.466848</v>
+      </c>
+      <c r="N34">
+        <v>193.608152</v>
+      </c>
+      <c r="O34">
+        <v>42.59379344</v>
+      </c>
+      <c r="P34">
+        <v>151.01435856</v>
+      </c>
+      <c r="Q34">
+        <v>200.31435856</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.08937306155406202</v>
+      </c>
+      <c r="T34">
+        <v>1.099414381610044</v>
+      </c>
+      <c r="U34">
+        <v>0.0495</v>
+      </c>
+      <c r="V34">
+        <v>0.22</v>
+      </c>
+      <c r="W34">
+        <v>0.03861000000000001</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>6.309155098899691</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.07340595491605124</v>
+      </c>
+      <c r="C35">
+        <v>1510.515676254297</v>
+      </c>
+      <c r="D35">
+        <v>1389.641676254297</v>
+      </c>
+      <c r="E35">
+        <v>-525.774</v>
+      </c>
+      <c r="F35">
+        <v>759.726</v>
+      </c>
+      <c r="G35">
+        <v>880.6</v>
+      </c>
+      <c r="H35">
+        <v>1016.7</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>279.375</v>
+      </c>
+      <c r="K35">
+        <v>49.30000000000001</v>
+      </c>
+      <c r="L35">
+        <v>230.075</v>
+      </c>
+      <c r="M35">
+        <v>38.6700534</v>
+      </c>
+      <c r="N35">
+        <v>191.4049466</v>
+      </c>
+      <c r="O35">
+        <v>42.109088252</v>
+      </c>
+      <c r="P35">
+        <v>149.295858348</v>
+      </c>
+      <c r="Q35">
+        <v>198.595858348</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.09000641032246455</v>
+      </c>
+      <c r="T35">
+        <v>1.113182833097055</v>
+      </c>
+      <c r="U35">
+        <v>0.0509</v>
+      </c>
+      <c r="V35">
+        <v>0.22</v>
+      </c>
+      <c r="W35">
+        <v>0.039702</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>5.949694395818962</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.07333358797534031</v>
+      </c>
+      <c r="C36">
+        <v>1488.846858036829</v>
+      </c>
+      <c r="D36">
+        <v>1390.994858036829</v>
+      </c>
+      <c r="E36">
+        <v>-502.752</v>
+      </c>
+      <c r="F36">
+        <v>782.748</v>
+      </c>
+      <c r="G36">
+        <v>880.6</v>
+      </c>
+      <c r="H36">
+        <v>1016.7</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>279.375</v>
+      </c>
+      <c r="K36">
+        <v>49.30000000000001</v>
+      </c>
+      <c r="L36">
+        <v>230.075</v>
+      </c>
+      <c r="M36">
+        <v>39.8418732</v>
+      </c>
+      <c r="N36">
+        <v>190.2331268</v>
+      </c>
+      <c r="O36">
+        <v>41.851287896</v>
+      </c>
+      <c r="P36">
+        <v>148.381838904</v>
+      </c>
+      <c r="Q36">
+        <v>197.681838904</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.09065895147778835</v>
+      </c>
+      <c r="T36">
+        <v>1.127368510386703</v>
+      </c>
+      <c r="U36">
+        <v>0.0509</v>
+      </c>
+      <c r="V36">
+        <v>0.22</v>
+      </c>
+      <c r="W36">
+        <v>0.039702</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>5.774703384177228</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.07326122103462938</v>
+      </c>
+      <c r="C37">
+        <v>1467.180677745043</v>
+      </c>
+      <c r="D37">
+        <v>1392.350677745043</v>
+      </c>
+      <c r="E37">
+        <v>-479.73</v>
+      </c>
+      <c r="F37">
+        <v>805.77</v>
+      </c>
+      <c r="G37">
+        <v>880.6</v>
+      </c>
+      <c r="H37">
+        <v>1016.7</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>279.375</v>
+      </c>
+      <c r="K37">
+        <v>49.30000000000001</v>
+      </c>
+      <c r="L37">
+        <v>230.075</v>
+      </c>
+      <c r="M37">
+        <v>41.013693</v>
+      </c>
+      <c r="N37">
+        <v>189.061307</v>
+      </c>
+      <c r="O37">
+        <v>41.59348754</v>
+      </c>
+      <c r="P37">
+        <v>147.46781946</v>
+      </c>
+      <c r="Q37">
+        <v>196.76781946</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.09133157082250676</v>
+      </c>
+      <c r="T37">
+        <v>1.141990670054495</v>
+      </c>
+      <c r="U37">
+        <v>0.0509</v>
+      </c>
+      <c r="V37">
+        <v>0.22</v>
+      </c>
+      <c r="W37">
+        <v>0.039702</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>5.609711858915022</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.07318885409391847</v>
+      </c>
+      <c r="C38">
+        <v>1445.51714310012</v>
+      </c>
+      <c r="D38">
+        <v>1393.70914310012</v>
+      </c>
+      <c r="E38">
+        <v>-456.7080000000001</v>
+      </c>
+      <c r="F38">
+        <v>828.7919999999999</v>
+      </c>
+      <c r="G38">
+        <v>880.6</v>
+      </c>
+      <c r="H38">
+        <v>1016.7</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>279.375</v>
+      </c>
+      <c r="K38">
+        <v>49.30000000000001</v>
+      </c>
+      <c r="L38">
+        <v>230.075</v>
+      </c>
+      <c r="M38">
+        <v>42.1855128</v>
+      </c>
+      <c r="N38">
+        <v>187.8894872</v>
+      </c>
+      <c r="O38">
+        <v>41.335687184</v>
+      </c>
+      <c r="P38">
+        <v>146.553800016</v>
+      </c>
+      <c r="Q38">
+        <v>195.853800016</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.09202520952174761</v>
+      </c>
+      <c r="T38">
+        <v>1.157069772211905</v>
+      </c>
+      <c r="U38">
+        <v>0.0509</v>
+      </c>
+      <c r="V38">
+        <v>0.22</v>
+      </c>
+      <c r="W38">
+        <v>0.039702</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>5.453886529500715</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.07311648715320754</v>
+      </c>
+      <c r="C39">
+        <v>1423.856261853404</v>
+      </c>
+      <c r="D39">
+        <v>1395.070261853404</v>
+      </c>
+      <c r="E39">
+        <v>-433.686</v>
+      </c>
+      <c r="F39">
+        <v>851.814</v>
+      </c>
+      <c r="G39">
+        <v>880.6</v>
+      </c>
+      <c r="H39">
+        <v>1016.7</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>279.375</v>
+      </c>
+      <c r="K39">
+        <v>49.30000000000001</v>
+      </c>
+      <c r="L39">
+        <v>230.075</v>
+      </c>
+      <c r="M39">
+        <v>43.3573326</v>
+      </c>
+      <c r="N39">
+        <v>186.7176674</v>
+      </c>
+      <c r="O39">
+        <v>41.077886828</v>
+      </c>
+      <c r="P39">
+        <v>145.639780572</v>
+      </c>
+      <c r="Q39">
+        <v>194.939780572</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.09274086849715484</v>
+      </c>
+      <c r="T39">
+        <v>1.172627576025105</v>
+      </c>
+      <c r="U39">
+        <v>0.0509</v>
+      </c>
+      <c r="V39">
+        <v>0.22</v>
+      </c>
+      <c r="W39">
+        <v>0.039702</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>5.30648419086556</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.07304412021249662</v>
+      </c>
+      <c r="C40">
+        <v>1402.198041786547</v>
+      </c>
+      <c r="D40">
+        <v>1396.434041786547</v>
+      </c>
+      <c r="E40">
+        <v>-410.6640000000001</v>
+      </c>
+      <c r="F40">
+        <v>874.8359999999999</v>
+      </c>
+      <c r="G40">
+        <v>880.6</v>
+      </c>
+      <c r="H40">
+        <v>1016.7</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>279.375</v>
+      </c>
+      <c r="K40">
+        <v>49.30000000000001</v>
+      </c>
+      <c r="L40">
+        <v>230.075</v>
+      </c>
+      <c r="M40">
+        <v>44.52915239999999</v>
+      </c>
+      <c r="N40">
+        <v>185.5458476</v>
+      </c>
+      <c r="O40">
+        <v>40.820086472</v>
+      </c>
+      <c r="P40">
+        <v>144.725761128</v>
+      </c>
+      <c r="Q40">
+        <v>194.025761128</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.0934796132459623</v>
+      </c>
+      <c r="T40">
+        <v>1.188687244477441</v>
+      </c>
+      <c r="U40">
+        <v>0.0509</v>
+      </c>
+      <c r="V40">
+        <v>0.22</v>
+      </c>
+      <c r="W40">
+        <v>0.039702</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>5.16683987005331</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.07297175327178569</v>
+      </c>
+      <c r="C41">
+        <v>1380.542490711664</v>
+      </c>
+      <c r="D41">
+        <v>1397.800490711664</v>
+      </c>
+      <c r="E41">
+        <v>-387.6420000000001</v>
+      </c>
+      <c r="F41">
+        <v>897.8579999999999</v>
+      </c>
+      <c r="G41">
+        <v>880.6</v>
+      </c>
+      <c r="H41">
+        <v>1016.7</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>279.375</v>
+      </c>
+      <c r="K41">
+        <v>49.30000000000001</v>
+      </c>
+      <c r="L41">
+        <v>230.075</v>
+      </c>
+      <c r="M41">
+        <v>45.7009722</v>
+      </c>
+      <c r="N41">
+        <v>184.3740278</v>
+      </c>
+      <c r="O41">
+        <v>40.562286116</v>
+      </c>
+      <c r="P41">
+        <v>143.811741684</v>
+      </c>
+      <c r="Q41">
+        <v>193.111741684</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.09424257913407491</v>
+      </c>
+      <c r="T41">
+        <v>1.205273459436411</v>
+      </c>
+      <c r="U41">
+        <v>0.0509</v>
+      </c>
+      <c r="V41">
+        <v>0.22</v>
+      </c>
+      <c r="W41">
+        <v>0.039702</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>5.034356796462199</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.07289938633107476</v>
+      </c>
+      <c r="C42">
+        <v>1358.889616471472</v>
+      </c>
+      <c r="D42">
+        <v>1399.169616471472</v>
+      </c>
+      <c r="E42">
+        <v>-364.62</v>
+      </c>
+      <c r="F42">
+        <v>920.88</v>
+      </c>
+      <c r="G42">
+        <v>880.6</v>
+      </c>
+      <c r="H42">
+        <v>1016.7</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>279.375</v>
+      </c>
+      <c r="K42">
+        <v>49.30000000000001</v>
+      </c>
+      <c r="L42">
+        <v>230.075</v>
+      </c>
+      <c r="M42">
+        <v>46.872792</v>
+      </c>
+      <c r="N42">
+        <v>183.202208</v>
+      </c>
+      <c r="O42">
+        <v>40.30448576</v>
+      </c>
+      <c r="P42">
+        <v>142.89772224</v>
+      </c>
+      <c r="Q42">
+        <v>192.19772224</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.09503097721845793</v>
+      </c>
+      <c r="T42">
+        <v>1.222412548227346</v>
+      </c>
+      <c r="U42">
+        <v>0.0509</v>
+      </c>
+      <c r="V42">
+        <v>0.22</v>
+      </c>
+      <c r="W42">
+        <v>0.039702</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>4.908497876550642</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.07282701939036385</v>
+      </c>
+      <c r="C43">
+        <v>1337.239426939449</v>
+      </c>
+      <c r="D43">
+        <v>1400.541426939448</v>
+      </c>
+      <c r="E43">
+        <v>-341.598</v>
+      </c>
+      <c r="F43">
+        <v>943.902</v>
+      </c>
+      <c r="G43">
+        <v>880.6</v>
+      </c>
+      <c r="H43">
+        <v>1016.7</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>279.375</v>
+      </c>
+      <c r="K43">
+        <v>49.30000000000001</v>
+      </c>
+      <c r="L43">
+        <v>230.075</v>
+      </c>
+      <c r="M43">
+        <v>48.04461180000001</v>
+      </c>
+      <c r="N43">
+        <v>182.0303882</v>
+      </c>
+      <c r="O43">
+        <v>40.04668540399999</v>
+      </c>
+      <c r="P43">
+        <v>141.983702796</v>
+      </c>
+      <c r="Q43">
+        <v>191.283702796</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.09584610066163363</v>
+      </c>
+      <c r="T43">
+        <v>1.240132623078992</v>
+      </c>
+      <c r="U43">
+        <v>0.0509</v>
+      </c>
+      <c r="V43">
+        <v>0.22</v>
+      </c>
+      <c r="W43">
+        <v>0.039702</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>4.788778416146968</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.07275465244965292</v>
+      </c>
+      <c r="C44">
+        <v>1315.591930019979</v>
+      </c>
+      <c r="D44">
+        <v>1401.915930019979</v>
+      </c>
+      <c r="E44">
+        <v>-318.5760000000001</v>
+      </c>
+      <c r="F44">
+        <v>966.9239999999999</v>
+      </c>
+      <c r="G44">
+        <v>880.6</v>
+      </c>
+      <c r="H44">
+        <v>1016.7</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>279.375</v>
+      </c>
+      <c r="K44">
+        <v>49.30000000000001</v>
+      </c>
+      <c r="L44">
+        <v>230.075</v>
+      </c>
+      <c r="M44">
+        <v>49.21643159999999</v>
+      </c>
+      <c r="N44">
+        <v>180.8585684</v>
+      </c>
+      <c r="O44">
+        <v>39.788885048</v>
+      </c>
+      <c r="P44">
+        <v>141.069683352</v>
+      </c>
+      <c r="Q44">
+        <v>190.369683352</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.0966893318097464</v>
+      </c>
+      <c r="T44">
+        <v>1.258463734994487</v>
+      </c>
+      <c r="U44">
+        <v>0.0509</v>
+      </c>
+      <c r="V44">
+        <v>0.22</v>
+      </c>
+      <c r="W44">
+        <v>0.039702</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>4.674759882429185</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.072682285508942</v>
+      </c>
+      <c r="C45">
+        <v>1293.947133648508</v>
+      </c>
+      <c r="D45">
+        <v>1403.293133648509</v>
+      </c>
+      <c r="E45">
+        <v>-295.5540000000001</v>
+      </c>
+      <c r="F45">
+        <v>989.9459999999999</v>
+      </c>
+      <c r="G45">
+        <v>880.6</v>
+      </c>
+      <c r="H45">
+        <v>1016.7</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>279.375</v>
+      </c>
+      <c r="K45">
+        <v>49.30000000000001</v>
+      </c>
+      <c r="L45">
+        <v>230.075</v>
+      </c>
+      <c r="M45">
+        <v>50.38825139999999</v>
+      </c>
+      <c r="N45">
+        <v>179.6867486</v>
+      </c>
+      <c r="O45">
+        <v>39.531084692</v>
+      </c>
+      <c r="P45">
+        <v>140.155663908</v>
+      </c>
+      <c r="Q45">
+        <v>189.455663908</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.0975621500156877</v>
+      </c>
+      <c r="T45">
+        <v>1.277438043819298</v>
+      </c>
+      <c r="U45">
+        <v>0.0509</v>
+      </c>
+      <c r="V45">
+        <v>0.22</v>
+      </c>
+      <c r="W45">
+        <v>0.039702</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>4.56604453632618</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.07350223856823107</v>
+      </c>
+      <c r="C46">
+        <v>1255.47735488667</v>
+      </c>
+      <c r="D46">
+        <v>1387.845354886669</v>
+      </c>
+      <c r="E46">
+        <v>-272.532</v>
+      </c>
+      <c r="F46">
+        <v>1012.968</v>
+      </c>
+      <c r="G46">
+        <v>880.6</v>
+      </c>
+      <c r="H46">
+        <v>1016.7</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>279.375</v>
+      </c>
+      <c r="K46">
+        <v>49.30000000000001</v>
+      </c>
+      <c r="L46">
+        <v>230.075</v>
+      </c>
+      <c r="M46">
+        <v>54.193788</v>
+      </c>
+      <c r="N46">
+        <v>175.881212</v>
+      </c>
+      <c r="O46">
+        <v>38.69386664</v>
+      </c>
+      <c r="P46">
+        <v>137.18734536</v>
+      </c>
+      <c r="Q46">
+        <v>186.48734536</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.09846614030041262</v>
+      </c>
+      <c r="T46">
+        <v>1.297090006530709</v>
+      </c>
+      <c r="U46">
+        <v>0.0535</v>
+      </c>
+      <c r="V46">
+        <v>0.22</v>
+      </c>
+      <c r="W46">
+        <v>0.04173</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>4.245412776829699</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.07345015162752014</v>
+      </c>
+      <c r="C47">
+        <v>1233.426540813904</v>
+      </c>
+      <c r="D47">
+        <v>1388.816540813904</v>
+      </c>
+      <c r="E47">
+        <v>-249.51</v>
+      </c>
+      <c r="F47">
+        <v>1035.99</v>
+      </c>
+      <c r="G47">
+        <v>880.6</v>
+      </c>
+      <c r="H47">
+        <v>1016.7</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>279.375</v>
+      </c>
+      <c r="K47">
+        <v>49.30000000000001</v>
+      </c>
+      <c r="L47">
+        <v>230.075</v>
+      </c>
+      <c r="M47">
+        <v>55.425465</v>
+      </c>
+      <c r="N47">
+        <v>174.649535</v>
+      </c>
+      <c r="O47">
+        <v>38.4228977</v>
+      </c>
+      <c r="P47">
+        <v>136.2266373</v>
+      </c>
+      <c r="Q47">
+        <v>185.5266373</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.09940300295912752</v>
+      </c>
+      <c r="T47">
+        <v>1.317456586067989</v>
+      </c>
+      <c r="U47">
+        <v>0.0535</v>
+      </c>
+      <c r="V47">
+        <v>0.22</v>
+      </c>
+      <c r="W47">
+        <v>0.04173</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>4.151070270677927</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.07339806468680921</v>
+      </c>
+      <c r="C48">
+        <v>1211.377086925252</v>
+      </c>
+      <c r="D48">
+        <v>1389.789086925252</v>
+      </c>
+      <c r="E48">
+        <v>-226.4880000000001</v>
+      </c>
+      <c r="F48">
+        <v>1059.012</v>
+      </c>
+      <c r="G48">
+        <v>880.6</v>
+      </c>
+      <c r="H48">
+        <v>1016.7</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>279.375</v>
+      </c>
+      <c r="K48">
+        <v>49.30000000000001</v>
+      </c>
+      <c r="L48">
+        <v>230.075</v>
+      </c>
+      <c r="M48">
+        <v>56.65714199999999</v>
+      </c>
+      <c r="N48">
+        <v>173.417858</v>
+      </c>
+      <c r="O48">
+        <v>38.15192876</v>
+      </c>
+      <c r="P48">
+        <v>135.26592924</v>
+      </c>
+      <c r="Q48">
+        <v>184.56592924</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.1003745642348319</v>
+      </c>
+      <c r="T48">
+        <v>1.33857748336591</v>
+      </c>
+      <c r="U48">
+        <v>0.0535</v>
+      </c>
+      <c r="V48">
+        <v>0.22</v>
+      </c>
+      <c r="W48">
+        <v>0.04173</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>4.060829612619711</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.07433579774609829</v>
+      </c>
+      <c r="C49">
+        <v>1171.051998745928</v>
+      </c>
+      <c r="D49">
+        <v>1372.485998745928</v>
+      </c>
+      <c r="E49">
+        <v>-203.4660000000001</v>
+      </c>
+      <c r="F49">
+        <v>1082.034</v>
+      </c>
+      <c r="G49">
+        <v>880.6</v>
+      </c>
+      <c r="H49">
+        <v>1016.7</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>279.375</v>
+      </c>
+      <c r="K49">
+        <v>49.30000000000001</v>
+      </c>
+      <c r="L49">
+        <v>230.075</v>
+      </c>
+      <c r="M49">
+        <v>60.8103108</v>
+      </c>
+      <c r="N49">
+        <v>169.2646892</v>
+      </c>
+      <c r="O49">
+        <v>37.238231624</v>
+      </c>
+      <c r="P49">
+        <v>132.026457576</v>
+      </c>
+      <c r="Q49">
+        <v>181.326457576</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.1013827882001855</v>
+      </c>
+      <c r="T49">
+        <v>1.360495395656205</v>
+      </c>
+      <c r="U49">
+        <v>0.0562</v>
+      </c>
+      <c r="V49">
+        <v>0.22</v>
+      </c>
+      <c r="W49">
+        <v>0.043836</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>3.783486664896309</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.07430477080538736</v>
+      </c>
+      <c r="C50">
+        <v>1148.595614263372</v>
+      </c>
+      <c r="D50">
+        <v>1373.051614263371</v>
+      </c>
+      <c r="E50">
+        <v>-180.4440000000002</v>
+      </c>
+      <c r="F50">
+        <v>1105.056</v>
+      </c>
+      <c r="G50">
+        <v>880.6</v>
+      </c>
+      <c r="H50">
+        <v>1016.7</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>279.375</v>
+      </c>
+      <c r="K50">
+        <v>49.30000000000001</v>
+      </c>
+      <c r="L50">
+        <v>230.075</v>
+      </c>
+      <c r="M50">
+        <v>62.10414719999999</v>
+      </c>
+      <c r="N50">
+        <v>167.9708528</v>
+      </c>
+      <c r="O50">
+        <v>36.953587616</v>
+      </c>
+      <c r="P50">
+        <v>131.017265184</v>
+      </c>
+      <c r="Q50">
+        <v>180.317265184</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.1024297900103603</v>
+      </c>
+      <c r="T50">
+        <v>1.38325630457305</v>
+      </c>
+      <c r="U50">
+        <v>0.0562</v>
+      </c>
+      <c r="V50">
+        <v>0.22</v>
+      </c>
+      <c r="W50">
+        <v>0.043836</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>3.704664026044303</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.07427374386467643</v>
+      </c>
+      <c r="C51">
+        <v>1126.139696164896</v>
+      </c>
+      <c r="D51">
+        <v>1373.617696164896</v>
+      </c>
+      <c r="E51">
+        <v>-157.422</v>
+      </c>
+      <c r="F51">
+        <v>1128.078</v>
+      </c>
+      <c r="G51">
+        <v>880.6</v>
+      </c>
+      <c r="H51">
+        <v>1016.7</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>279.375</v>
+      </c>
+      <c r="K51">
+        <v>49.30000000000001</v>
+      </c>
+      <c r="L51">
+        <v>230.075</v>
+      </c>
+      <c r="M51">
+        <v>63.3979836</v>
+      </c>
+      <c r="N51">
+        <v>166.6770164</v>
+      </c>
+      <c r="O51">
+        <v>36.668943608</v>
+      </c>
+      <c r="P51">
+        <v>130.008072792</v>
+      </c>
+      <c r="Q51">
+        <v>179.308072792</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.1035178507150518</v>
+      </c>
+      <c r="T51">
+        <v>1.406909798153301</v>
+      </c>
+      <c r="U51">
+        <v>0.0562</v>
+      </c>
+      <c r="V51">
+        <v>0.22</v>
+      </c>
+      <c r="W51">
+        <v>0.043836</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>3.629058637757684</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.0742427169239655</v>
+      </c>
+      <c r="C52">
+        <v>1103.684245027583</v>
+      </c>
+      <c r="D52">
+        <v>1374.184245027582</v>
+      </c>
+      <c r="E52">
+        <v>-134.4000000000001</v>
+      </c>
+      <c r="F52">
+        <v>1151.1</v>
+      </c>
+      <c r="G52">
+        <v>880.6</v>
+      </c>
+      <c r="H52">
+        <v>1016.7</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>279.375</v>
+      </c>
+      <c r="K52">
+        <v>49.30000000000001</v>
+      </c>
+      <c r="L52">
+        <v>230.075</v>
+      </c>
+      <c r="M52">
+        <v>64.69181999999999</v>
+      </c>
+      <c r="N52">
+        <v>165.38318</v>
+      </c>
+      <c r="O52">
+        <v>36.3842996</v>
+      </c>
+      <c r="P52">
+        <v>128.9988804</v>
+      </c>
+      <c r="Q52">
+        <v>178.2988804</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.104649433847931</v>
+      </c>
+      <c r="T52">
+        <v>1.431509431476761</v>
+      </c>
+      <c r="U52">
+        <v>0.0562</v>
+      </c>
+      <c r="V52">
+        <v>0.22</v>
+      </c>
+      <c r="W52">
+        <v>0.043836</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>3.55647746500253</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.07608134998325458</v>
+      </c>
+      <c r="C53">
+        <v>1047.876473249466</v>
+      </c>
+      <c r="D53">
+        <v>1341.398473249465</v>
+      </c>
+      <c r="E53">
+        <v>-111.3780000000002</v>
+      </c>
+      <c r="F53">
+        <v>1174.122</v>
+      </c>
+      <c r="G53">
+        <v>880.6</v>
+      </c>
+      <c r="H53">
+        <v>1016.7</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>279.375</v>
+      </c>
+      <c r="K53">
+        <v>49.30000000000001</v>
+      </c>
+      <c r="L53">
+        <v>230.075</v>
+      </c>
+      <c r="M53">
+        <v>71.5040298</v>
+      </c>
+      <c r="N53">
+        <v>158.5709702</v>
+      </c>
+      <c r="O53">
+        <v>34.88561344399999</v>
+      </c>
+      <c r="P53">
+        <v>123.685356756</v>
+      </c>
+      <c r="Q53">
+        <v>172.985356756</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.1058272040474583</v>
+      </c>
+      <c r="T53">
+        <v>1.457113131466485</v>
+      </c>
+      <c r="U53">
+        <v>0.0609</v>
+      </c>
+      <c r="V53">
+        <v>0.22</v>
+      </c>
+      <c r="W53">
+        <v>0.047502</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>3.21765081833192</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.07608698304254366</v>
+      </c>
+      <c r="C54">
+        <v>1024.756430435414</v>
+      </c>
+      <c r="D54">
+        <v>1341.300430435414</v>
+      </c>
+      <c r="E54">
+        <v>-88.35599999999999</v>
+      </c>
+      <c r="F54">
+        <v>1197.144</v>
+      </c>
+      <c r="G54">
+        <v>880.6</v>
+      </c>
+      <c r="H54">
+        <v>1016.7</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>279.375</v>
+      </c>
+      <c r="K54">
+        <v>49.30000000000001</v>
+      </c>
+      <c r="L54">
+        <v>230.075</v>
+      </c>
+      <c r="M54">
+        <v>72.90606960000001</v>
+      </c>
+      <c r="N54">
+        <v>157.1689304</v>
+      </c>
+      <c r="O54">
+        <v>34.57716468799999</v>
+      </c>
+      <c r="P54">
+        <v>122.591765712</v>
+      </c>
+      <c r="Q54">
+        <v>171.891765712</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.1070540480052993</v>
+      </c>
+      <c r="T54">
+        <v>1.483783652289115</v>
+      </c>
+      <c r="U54">
+        <v>0.0609</v>
+      </c>
+      <c r="V54">
+        <v>0.22</v>
+      </c>
+      <c r="W54">
+        <v>0.047502</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>3.155772917979383</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.07609261610183272</v>
+      </c>
+      <c r="C55">
+        <v>1001.636401952215</v>
+      </c>
+      <c r="D55">
+        <v>1341.202401952214</v>
+      </c>
+      <c r="E55">
+        <v>-65.33400000000006</v>
+      </c>
+      <c r="F55">
+        <v>1220.166</v>
+      </c>
+      <c r="G55">
+        <v>880.6</v>
+      </c>
+      <c r="H55">
+        <v>1016.7</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>279.375</v>
+      </c>
+      <c r="K55">
+        <v>49.30000000000001</v>
+      </c>
+      <c r="L55">
+        <v>230.075</v>
+      </c>
+      <c r="M55">
+        <v>74.30810940000001</v>
+      </c>
+      <c r="N55">
+        <v>155.7668906</v>
+      </c>
+      <c r="O55">
+        <v>34.268715932</v>
+      </c>
+      <c r="P55">
+        <v>121.498174668</v>
+      </c>
+      <c r="Q55">
+        <v>170.798174668</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.1083330980890058</v>
+      </c>
+      <c r="T55">
+        <v>1.511589088891431</v>
+      </c>
+      <c r="U55">
+        <v>0.0609</v>
+      </c>
+      <c r="V55">
+        <v>0.22</v>
+      </c>
+      <c r="W55">
+        <v>0.047502</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>3.096230032734489</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.0760982491611218</v>
+      </c>
+      <c r="C56">
+        <v>978.5163877967236</v>
+      </c>
+      <c r="D56">
+        <v>1341.104387796724</v>
+      </c>
+      <c r="E56">
+        <v>-42.31200000000013</v>
+      </c>
+      <c r="F56">
+        <v>1243.188</v>
+      </c>
+      <c r="G56">
+        <v>880.6</v>
+      </c>
+      <c r="H56">
+        <v>1016.7</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>279.375</v>
+      </c>
+      <c r="K56">
+        <v>49.30000000000001</v>
+      </c>
+      <c r="L56">
+        <v>230.075</v>
+      </c>
+      <c r="M56">
+        <v>75.71014919999999</v>
+      </c>
+      <c r="N56">
+        <v>154.3648508</v>
+      </c>
+      <c r="O56">
+        <v>33.960267176</v>
+      </c>
+      <c r="P56">
+        <v>120.404583624</v>
+      </c>
+      <c r="Q56">
+        <v>169.704583624</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.109667759045917</v>
+      </c>
+      <c r="T56">
+        <v>1.540603457519934</v>
+      </c>
+      <c r="U56">
+        <v>0.0609</v>
+      </c>
+      <c r="V56">
+        <v>0.22</v>
+      </c>
+      <c r="W56">
+        <v>0.047502</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>3.038892439535703</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.08009358222041088</v>
+      </c>
+      <c r="C57">
+        <v>889.4069225159219</v>
+      </c>
+      <c r="D57">
+        <v>1275.016922515922</v>
+      </c>
+      <c r="E57">
+        <v>-19.28999999999996</v>
+      </c>
+      <c r="F57">
+        <v>1266.21</v>
+      </c>
+      <c r="G57">
+        <v>880.6</v>
+      </c>
+      <c r="H57">
+        <v>1016.7</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>279.375</v>
+      </c>
+      <c r="K57">
+        <v>49.30000000000001</v>
+      </c>
+      <c r="L57">
+        <v>230.075</v>
+      </c>
+      <c r="M57">
+        <v>88.887942</v>
+      </c>
+      <c r="N57">
+        <v>141.187058</v>
+      </c>
+      <c r="O57">
+        <v>31.06115276</v>
+      </c>
+      <c r="P57">
+        <v>110.12590524</v>
+      </c>
+      <c r="Q57">
+        <v>159.42590524</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.1110617382675797</v>
+      </c>
+      <c r="T57">
+        <v>1.570907353643038</v>
+      </c>
+      <c r="U57">
+        <v>0.0702</v>
+      </c>
+      <c r="V57">
+        <v>0.22</v>
+      </c>
+      <c r="W57">
+        <v>0.054756</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>B1/B+</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>2.588371322625514</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.08017175527969995</v>
+      </c>
+      <c r="C58">
+        <v>865.1567537696815</v>
+      </c>
+      <c r="D58">
+        <v>1273.788753769682</v>
+      </c>
+      <c r="E58">
+        <v>3.731999999999971</v>
+      </c>
+      <c r="F58">
+        <v>1289.232</v>
+      </c>
+      <c r="G58">
+        <v>880.6</v>
+      </c>
+      <c r="H58">
+        <v>1016.7</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>279.375</v>
+      </c>
+      <c r="K58">
+        <v>49.30000000000001</v>
+      </c>
+      <c r="L58">
+        <v>230.075</v>
+      </c>
+      <c r="M58">
+        <v>90.50408639999999</v>
+      </c>
+      <c r="N58">
+        <v>139.5709136</v>
+      </c>
+      <c r="O58">
+        <v>30.705600992</v>
+      </c>
+      <c r="P58">
+        <v>108.865312608</v>
+      </c>
+      <c r="Q58">
+        <v>158.165312608</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.1125190801811363</v>
+      </c>
+      <c r="T58">
+        <v>1.602588699589919</v>
+      </c>
+      <c r="U58">
+        <v>0.0702</v>
+      </c>
+      <c r="V58">
+        <v>0.22</v>
+      </c>
+      <c r="W58">
+        <v>0.054756</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>B1/B+</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>2.542150406150059</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.08233954833898902</v>
+      </c>
+      <c r="C59">
+        <v>808.9948172970132</v>
+      </c>
+      <c r="D59">
+        <v>1240.648817297013</v>
+      </c>
+      <c r="E59">
+        <v>26.75400000000013</v>
+      </c>
+      <c r="F59">
+        <v>1312.254</v>
+      </c>
+      <c r="G59">
+        <v>880.6</v>
+      </c>
+      <c r="H59">
+        <v>1016.7</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>279.375</v>
+      </c>
+      <c r="K59">
+        <v>49.30000000000001</v>
+      </c>
+      <c r="L59">
+        <v>230.075</v>
+      </c>
+      <c r="M59">
+        <v>98.28782460000001</v>
+      </c>
+      <c r="N59">
+        <v>131.7871754</v>
+      </c>
+      <c r="O59">
+        <v>28.99317858799999</v>
+      </c>
+      <c r="P59">
+        <v>102.793996812</v>
+      </c>
+      <c r="Q59">
+        <v>152.093996812</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.1140442054395094</v>
+      </c>
+      <c r="T59">
+        <v>1.635743596511073</v>
+      </c>
+      <c r="U59">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V59">
+        <v>0.22</v>
+      </c>
+      <c r="W59">
+        <v>0.05842199999999999</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>2.34082910000635</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.0824543813982781</v>
+      </c>
+      <c r="C60">
+        <v>784.2653432137067</v>
+      </c>
+      <c r="D60">
+        <v>1238.941343213706</v>
+      </c>
+      <c r="E60">
+        <v>49.77599999999984</v>
+      </c>
+      <c r="F60">
+        <v>1335.276</v>
+      </c>
+      <c r="G60">
+        <v>880.6</v>
+      </c>
+      <c r="H60">
+        <v>1016.7</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>279.375</v>
+      </c>
+      <c r="K60">
+        <v>49.30000000000001</v>
+      </c>
+      <c r="L60">
+        <v>230.075</v>
+      </c>
+      <c r="M60">
+        <v>100.0121724</v>
+      </c>
+      <c r="N60">
+        <v>130.0628276</v>
+      </c>
+      <c r="O60">
+        <v>28.613822072</v>
+      </c>
+      <c r="P60">
+        <v>101.449005528</v>
+      </c>
+      <c r="Q60">
+        <v>150.749005528</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.1156419557101859</v>
+      </c>
+      <c r="T60">
+        <v>1.67047729804752</v>
+      </c>
+      <c r="U60">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V60">
+        <v>0.22</v>
+      </c>
+      <c r="W60">
+        <v>0.05842199999999999</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>2.300469977592448</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.08256921445756717</v>
+      </c>
+      <c r="C61">
+        <v>759.5405625790759</v>
+      </c>
+      <c r="D61">
+        <v>1237.238562579076</v>
+      </c>
+      <c r="E61">
+        <v>72.79799999999977</v>
+      </c>
+      <c r="F61">
+        <v>1358.298</v>
+      </c>
+      <c r="G61">
+        <v>880.6</v>
+      </c>
+      <c r="H61">
+        <v>1016.7</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>279.375</v>
+      </c>
+      <c r="K61">
+        <v>49.30000000000001</v>
+      </c>
+      <c r="L61">
+        <v>230.075</v>
+      </c>
+      <c r="M61">
+        <v>101.7365202</v>
+      </c>
+      <c r="N61">
+        <v>128.3384798</v>
+      </c>
+      <c r="O61">
+        <v>28.234465556</v>
+      </c>
+      <c r="P61">
+        <v>100.104014244</v>
+      </c>
+      <c r="Q61">
+        <v>149.404014244</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.1173176450184565</v>
+      </c>
+      <c r="T61">
+        <v>1.706905326488185</v>
+      </c>
+      <c r="U61">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V61">
+        <v>0.22</v>
+      </c>
+      <c r="W61">
+        <v>0.05842199999999999</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>2.261478961023085</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.08268404751685623</v>
+      </c>
+      <c r="C62">
+        <v>734.8204560678839</v>
+      </c>
+      <c r="D62">
+        <v>1235.540456067884</v>
+      </c>
+      <c r="E62">
+        <v>95.81999999999994</v>
+      </c>
+      <c r="F62">
+        <v>1381.32</v>
+      </c>
+      <c r="G62">
+        <v>880.6</v>
+      </c>
+      <c r="H62">
+        <v>1016.7</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>279.375</v>
+      </c>
+      <c r="K62">
+        <v>49.30000000000001</v>
+      </c>
+      <c r="L62">
+        <v>230.075</v>
+      </c>
+      <c r="M62">
+        <v>103.460868</v>
+      </c>
+      <c r="N62">
+        <v>126.614132</v>
+      </c>
+      <c r="O62">
+        <v>27.85510904</v>
+      </c>
+      <c r="P62">
+        <v>98.75902296</v>
+      </c>
+      <c r="Q62">
+        <v>148.05902296</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.1190771187921406</v>
+      </c>
+      <c r="T62">
+        <v>1.745154756350883</v>
+      </c>
+      <c r="U62">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V62">
+        <v>0.22</v>
+      </c>
+      <c r="W62">
+        <v>0.05842199999999999</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>2.223787645006033</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.08279888057614532</v>
+      </c>
+      <c r="C63">
+        <v>710.1050044608457</v>
+      </c>
+      <c r="D63">
+        <v>1233.847004460846</v>
+      </c>
+      <c r="E63">
+        <v>118.8419999999999</v>
+      </c>
+      <c r="F63">
+        <v>1404.342</v>
+      </c>
+      <c r="G63">
+        <v>880.6</v>
+      </c>
+      <c r="H63">
+        <v>1016.7</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>279.375</v>
+      </c>
+      <c r="K63">
+        <v>49.30000000000001</v>
+      </c>
+      <c r="L63">
+        <v>230.075</v>
+      </c>
+      <c r="M63">
+        <v>105.1852158</v>
+      </c>
+      <c r="N63">
+        <v>124.8897842</v>
+      </c>
+      <c r="O63">
+        <v>27.475752524</v>
+      </c>
+      <c r="P63">
+        <v>97.41403167600001</v>
+      </c>
+      <c r="Q63">
+        <v>146.714031676</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.1209268219901162</v>
+      </c>
+      <c r="T63">
+        <v>1.785365695437308</v>
+      </c>
+      <c r="U63">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V63">
+        <v>0.22</v>
+      </c>
+      <c r="W63">
+        <v>0.05842199999999999</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>2.187332109842</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.0829137136354344</v>
+      </c>
+      <c r="C64">
+        <v>685.3941886438995</v>
+      </c>
+      <c r="D64">
+        <v>1232.158188643899</v>
+      </c>
+      <c r="E64">
+        <v>141.8639999999998</v>
+      </c>
+      <c r="F64">
+        <v>1427.364</v>
+      </c>
+      <c r="G64">
+        <v>880.6</v>
+      </c>
+      <c r="H64">
+        <v>1016.7</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>279.375</v>
+      </c>
+      <c r="K64">
+        <v>49.30000000000001</v>
+      </c>
+      <c r="L64">
+        <v>230.075</v>
+      </c>
+      <c r="M64">
+        <v>106.9095636</v>
+      </c>
+      <c r="N64">
+        <v>123.1654364</v>
+      </c>
+      <c r="O64">
+        <v>27.096396008</v>
+      </c>
+      <c r="P64">
+        <v>96.06904039200001</v>
+      </c>
+      <c r="Q64">
+        <v>145.369040392</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.1228738779879852</v>
+      </c>
+      <c r="T64">
+        <v>1.82769299973881</v>
+      </c>
+      <c r="U64">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V64">
+        <v>0.22</v>
+      </c>
+      <c r="W64">
+        <v>0.05842199999999999</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>2.152052559683257</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.08302854669472347</v>
+      </c>
+      <c r="C65">
+        <v>660.6879896074902</v>
+      </c>
+      <c r="D65">
+        <v>1230.47398960749</v>
+      </c>
+      <c r="E65">
+        <v>164.886</v>
+      </c>
+      <c r="F65">
+        <v>1450.386</v>
+      </c>
+      <c r="G65">
+        <v>880.6</v>
+      </c>
+      <c r="H65">
+        <v>1016.7</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>279.375</v>
+      </c>
+      <c r="K65">
+        <v>49.30000000000001</v>
+      </c>
+      <c r="L65">
+        <v>230.075</v>
+      </c>
+      <c r="M65">
+        <v>108.6339114</v>
+      </c>
+      <c r="N65">
+        <v>121.4410886</v>
+      </c>
+      <c r="O65">
+        <v>26.717039492</v>
+      </c>
+      <c r="P65">
+        <v>94.724049108</v>
+      </c>
+      <c r="Q65">
+        <v>144.024049108</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.1249261802560094</v>
+      </c>
+      <c r="T65">
+        <v>1.872308266434986</v>
+      </c>
+      <c r="U65">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V65">
+        <v>0.22</v>
+      </c>
+      <c r="W65">
+        <v>0.05842199999999999</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>2.117892995243841</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.08314337975401254</v>
+      </c>
+      <c r="C66">
+        <v>635.9863884458537</v>
+      </c>
+      <c r="D66">
+        <v>1228.794388445854</v>
+      </c>
+      <c r="E66">
+        <v>187.9079999999999</v>
+      </c>
+      <c r="F66">
+        <v>1473.408</v>
+      </c>
+      <c r="G66">
+        <v>880.6</v>
+      </c>
+      <c r="H66">
+        <v>1016.7</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>279.375</v>
+      </c>
+      <c r="K66">
+        <v>49.30000000000001</v>
+      </c>
+      <c r="L66">
+        <v>230.075</v>
+      </c>
+      <c r="M66">
+        <v>110.3582592</v>
+      </c>
+      <c r="N66">
+        <v>119.7167408</v>
+      </c>
+      <c r="O66">
+        <v>26.337682976</v>
+      </c>
+      <c r="P66">
+        <v>93.379057824</v>
+      </c>
+      <c r="Q66">
+        <v>142.679057824</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.1270924993167015</v>
+      </c>
+      <c r="T66">
+        <v>1.919402159058728</v>
+      </c>
+      <c r="U66">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V66">
+        <v>0.22</v>
+      </c>
+      <c r="W66">
+        <v>0.05842199999999999</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>2.084800917193156</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.0832582128133016</v>
+      </c>
+      <c r="C67">
+        <v>611.2893663563123</v>
+      </c>
+      <c r="D67">
+        <v>1227.119366356312</v>
+      </c>
+      <c r="E67">
+        <v>210.9299999999998</v>
+      </c>
+      <c r="F67">
+        <v>1496.43</v>
+      </c>
+      <c r="G67">
+        <v>880.6</v>
+      </c>
+      <c r="H67">
+        <v>1016.7</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>279.375</v>
+      </c>
+      <c r="K67">
+        <v>49.30000000000001</v>
+      </c>
+      <c r="L67">
+        <v>230.075</v>
+      </c>
+      <c r="M67">
+        <v>112.082607</v>
+      </c>
+      <c r="N67">
+        <v>117.992393</v>
+      </c>
+      <c r="O67">
+        <v>25.95832646</v>
+      </c>
+      <c r="P67">
+        <v>92.03406654</v>
+      </c>
+      <c r="Q67">
+        <v>141.33406654</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.1293826080380046</v>
+      </c>
+      <c r="T67">
+        <v>1.96918713126097</v>
+      </c>
+      <c r="U67">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V67">
+        <v>0.22</v>
+      </c>
+      <c r="W67">
+        <v>0.05842199999999999</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>2.052727056928646</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.0833730458725907</v>
+      </c>
+      <c r="C68">
+        <v>586.596904638571</v>
+      </c>
+      <c r="D68">
+        <v>1225.448904638571</v>
+      </c>
+      <c r="E68">
+        <v>233.952</v>
+      </c>
+      <c r="F68">
+        <v>1519.452</v>
+      </c>
+      <c r="G68">
+        <v>880.6</v>
+      </c>
+      <c r="H68">
+        <v>1016.7</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>279.375</v>
+      </c>
+      <c r="K68">
+        <v>49.30000000000001</v>
+      </c>
+      <c r="L68">
+        <v>230.075</v>
+      </c>
+      <c r="M68">
+        <v>113.8069548</v>
+      </c>
+      <c r="N68">
+        <v>116.2680452</v>
+      </c>
+      <c r="O68">
+        <v>25.578969944</v>
+      </c>
+      <c r="P68">
+        <v>90.689075256</v>
+      </c>
+      <c r="Q68">
+        <v>139.989075256</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.1318074290370315</v>
+      </c>
+      <c r="T68">
+        <v>2.021900631239814</v>
+      </c>
+      <c r="U68">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V68">
+        <v>0.22</v>
+      </c>
+      <c r="W68">
+        <v>0.05842199999999999</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>2.021625131823666</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.09200625893187976</v>
+      </c>
+      <c r="C69">
+        <v>449.8032773729294</v>
+      </c>
+      <c r="D69">
+        <v>1111.677277372929</v>
+      </c>
+      <c r="E69">
+        <v>256.9739999999999</v>
+      </c>
+      <c r="F69">
+        <v>1542.474</v>
+      </c>
+      <c r="G69">
+        <v>880.6</v>
+      </c>
+      <c r="H69">
+        <v>1016.7</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>279.375</v>
+      </c>
+      <c r="K69">
+        <v>49.30000000000001</v>
+      </c>
+      <c r="L69">
+        <v>230.075</v>
+      </c>
+      <c r="M69">
+        <v>140.6736288</v>
+      </c>
+      <c r="N69">
+        <v>89.4013712</v>
+      </c>
+      <c r="O69">
+        <v>19.668301664</v>
+      </c>
+      <c r="P69">
+        <v>69.733069536</v>
+      </c>
+      <c r="Q69">
+        <v>119.033069536</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.1343792088844841</v>
+      </c>
+      <c r="T69">
+        <v>2.077808888793133</v>
+      </c>
+      <c r="U69">
+        <v>0.0912</v>
+      </c>
+      <c r="V69">
+        <v>0.22</v>
+      </c>
+      <c r="W69">
+        <v>0.071136</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>1.635523317075332</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.09224823199116886</v>
+      </c>
+      <c r="C70">
+        <v>423.8960276179359</v>
+      </c>
+      <c r="D70">
+        <v>1108.792027617936</v>
+      </c>
+      <c r="E70">
+        <v>279.9960000000001</v>
+      </c>
+      <c r="F70">
+        <v>1565.496</v>
+      </c>
+      <c r="G70">
+        <v>880.6</v>
+      </c>
+      <c r="H70">
+        <v>1016.7</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>279.375</v>
+      </c>
+      <c r="K70">
+        <v>49.30000000000001</v>
+      </c>
+      <c r="L70">
+        <v>230.075</v>
+      </c>
+      <c r="M70">
+        <v>142.7732352</v>
+      </c>
+      <c r="N70">
+        <v>87.30176479999997</v>
+      </c>
+      <c r="O70">
+        <v>19.20638825599999</v>
+      </c>
+      <c r="P70">
+        <v>68.09537654399998</v>
+      </c>
+      <c r="Q70">
+        <v>117.395376544</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.1371117249724026</v>
+      </c>
+      <c r="T70">
+        <v>2.137211412443536</v>
+      </c>
+      <c r="U70">
+        <v>0.0912</v>
+      </c>
+      <c r="V70">
+        <v>0.22</v>
+      </c>
+      <c r="W70">
+        <v>0.071136</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>1.61147150358893</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.09249020505045791</v>
+      </c>
+      <c r="C71">
+        <v>398.0037158604914</v>
+      </c>
+      <c r="D71">
+        <v>1105.921715860492</v>
+      </c>
+      <c r="E71">
+        <v>303.018</v>
+      </c>
+      <c r="F71">
+        <v>1588.518</v>
+      </c>
+      <c r="G71">
+        <v>880.6</v>
+      </c>
+      <c r="H71">
+        <v>1016.7</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>279.375</v>
+      </c>
+      <c r="K71">
+        <v>49.30000000000001</v>
+      </c>
+      <c r="L71">
+        <v>230.075</v>
+      </c>
+      <c r="M71">
+        <v>144.8728416</v>
+      </c>
+      <c r="N71">
+        <v>85.20215839999997</v>
+      </c>
+      <c r="O71">
+        <v>18.744474848</v>
+      </c>
+      <c r="P71">
+        <v>66.45768355199998</v>
+      </c>
+      <c r="Q71">
+        <v>115.757683552</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.140020532420832</v>
+      </c>
+      <c r="T71">
+        <v>2.200446356974608</v>
+      </c>
+      <c r="U71">
+        <v>0.0912</v>
+      </c>
+      <c r="V71">
+        <v>0.22</v>
+      </c>
+      <c r="W71">
+        <v>0.071136</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>1.588116844116627</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.09273217810974699</v>
+      </c>
+      <c r="C72">
+        <v>372.126226390882</v>
+      </c>
+      <c r="D72">
+        <v>1103.066226390882</v>
+      </c>
+      <c r="E72">
+        <v>326.04</v>
+      </c>
+      <c r="F72">
+        <v>1611.54</v>
+      </c>
+      <c r="G72">
+        <v>880.6</v>
+      </c>
+      <c r="H72">
+        <v>1016.7</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>279.375</v>
+      </c>
+      <c r="K72">
+        <v>49.30000000000001</v>
+      </c>
+      <c r="L72">
+        <v>230.075</v>
+      </c>
+      <c r="M72">
+        <v>146.972448</v>
+      </c>
+      <c r="N72">
+        <v>83.10255199999997</v>
+      </c>
+      <c r="O72">
+        <v>18.28256143999999</v>
+      </c>
+      <c r="P72">
+        <v>64.81999055999998</v>
+      </c>
+      <c r="Q72">
+        <v>114.11999056</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.1431232603658233</v>
+      </c>
+      <c r="T72">
+        <v>2.267896964474419</v>
+      </c>
+      <c r="U72">
+        <v>0.0912</v>
+      </c>
+      <c r="V72">
+        <v>0.22</v>
+      </c>
+      <c r="W72">
+        <v>0.071136</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>1.565429460629246</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.09297415116903607</v>
+      </c>
+      <c r="C73">
+        <v>346.2634446913667</v>
+      </c>
+      <c r="D73">
+        <v>1100.225444691367</v>
+      </c>
+      <c r="E73">
+        <v>349.0619999999999</v>
+      </c>
+      <c r="F73">
+        <v>1634.562</v>
+      </c>
+      <c r="G73">
+        <v>880.6</v>
+      </c>
+      <c r="H73">
+        <v>1016.7</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>279.375</v>
+      </c>
+      <c r="K73">
+        <v>49.30000000000001</v>
+      </c>
+      <c r="L73">
+        <v>230.075</v>
+      </c>
+      <c r="M73">
+        <v>149.0720544</v>
+      </c>
+      <c r="N73">
+        <v>81.0029456</v>
+      </c>
+      <c r="O73">
+        <v>17.820648032</v>
+      </c>
+      <c r="P73">
+        <v>63.182297568</v>
+      </c>
+      <c r="Q73">
+        <v>112.482297568</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.1464399695484002</v>
+      </c>
+      <c r="T73">
+        <v>2.3399993380087</v>
+      </c>
+      <c r="U73">
+        <v>0.0912</v>
+      </c>
+      <c r="V73">
+        <v>0.22</v>
+      </c>
+      <c r="W73">
+        <v>0.071136</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>1.543381158366863</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.09321612422832513</v>
+      </c>
+      <c r="C74">
+        <v>320.4152574208688</v>
+      </c>
+      <c r="D74">
+        <v>1097.399257420868</v>
+      </c>
+      <c r="E74">
+        <v>372.0839999999998</v>
+      </c>
+      <c r="F74">
+        <v>1657.584</v>
+      </c>
+      <c r="G74">
+        <v>880.6</v>
+      </c>
+      <c r="H74">
+        <v>1016.7</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>279.375</v>
+      </c>
+      <c r="K74">
+        <v>49.30000000000001</v>
+      </c>
+      <c r="L74">
+        <v>230.075</v>
+      </c>
+      <c r="M74">
+        <v>151.1716608</v>
+      </c>
+      <c r="N74">
+        <v>78.9033392</v>
+      </c>
+      <c r="O74">
+        <v>17.358734624</v>
+      </c>
+      <c r="P74">
+        <v>61.544604576</v>
+      </c>
+      <c r="Q74">
+        <v>110.844604576</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.1499935865297326</v>
+      </c>
+      <c r="T74">
+        <v>2.417251881081144</v>
+      </c>
+      <c r="U74">
+        <v>0.0912</v>
+      </c>
+      <c r="V74">
+        <v>0.22</v>
+      </c>
+      <c r="W74">
+        <v>0.071136</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>1.521945308945101</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.0934580972876142</v>
+      </c>
+      <c r="C75">
+        <v>294.5815523998981</v>
+      </c>
+      <c r="D75">
+        <v>1094.587552399898</v>
+      </c>
+      <c r="E75">
+        <v>395.1059999999998</v>
+      </c>
+      <c r="F75">
+        <v>1680.606</v>
+      </c>
+      <c r="G75">
+        <v>880.6</v>
+      </c>
+      <c r="H75">
+        <v>1016.7</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>279.375</v>
+      </c>
+      <c r="K75">
+        <v>49.30000000000001</v>
+      </c>
+      <c r="L75">
+        <v>230.075</v>
+      </c>
+      <c r="M75">
+        <v>153.2712672</v>
+      </c>
+      <c r="N75">
+        <v>76.80373280000001</v>
+      </c>
+      <c r="O75">
+        <v>16.896821216</v>
+      </c>
+      <c r="P75">
+        <v>59.906911584</v>
+      </c>
+      <c r="Q75">
+        <v>109.206911584</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.1538104343985711</v>
+      </c>
+      <c r="T75">
+        <v>2.500226834751546</v>
+      </c>
+      <c r="U75">
+        <v>0.0912</v>
+      </c>
+      <c r="V75">
+        <v>0.22</v>
+      </c>
+      <c r="W75">
+        <v>0.071136</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>1.501096743069141</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.1357860709359953</v>
+      </c>
+      <c r="C76">
+        <v>-67.19837521418435</v>
+      </c>
+      <c r="D76">
+        <v>755.8296247858156</v>
+      </c>
+      <c r="E76">
+        <v>418.1279999999999</v>
+      </c>
+      <c r="F76">
+        <v>1703.628</v>
+      </c>
+      <c r="G76">
+        <v>880.6</v>
+      </c>
+      <c r="H76">
+        <v>1016.7</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>279.375</v>
+      </c>
+      <c r="K76">
+        <v>49.30000000000001</v>
+      </c>
+      <c r="L76">
+        <v>230.075</v>
+      </c>
+      <c r="M76">
+        <v>266.7881448</v>
+      </c>
+      <c r="N76">
+        <v>-36.71314480000001</v>
+      </c>
+      <c r="O76">
+        <v>-8.076891856000001</v>
+      </c>
+      <c r="P76">
+        <v>-28.63625294400001</v>
+      </c>
+      <c r="Q76">
+        <v>20.66374705600001</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.1611085177870806</v>
+      </c>
+      <c r="T76">
+        <v>2.658880821458274</v>
+      </c>
+      <c r="U76">
+        <v>0.1566</v>
+      </c>
+      <c r="V76">
+        <v>0.1897254469007425</v>
+      </c>
+      <c r="W76">
+        <v>0.1268889950153437</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.8623883950033749</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.1369640709359953</v>
+      </c>
+      <c r="C77">
+        <v>-96.67477858535858</v>
+      </c>
+      <c r="D77">
+        <v>749.3752214146413</v>
+      </c>
+      <c r="E77">
+        <v>441.1499999999999</v>
+      </c>
+      <c r="F77">
+        <v>1726.65</v>
+      </c>
+      <c r="G77">
+        <v>880.6</v>
+      </c>
+      <c r="H77">
+        <v>1016.7</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>279.375</v>
+      </c>
+      <c r="K77">
+        <v>49.30000000000001</v>
+      </c>
+      <c r="L77">
+        <v>230.075</v>
+      </c>
+      <c r="M77">
+        <v>270.39339</v>
+      </c>
+      <c r="N77">
+        <v>-40.31839000000002</v>
+      </c>
+      <c r="O77">
+        <v>-8.870045800000005</v>
+      </c>
+      <c r="P77">
+        <v>-31.44834420000002</v>
+      </c>
+      <c r="Q77">
+        <v>17.8516558</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.1660008584985639</v>
+      </c>
+      <c r="T77">
+        <v>2.765236054316606</v>
+      </c>
+      <c r="U77">
+        <v>0.1566</v>
+      </c>
+      <c r="V77">
+        <v>0.1871957742753992</v>
+      </c>
+      <c r="W77">
+        <v>0.1272851417484725</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.8508898830699966</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.1381420709359953</v>
+      </c>
+      <c r="C78">
+        <v>-126.0418806427467</v>
+      </c>
+      <c r="D78">
+        <v>743.0301193572532</v>
+      </c>
+      <c r="E78">
+        <v>464.1719999999998</v>
+      </c>
+      <c r="F78">
+        <v>1749.672</v>
+      </c>
+      <c r="G78">
+        <v>880.6</v>
+      </c>
+      <c r="H78">
+        <v>1016.7</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>279.375</v>
+      </c>
+      <c r="K78">
+        <v>49.30000000000001</v>
+      </c>
+      <c r="L78">
+        <v>230.075</v>
+      </c>
+      <c r="M78">
+        <v>273.9986352</v>
+      </c>
+      <c r="N78">
+        <v>-43.92363520000004</v>
+      </c>
+      <c r="O78">
+        <v>-9.663199744000007</v>
+      </c>
+      <c r="P78">
+        <v>-34.26043545600002</v>
+      </c>
+      <c r="Q78">
+        <v>15.03956454399999</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.1713008942693374</v>
+      </c>
+      <c r="T78">
+        <v>2.880454223246464</v>
+      </c>
+      <c r="U78">
+        <v>0.1566</v>
+      </c>
+      <c r="V78">
+        <v>0.1847326719823019</v>
+      </c>
+      <c r="W78">
+        <v>0.1276708635675715</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.8396939635559176</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.1393200709359953</v>
+      </c>
+      <c r="C79">
+        <v>-155.3024345000451</v>
+      </c>
+      <c r="D79">
+        <v>736.7915654999548</v>
+      </c>
+      <c r="E79">
+        <v>487.194</v>
+      </c>
+      <c r="F79">
+        <v>1772.694</v>
+      </c>
+      <c r="G79">
+        <v>880.6</v>
+      </c>
+      <c r="H79">
+        <v>1016.7</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>279.375</v>
+      </c>
+      <c r="K79">
+        <v>49.30000000000001</v>
+      </c>
+      <c r="L79">
+        <v>230.075</v>
+      </c>
+      <c r="M79">
+        <v>277.6038804</v>
+      </c>
+      <c r="N79">
+        <v>-47.52888040000005</v>
+      </c>
+      <c r="O79">
+        <v>-10.45635368800001</v>
+      </c>
+      <c r="P79">
+        <v>-37.07252671200004</v>
+      </c>
+      <c r="Q79">
+        <v>12.22747328799997</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.1770618027158303</v>
+      </c>
+      <c r="T79">
+        <v>3.005691363387615</v>
+      </c>
+      <c r="U79">
+        <v>0.1566</v>
+      </c>
+      <c r="V79">
+        <v>0.1823335463721421</v>
+      </c>
+      <c r="W79">
+        <v>0.1280465666381226</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.8287888471461005</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.1404980709359953</v>
+      </c>
+      <c r="C80">
+        <v>-184.4591015791507</v>
+      </c>
+      <c r="D80">
+        <v>730.6568984208492</v>
+      </c>
+      <c r="E80">
+        <v>510.2159999999999</v>
+      </c>
+      <c r="F80">
+        <v>1795.716</v>
+      </c>
+      <c r="G80">
+        <v>880.6</v>
+      </c>
+      <c r="H80">
+        <v>1016.7</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>279.375</v>
+      </c>
+      <c r="K80">
+        <v>49.30000000000001</v>
+      </c>
+      <c r="L80">
+        <v>230.075</v>
+      </c>
+      <c r="M80">
+        <v>281.2091256</v>
+      </c>
+      <c r="N80">
+        <v>-51.1341256</v>
+      </c>
+      <c r="O80">
+        <v>-11.249507632</v>
+      </c>
+      <c r="P80">
+        <v>-39.884617968</v>
+      </c>
+      <c r="Q80">
+        <v>9.415382032000011</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.1833464301120044</v>
+      </c>
+      <c r="T80">
+        <v>3.142313698087052</v>
+      </c>
+      <c r="U80">
+        <v>0.1566</v>
+      </c>
+      <c r="V80">
+        <v>0.1799959368032685</v>
+      </c>
+      <c r="W80">
+        <v>0.1284126362966082</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.818163349105766</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.1416760709359953</v>
+      </c>
+      <c r="C81">
+        <v>-213.5144553958594</v>
+      </c>
+      <c r="D81">
+        <v>724.6235446041404</v>
+      </c>
+      <c r="E81">
+        <v>533.2379999999998</v>
+      </c>
+      <c r="F81">
+        <v>1818.738</v>
+      </c>
+      <c r="G81">
+        <v>880.6</v>
+      </c>
+      <c r="H81">
+        <v>1016.7</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>279.375</v>
+      </c>
+      <c r="K81">
+        <v>49.30000000000001</v>
+      </c>
+      <c r="L81">
+        <v>230.075</v>
+      </c>
+      <c r="M81">
+        <v>284.8143708</v>
+      </c>
+      <c r="N81">
+        <v>-54.73937080000002</v>
+      </c>
+      <c r="O81">
+        <v>-12.042661576</v>
+      </c>
+      <c r="P81">
+        <v>-42.69670922400002</v>
+      </c>
+      <c r="Q81">
+        <v>6.603290775999994</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.1902295934506713</v>
+      </c>
+      <c r="T81">
+        <v>3.291947683710245</v>
+      </c>
+      <c r="U81">
+        <v>0.1566</v>
+      </c>
+      <c r="V81">
+        <v>0.1777175072234803</v>
+      </c>
+      <c r="W81">
+        <v>0.128769438368803</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.8078068510158195</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.185912533269713</v>
+      </c>
+      <c r="C82">
+        <v>-408.0480380406038</v>
+      </c>
+      <c r="D82">
+        <v>553.1119619593961</v>
+      </c>
+      <c r="E82">
+        <v>556.26</v>
+      </c>
+      <c r="F82">
+        <v>1841.76</v>
+      </c>
+      <c r="G82">
+        <v>880.6</v>
+      </c>
+      <c r="H82">
+        <v>1016.7</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>279.375</v>
+      </c>
+      <c r="K82">
+        <v>49.30000000000001</v>
+      </c>
+      <c r="L82">
+        <v>230.075</v>
+      </c>
+      <c r="M82">
+        <v>384.559488</v>
+      </c>
+      <c r="N82">
+        <v>-154.4844880000001</v>
+      </c>
+      <c r="O82">
+        <v>-33.98658736000002</v>
+      </c>
+      <c r="P82">
+        <v>-120.49790064</v>
+      </c>
+      <c r="Q82">
+        <v>-71.19790064000003</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.2042933847917934</v>
+      </c>
+      <c r="T82">
+        <v>3.597682278082465</v>
+      </c>
+      <c r="U82">
+        <v>0.2088</v>
+      </c>
+      <c r="V82">
+        <v>0.1316220287873901</v>
+      </c>
+      <c r="W82">
+        <v>0.181317320389193</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.5982819490335913</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.1876125332697131</v>
+      </c>
+      <c r="C83">
+        <v>-436.0557837104154</v>
+      </c>
+      <c r="D83">
+        <v>548.1262162895844</v>
+      </c>
+      <c r="E83">
+        <v>579.2819999999999</v>
+      </c>
+      <c r="F83">
+        <v>1864.782</v>
+      </c>
+      <c r="G83">
+        <v>880.6</v>
+      </c>
+      <c r="H83">
+        <v>1016.7</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>279.375</v>
+      </c>
+      <c r="K83">
+        <v>49.30000000000001</v>
+      </c>
+      <c r="L83">
+        <v>230.075</v>
+      </c>
+      <c r="M83">
+        <v>389.3664816</v>
+      </c>
+      <c r="N83">
+        <v>-159.2914816</v>
+      </c>
+      <c r="O83">
+        <v>-35.044125952</v>
+      </c>
+      <c r="P83">
+        <v>-124.247355648</v>
+      </c>
+      <c r="Q83">
+        <v>-74.94735564799998</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.2130035629387299</v>
+      </c>
+      <c r="T83">
+        <v>3.787033976928911</v>
+      </c>
+      <c r="U83">
+        <v>0.2088</v>
+      </c>
+      <c r="V83">
+        <v>0.1299970654690273</v>
+      </c>
+      <c r="W83">
+        <v>0.1816566127300671</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.5908957521319421</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.189312533269713</v>
+      </c>
+      <c r="C84">
+        <v>-463.9744494232796</v>
+      </c>
+      <c r="D84">
+        <v>543.2295505767204</v>
+      </c>
+      <c r="E84">
+        <v>602.3040000000001</v>
+      </c>
+      <c r="F84">
+        <v>1887.804</v>
+      </c>
+      <c r="G84">
+        <v>880.6</v>
+      </c>
+      <c r="H84">
+        <v>1016.7</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>279.375</v>
+      </c>
+      <c r="K84">
+        <v>49.30000000000001</v>
+      </c>
+      <c r="L84">
+        <v>230.075</v>
+      </c>
+      <c r="M84">
+        <v>394.1734752</v>
+      </c>
+      <c r="N84">
+        <v>-164.0984752000001</v>
+      </c>
+      <c r="O84">
+        <v>-36.10166454400001</v>
+      </c>
+      <c r="P84">
+        <v>-127.996810656</v>
+      </c>
+      <c r="Q84">
+        <v>-78.69681065600003</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.2226815386575483</v>
+      </c>
+      <c r="T84">
+        <v>3.997424753424962</v>
+      </c>
+      <c r="U84">
+        <v>0.2088</v>
+      </c>
+      <c r="V84">
+        <v>0.1284117354023318</v>
+      </c>
+      <c r="W84">
+        <v>0.1819876296479931</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.5836897063742355</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.1910125332697131</v>
+      </c>
+      <c r="C85">
+        <v>-491.8064014181989</v>
+      </c>
+      <c r="D85">
+        <v>538.4195985818011</v>
+      </c>
+      <c r="E85">
+        <v>625.326</v>
+      </c>
+      <c r="F85">
+        <v>1910.826</v>
+      </c>
+      <c r="G85">
+        <v>880.6</v>
+      </c>
+      <c r="H85">
+        <v>1016.7</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>279.375</v>
+      </c>
+      <c r="K85">
+        <v>49.30000000000001</v>
+      </c>
+      <c r="L85">
+        <v>230.075</v>
+      </c>
+      <c r="M85">
+        <v>398.9804688</v>
+      </c>
+      <c r="N85">
+        <v>-168.9054688000001</v>
+      </c>
+      <c r="O85">
+        <v>-37.15920313600001</v>
+      </c>
+      <c r="P85">
+        <v>-131.746265664</v>
+      </c>
+      <c r="Q85">
+        <v>-82.44626566400004</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.2334980997550511</v>
+      </c>
+      <c r="T85">
+        <v>4.232567385979372</v>
+      </c>
+      <c r="U85">
+        <v>0.2088</v>
+      </c>
+      <c r="V85">
+        <v>0.126864606060135</v>
+      </c>
+      <c r="W85">
+        <v>0.1823106702546438</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.5766573002733411</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.192712533269713</v>
+      </c>
+      <c r="C86">
+        <v>-519.5539228635503</v>
+      </c>
+      <c r="D86">
+        <v>533.6940771364494</v>
+      </c>
+      <c r="E86">
+        <v>648.3479999999997</v>
+      </c>
+      <c r="F86">
+        <v>1933.848</v>
+      </c>
+      <c r="G86">
+        <v>880.6</v>
+      </c>
+      <c r="H86">
+        <v>1016.7</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>279.375</v>
+      </c>
+      <c r="K86">
+        <v>49.30000000000001</v>
+      </c>
+      <c r="L86">
+        <v>230.075</v>
+      </c>
+      <c r="M86">
+        <v>403.7874624</v>
+      </c>
+      <c r="N86">
+        <v>-173.7124624</v>
+      </c>
+      <c r="O86">
+        <v>-38.216741728</v>
+      </c>
+      <c r="P86">
+        <v>-135.495720672</v>
+      </c>
+      <c r="Q86">
+        <v>-86.19572067199999</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.2456667309897417</v>
+      </c>
+      <c r="T86">
+        <v>4.49710284760308</v>
+      </c>
+      <c r="U86">
+        <v>0.2088</v>
+      </c>
+      <c r="V86">
+        <v>0.1253543131308477</v>
+      </c>
+      <c r="W86">
+        <v>0.182626019418279</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.5697923324129441</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.194412533269713</v>
+      </c>
+      <c r="C87">
+        <v>-547.2192174707807</v>
+      </c>
+      <c r="D87">
+        <v>529.0507825292193</v>
+      </c>
+      <c r="E87">
+        <v>671.3699999999999</v>
+      </c>
+      <c r="F87">
+        <v>1956.87</v>
+      </c>
+      <c r="G87">
+        <v>880.6</v>
+      </c>
+      <c r="H87">
+        <v>1016.7</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>279.375</v>
+      </c>
+      <c r="K87">
+        <v>49.30000000000001</v>
+      </c>
+      <c r="L87">
+        <v>230.075</v>
+      </c>
+      <c r="M87">
+        <v>408.594456</v>
+      </c>
+      <c r="N87">
+        <v>-178.519456</v>
+      </c>
+      <c r="O87">
+        <v>-39.27428032</v>
+      </c>
+      <c r="P87">
+        <v>-139.24517568</v>
+      </c>
+      <c r="Q87">
+        <v>-89.94517567999998</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.2594578463890578</v>
+      </c>
+      <c r="T87">
+        <v>4.796909704109952</v>
+      </c>
+      <c r="U87">
+        <v>0.2088</v>
+      </c>
+      <c r="V87">
+        <v>0.1238795565057789</v>
+      </c>
+      <c r="W87">
+        <v>0.1829339486015934</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.563088893208086</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.1961125332697131</v>
+      </c>
+      <c r="C88">
+        <v>-574.8044129210834</v>
+      </c>
+      <c r="D88">
+        <v>524.4875870789162</v>
+      </c>
+      <c r="E88">
+        <v>694.3919999999998</v>
+      </c>
+      <c r="F88">
+        <v>1979.892</v>
+      </c>
+      <c r="G88">
+        <v>880.6</v>
+      </c>
+      <c r="H88">
+        <v>1016.7</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>279.375</v>
+      </c>
+      <c r="K88">
+        <v>49.30000000000001</v>
+      </c>
+      <c r="L88">
+        <v>230.075</v>
+      </c>
+      <c r="M88">
+        <v>413.4014496</v>
+      </c>
+      <c r="N88">
+        <v>-183.3264496</v>
+      </c>
+      <c r="O88">
+        <v>-40.331818912</v>
+      </c>
+      <c r="P88">
+        <v>-142.994630688</v>
+      </c>
+      <c r="Q88">
+        <v>-93.69463068799999</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.2752191211311333</v>
+      </c>
+      <c r="T88">
+        <v>5.139546111546378</v>
+      </c>
+      <c r="U88">
+        <v>0.2088</v>
+      </c>
+      <c r="V88">
+        <v>0.1224390965464094</v>
+      </c>
+      <c r="W88">
+        <v>0.1832347166411097</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.5565413479382246</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.197812533269713</v>
+      </c>
+      <c r="C89">
+        <v>-602.3115641162622</v>
+      </c>
+      <c r="D89">
+        <v>520.0024358837377</v>
+      </c>
+      <c r="E89">
+        <v>717.4139999999998</v>
+      </c>
+      <c r="F89">
+        <v>2002.914</v>
+      </c>
+      <c r="G89">
+        <v>880.6</v>
+      </c>
+      <c r="H89">
+        <v>1016.7</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>279.375</v>
+      </c>
+      <c r="K89">
+        <v>49.30000000000001</v>
+      </c>
+      <c r="L89">
+        <v>230.075</v>
+      </c>
+      <c r="M89">
+        <v>418.2084432</v>
+      </c>
+      <c r="N89">
+        <v>-188.1334432</v>
+      </c>
+      <c r="O89">
+        <v>-41.389357504</v>
+      </c>
+      <c r="P89">
+        <v>-146.744085696</v>
+      </c>
+      <c r="Q89">
+        <v>-97.44408569599997</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.2934052073719898</v>
+      </c>
+      <c r="T89">
+        <v>5.53489581243456</v>
+      </c>
+      <c r="U89">
+        <v>0.2088</v>
+      </c>
+      <c r="V89">
+        <v>0.1210317506090944</v>
+      </c>
+      <c r="W89">
+        <v>0.1835285704728211</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.5501443209504289</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.199512533269713</v>
+      </c>
+      <c r="C90">
+        <v>-629.7426562642042</v>
+      </c>
+      <c r="D90">
+        <v>515.5933437357955</v>
+      </c>
+      <c r="E90">
+        <v>740.4359999999999</v>
+      </c>
+      <c r="F90">
+        <v>2025.936</v>
+      </c>
+      <c r="G90">
+        <v>880.6</v>
+      </c>
+      <c r="H90">
+        <v>1016.7</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>279.375</v>
+      </c>
+      <c r="K90">
+        <v>49.30000000000001</v>
+      </c>
+      <c r="L90">
+        <v>230.075</v>
+      </c>
+      <c r="M90">
+        <v>423.0154368</v>
+      </c>
+      <c r="N90">
+        <v>-192.9404368</v>
+      </c>
+      <c r="O90">
+        <v>-42.44689609600001</v>
+      </c>
+      <c r="P90">
+        <v>-150.493540704</v>
+      </c>
+      <c r="Q90">
+        <v>-101.193540704</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.3146223079863223</v>
+      </c>
+      <c r="T90">
+        <v>5.996137130137441</v>
+      </c>
+      <c r="U90">
+        <v>0.2088</v>
+      </c>
+      <c r="V90">
+        <v>0.1196563898067183</v>
+      </c>
+      <c r="W90">
+        <v>0.1838157458083572</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.5438926809396285</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.2012125332697131</v>
+      </c>
+      <c r="C91">
+        <v>-657.0996078087087</v>
+      </c>
+      <c r="D91">
+        <v>511.2583921912914</v>
+      </c>
+      <c r="E91">
+        <v>763.4580000000001</v>
+      </c>
+      <c r="F91">
+        <v>2048.958</v>
+      </c>
+      <c r="G91">
+        <v>880.6</v>
+      </c>
+      <c r="H91">
+        <v>1016.7</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>279.375</v>
+      </c>
+      <c r="K91">
+        <v>49.30000000000001</v>
+      </c>
+      <c r="L91">
+        <v>230.075</v>
+      </c>
+      <c r="M91">
+        <v>427.8224304</v>
+      </c>
+      <c r="N91">
+        <v>-197.7474304</v>
+      </c>
+      <c r="O91">
+        <v>-43.50443468800001</v>
+      </c>
+      <c r="P91">
+        <v>-154.242995712</v>
+      </c>
+      <c r="Q91">
+        <v>-104.942995712</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.3396970632578062</v>
+      </c>
+      <c r="T91">
+        <v>6.541240505604482</v>
+      </c>
+      <c r="U91">
+        <v>0.2088</v>
+      </c>
+      <c r="V91">
+        <v>0.1183119359886652</v>
+      </c>
+      <c r="W91">
+        <v>0.1840964677655667</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.5377815272212056</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.202912533269713</v>
+      </c>
+      <c r="C92">
+        <v>-684.3842732127437</v>
+      </c>
+      <c r="D92">
+        <v>506.9957267872562</v>
+      </c>
+      <c r="E92">
+        <v>786.48</v>
+      </c>
+      <c r="F92">
+        <v>2071.98</v>
+      </c>
+      <c r="G92">
+        <v>880.6</v>
+      </c>
+      <c r="H92">
+        <v>1016.7</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>279.375</v>
+      </c>
+      <c r="K92">
+        <v>49.30000000000001</v>
+      </c>
+      <c r="L92">
+        <v>230.075</v>
+      </c>
+      <c r="M92">
+        <v>432.629424</v>
+      </c>
+      <c r="N92">
+        <v>-202.554424</v>
+      </c>
+      <c r="O92">
+        <v>-44.56197328000001</v>
+      </c>
+      <c r="P92">
+        <v>-157.99245072</v>
+      </c>
+      <c r="Q92">
+        <v>-108.69245072</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.3697867695835867</v>
+      </c>
+      <c r="T92">
+        <v>7.19536455616493</v>
+      </c>
+      <c r="U92">
+        <v>0.2088</v>
+      </c>
+      <c r="V92">
+        <v>0.1169973589221245</v>
+      </c>
+      <c r="W92">
+        <v>0.1843709514570604</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.5318061769187479</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.204612533269713</v>
+      </c>
+      <c r="C93">
+        <v>-711.5984456036263</v>
+      </c>
+      <c r="D93">
+        <v>502.8035543963736</v>
+      </c>
+      <c r="E93">
+        <v>809.502</v>
+      </c>
+      <c r="F93">
+        <v>2095.002</v>
+      </c>
+      <c r="G93">
+        <v>880.6</v>
+      </c>
+      <c r="H93">
+        <v>1016.7</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>279.375</v>
+      </c>
+      <c r="K93">
+        <v>49.30000000000001</v>
+      </c>
+      <c r="L93">
+        <v>230.075</v>
+      </c>
+      <c r="M93">
+        <v>437.4364176</v>
+      </c>
+      <c r="N93">
+        <v>-207.3614176</v>
+      </c>
+      <c r="O93">
+        <v>-45.61951187200001</v>
+      </c>
+      <c r="P93">
+        <v>-161.741905728</v>
+      </c>
+      <c r="Q93">
+        <v>-112.441905728</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.4065630773150964</v>
+      </c>
+      <c r="T93">
+        <v>7.994849506849922</v>
+      </c>
+      <c r="U93">
+        <v>0.2088</v>
+      </c>
+      <c r="V93">
+        <v>0.115711673659244</v>
+      </c>
+      <c r="W93">
+        <v>0.1846394025399498</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.5259621529965638</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.206312533269713</v>
+      </c>
+      <c r="C94">
+        <v>-738.7438592880408</v>
+      </c>
+      <c r="D94">
+        <v>498.6801407119592</v>
+      </c>
+      <c r="E94">
+        <v>832.5239999999999</v>
+      </c>
+      <c r="F94">
+        <v>2118.024</v>
+      </c>
+      <c r="G94">
+        <v>880.6</v>
+      </c>
+      <c r="H94">
+        <v>1016.7</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>279.375</v>
+      </c>
+      <c r="K94">
+        <v>49.30000000000001</v>
+      </c>
+      <c r="L94">
+        <v>230.075</v>
+      </c>
+      <c r="M94">
+        <v>442.2434112</v>
+      </c>
+      <c r="N94">
+        <v>-212.1684112</v>
+      </c>
+      <c r="O94">
+        <v>-46.67705046400001</v>
+      </c>
+      <c r="P94">
+        <v>-165.491360736</v>
+      </c>
+      <c r="Q94">
+        <v>-116.191360736</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.4525334619794836</v>
+      </c>
+      <c r="T94">
+        <v>8.994205695206166</v>
+      </c>
+      <c r="U94">
+        <v>0.2088</v>
+      </c>
+      <c r="V94">
+        <v>0.1144539380759914</v>
+      </c>
+      <c r="W94">
+        <v>0.184902017729733</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.520245173072688</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.208012533269713</v>
+      </c>
+      <c r="C95">
+        <v>-765.8221921443142</v>
+      </c>
+      <c r="D95">
+        <v>494.6238078556856</v>
+      </c>
+      <c r="E95">
+        <v>855.5459999999998</v>
+      </c>
+      <c r="F95">
+        <v>2141.046</v>
+      </c>
+      <c r="G95">
+        <v>880.6</v>
+      </c>
+      <c r="H95">
+        <v>1016.7</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>279.375</v>
+      </c>
+      <c r="K95">
+        <v>49.30000000000001</v>
+      </c>
+      <c r="L95">
+        <v>230.075</v>
+      </c>
+      <c r="M95">
+        <v>447.0504048</v>
+      </c>
+      <c r="N95">
+        <v>-216.9754048</v>
+      </c>
+      <c r="O95">
+        <v>-47.734589056</v>
+      </c>
+      <c r="P95">
+        <v>-169.240815744</v>
+      </c>
+      <c r="Q95">
+        <v>-119.940815744</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>0.5116382422622671</v>
+      </c>
+      <c r="T95">
+        <v>10.27909222309276</v>
+      </c>
+      <c r="U95">
+        <v>0.2088</v>
+      </c>
+      <c r="V95">
+        <v>0.1132232505697979</v>
+      </c>
+      <c r="W95">
+        <v>0.1851589852810262</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.514651138953627</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.2097125332697131</v>
+      </c>
+      <c r="C96">
+        <v>-792.8350678988818</v>
+      </c>
+      <c r="D96">
+        <v>490.632932101118</v>
+      </c>
+      <c r="E96">
+        <v>878.5679999999998</v>
+      </c>
+      <c r="F96">
+        <v>2164.068</v>
+      </c>
+      <c r="G96">
+        <v>880.6</v>
+      </c>
+      <c r="H96">
+        <v>1016.7</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>279.375</v>
+      </c>
+      <c r="K96">
+        <v>49.30000000000001</v>
+      </c>
+      <c r="L96">
+        <v>230.075</v>
+      </c>
+      <c r="M96">
+        <v>451.8573984</v>
+      </c>
+      <c r="N96">
+        <v>-221.7823984</v>
+      </c>
+      <c r="O96">
+        <v>-48.792127648</v>
+      </c>
+      <c r="P96">
+        <v>-172.990270752</v>
+      </c>
+      <c r="Q96">
+        <v>-123.690270752</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>0.5904446159726451</v>
+      </c>
+      <c r="T96">
+        <v>11.99227426027489</v>
+      </c>
+      <c r="U96">
+        <v>0.2088</v>
+      </c>
+      <c r="V96">
+        <v>0.1120187479041618</v>
+      </c>
+      <c r="W96">
+        <v>0.185410485437611</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.5091761268370991</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.211412533269713</v>
+      </c>
+      <c r="C97">
+        <v>-819.7840582934234</v>
+      </c>
+      <c r="D97">
+        <v>486.7059417065767</v>
+      </c>
+      <c r="E97">
+        <v>901.5900000000001</v>
+      </c>
+      <c r="F97">
+        <v>2187.09</v>
+      </c>
+      <c r="G97">
+        <v>880.6</v>
+      </c>
+      <c r="H97">
+        <v>1016.7</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>279.375</v>
+      </c>
+      <c r="K97">
+        <v>49.30000000000001</v>
+      </c>
+      <c r="L97">
+        <v>230.075</v>
+      </c>
+      <c r="M97">
+        <v>456.6643920000001</v>
+      </c>
+      <c r="N97">
+        <v>-226.5893920000001</v>
+      </c>
+      <c r="O97">
+        <v>-49.84966624000002</v>
+      </c>
+      <c r="P97">
+        <v>-176.7397257600001</v>
+      </c>
+      <c r="Q97">
+        <v>-127.43972576</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>0.7007735391671743</v>
+      </c>
+      <c r="T97">
+        <v>14.39072911232988</v>
+      </c>
+      <c r="U97">
+        <v>0.2088</v>
+      </c>
+      <c r="V97">
+        <v>0.1108396031893811</v>
+      </c>
+      <c r="W97">
+        <v>0.1856566908540572</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.5038163781335505</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.2424019034959886</v>
+      </c>
+      <c r="C98">
+        <v>-904.7766173580292</v>
+      </c>
+      <c r="D98">
+        <v>424.7353826419704</v>
+      </c>
+      <c r="E98">
+        <v>924.6119999999996</v>
+      </c>
+      <c r="F98">
+        <v>2210.112</v>
+      </c>
+      <c r="G98">
+        <v>880.6</v>
+      </c>
+      <c r="H98">
+        <v>1016.7</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>279.375</v>
+      </c>
+      <c r="K98">
+        <v>49.30000000000001</v>
+      </c>
+      <c r="L98">
+        <v>230.075</v>
+      </c>
+      <c r="M98">
+        <v>527.7747456</v>
+      </c>
+      <c r="N98">
+        <v>-297.6997456</v>
+      </c>
+      <c r="O98">
+        <v>-65.49394403199999</v>
+      </c>
+      <c r="P98">
+        <v>-232.205801568</v>
+      </c>
+      <c r="Q98">
+        <v>-182.905801568</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>0.8785011796158542</v>
+      </c>
+      <c r="T98">
+        <v>18.25437346990987</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>0.09590549836267119</v>
+      </c>
+      <c r="W98">
+        <v>0.2158977669909941</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.4359340834666872</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.2444019034959886</v>
+      </c>
+      <c r="C99">
+        <v>-931.2604036305186</v>
+      </c>
+      <c r="D99">
+        <v>421.2735963694809</v>
+      </c>
+      <c r="E99">
+        <v>947.6339999999996</v>
+      </c>
+      <c r="F99">
+        <v>2233.134</v>
+      </c>
+      <c r="G99">
+        <v>880.6</v>
+      </c>
+      <c r="H99">
+        <v>1016.7</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>279.375</v>
+      </c>
+      <c r="K99">
+        <v>49.30000000000001</v>
+      </c>
+      <c r="L99">
+        <v>230.075</v>
+      </c>
+      <c r="M99">
+        <v>533.2723991999999</v>
+      </c>
+      <c r="N99">
+        <v>-303.1973991999999</v>
+      </c>
+      <c r="O99">
+        <v>-66.70342782399997</v>
+      </c>
+      <c r="P99">
+        <v>-236.4939713759999</v>
+      </c>
+      <c r="Q99">
+        <v>-187.1939713759999</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>1.158401572821139</v>
+      </c>
+      <c r="T99">
+        <v>24.33916462654649</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>0.09491678188470552</v>
+      </c>
+      <c r="W99">
+        <v>0.2161338724859323</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.4314399176577524</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.2464019034959886</v>
+      </c>
+      <c r="C100">
+        <v>-957.6882158561612</v>
+      </c>
+      <c r="D100">
+        <v>417.8677841438388</v>
+      </c>
+      <c r="E100">
+        <v>970.6559999999999</v>
+      </c>
+      <c r="F100">
+        <v>2256.156</v>
+      </c>
+      <c r="G100">
+        <v>880.6</v>
+      </c>
+      <c r="H100">
+        <v>1016.7</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>279.375</v>
+      </c>
+      <c r="K100">
+        <v>49.30000000000001</v>
+      </c>
+      <c r="L100">
+        <v>230.075</v>
+      </c>
+      <c r="M100">
+        <v>538.7700528</v>
+      </c>
+      <c r="N100">
+        <v>-308.6950528</v>
+      </c>
+      <c r="O100">
+        <v>-67.91291161600002</v>
+      </c>
+      <c r="P100">
+        <v>-240.782141184</v>
+      </c>
+      <c r="Q100">
+        <v>-191.482141184</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>1.718202359231708</v>
+      </c>
+      <c r="T100">
+        <v>36.50874693981974</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>0.09394824329404523</v>
+      </c>
+      <c r="W100">
+        <v>0.216365159501382</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.4270374695183874</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.2484019034959886</v>
+      </c>
+      <c r="C101">
+        <v>-984.0614007244055</v>
+      </c>
+      <c r="D101">
+        <v>414.5165992755943</v>
+      </c>
+      <c r="E101">
+        <v>993.6779999999999</v>
+      </c>
+      <c r="F101">
+        <v>2279.178</v>
+      </c>
+      <c r="G101">
+        <v>880.6</v>
+      </c>
+      <c r="H101">
+        <v>1016.7</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>279.375</v>
+      </c>
+      <c r="K101">
+        <v>49.30000000000001</v>
+      </c>
+      <c r="L101">
+        <v>230.075</v>
+      </c>
+      <c r="M101">
+        <v>544.2677064</v>
+      </c>
+      <c r="N101">
+        <v>-314.1927064</v>
+      </c>
+      <c r="O101">
+        <v>-69.12239540799999</v>
+      </c>
+      <c r="P101">
+        <v>-245.070310992</v>
+      </c>
+      <c r="Q101">
+        <v>-195.770310992</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>3.397604718463417</v>
+      </c>
+      <c r="T101">
+        <v>73.01749387963949</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>0.09299927113955994</v>
+      </c>
+      <c r="W101">
+        <v>0.2165917740518731</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.4227239597252724</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/norway/norway_air_transport.xlsx
+++ b/research/traditional_assets/database/data/norway/norway_air_transport.xlsx
@@ -1397,7 +1397,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1534,22 +1534,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.0806226732488448</v>
+        <v>0.08048040336769734</v>
       </c>
       <c r="C2">
-        <v>2154.736144707648</v>
+        <v>2135.211230617439</v>
       </c>
       <c r="D2">
-        <v>1066.736144707648</v>
+        <v>1071.112230617439</v>
       </c>
       <c r="E2">
-        <v>-1456.8</v>
+        <v>-1432.899</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>23.901</v>
       </c>
       <c r="G2">
         <v>1088</v>
@@ -1570,28 +1570,28 @@
         <v>305.075</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>1.2022203</v>
       </c>
       <c r="N2">
-        <v>305.075</v>
+        <v>303.8727797</v>
       </c>
       <c r="O2">
-        <v>67.1165</v>
+        <v>66.852011534</v>
       </c>
       <c r="P2">
-        <v>237.9585</v>
+        <v>237.020768166</v>
       </c>
       <c r="Q2">
-        <v>352.2585</v>
+        <v>351.320768166</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.0806226732488448</v>
+        <v>0.08089703370474478</v>
       </c>
       <c r="T2">
-        <v>0.8042187817285175</v>
+        <v>0.8105550509178936</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1608,7 +1608,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>253.75964787818</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1616,22 +1616,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08048040336769734</v>
+        <v>0.08033813348654988</v>
       </c>
       <c r="C3">
-        <v>2135.211230617439</v>
+        <v>2115.72236857518</v>
       </c>
       <c r="D3">
-        <v>1071.112230617439</v>
+        <v>1075.52436857518</v>
       </c>
       <c r="E3">
-        <v>-1432.899</v>
+        <v>-1408.998</v>
       </c>
       <c r="F3">
-        <v>23.901</v>
+        <v>47.802</v>
       </c>
       <c r="G3">
         <v>1088</v>
@@ -1652,28 +1652,28 @@
         <v>305.075</v>
       </c>
       <c r="M3">
-        <v>1.2022203</v>
+        <v>2.4044406</v>
       </c>
       <c r="N3">
-        <v>303.8727797</v>
+        <v>302.6705594</v>
       </c>
       <c r="O3">
-        <v>66.852011534</v>
+        <v>66.587523068</v>
       </c>
       <c r="P3">
-        <v>237.020768166</v>
+        <v>236.083036332</v>
       </c>
       <c r="Q3">
-        <v>351.320768166</v>
+        <v>350.383036332</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08089703370474478</v>
+        <v>0.08117699335362233</v>
       </c>
       <c r="T3">
-        <v>0.8105550509178936</v>
+        <v>0.8170206317233796</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1690,7 +1690,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>253.75964787818</v>
+        <v>126.87982393909</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1698,22 +1698,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08033813348654988</v>
+        <v>0.08019586360540241</v>
       </c>
       <c r="C4">
-        <v>2115.72236857518</v>
+        <v>2096.270005941691</v>
       </c>
       <c r="D4">
-        <v>1075.52436857518</v>
+        <v>1079.973005941691</v>
       </c>
       <c r="E4">
-        <v>-1408.998</v>
+        <v>-1385.097</v>
       </c>
       <c r="F4">
-        <v>47.802</v>
+        <v>71.70299999999999</v>
       </c>
       <c r="G4">
         <v>1088</v>
@@ -1734,28 +1734,28 @@
         <v>305.075</v>
       </c>
       <c r="M4">
-        <v>2.4044406</v>
+        <v>3.606660899999999</v>
       </c>
       <c r="N4">
-        <v>302.6705594</v>
+        <v>301.4683391</v>
       </c>
       <c r="O4">
-        <v>66.587523068</v>
+        <v>66.32303460199999</v>
       </c>
       <c r="P4">
-        <v>236.083036332</v>
+        <v>235.145304498</v>
       </c>
       <c r="Q4">
-        <v>350.383036332</v>
+        <v>349.445304498</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08117699335362233</v>
+        <v>0.08146272536639425</v>
       </c>
       <c r="T4">
-        <v>0.8170206317233796</v>
+        <v>0.8236195234733085</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1772,7 +1772,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>126.87982393909</v>
+        <v>84.5865492927267</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1780,22 +1780,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08019586360540241</v>
+        <v>0.08005359372425497</v>
       </c>
       <c r="C5">
-        <v>2096.270005941691</v>
+        <v>2076.854597510116</v>
       </c>
       <c r="D5">
-        <v>1079.973005941691</v>
+        <v>1084.458597510116</v>
       </c>
       <c r="E5">
-        <v>-1385.097</v>
+        <v>-1361.196</v>
       </c>
       <c r="F5">
-        <v>71.70299999999999</v>
+        <v>95.604</v>
       </c>
       <c r="G5">
         <v>1088</v>
@@ -1816,28 +1816,28 @@
         <v>305.075</v>
       </c>
       <c r="M5">
-        <v>3.606660899999999</v>
+        <v>4.8088812</v>
       </c>
       <c r="N5">
-        <v>301.4683391</v>
+        <v>300.2661188</v>
       </c>
       <c r="O5">
-        <v>66.32303460199999</v>
+        <v>66.058546136</v>
       </c>
       <c r="P5">
-        <v>235.145304498</v>
+        <v>234.207572664</v>
       </c>
       <c r="Q5">
-        <v>349.445304498</v>
+        <v>348.507572664</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08146272536639425</v>
+        <v>0.08175441012943226</v>
       </c>
       <c r="T5">
-        <v>0.8236195234733085</v>
+        <v>0.8303558921346943</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1854,7 +1854,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>84.5865492927267</v>
+        <v>63.43991196954502</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1862,22 +1862,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08005359372425497</v>
+        <v>0.07991132384310751</v>
       </c>
       <c r="C6">
-        <v>2076.854597510116</v>
+        <v>2057.476605660921</v>
       </c>
       <c r="D6">
-        <v>1084.458597510116</v>
+        <v>1088.98160566092</v>
       </c>
       <c r="E6">
-        <v>-1361.196</v>
+        <v>-1337.295</v>
       </c>
       <c r="F6">
-        <v>95.604</v>
+        <v>119.505</v>
       </c>
       <c r="G6">
         <v>1088</v>
@@ -1898,28 +1898,28 @@
         <v>305.075</v>
       </c>
       <c r="M6">
-        <v>4.8088812</v>
+        <v>6.0111015</v>
       </c>
       <c r="N6">
-        <v>300.2661188</v>
+        <v>299.0638985</v>
       </c>
       <c r="O6">
-        <v>66.058546136</v>
+        <v>65.79405767</v>
       </c>
       <c r="P6">
-        <v>234.207572664</v>
+        <v>233.26984083</v>
       </c>
       <c r="Q6">
-        <v>348.507572664</v>
+        <v>347.56984083</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08175441012943226</v>
+        <v>0.0820522356243237</v>
       </c>
       <c r="T6">
-        <v>0.8303558921346943</v>
+        <v>0.8372340790836883</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1936,7 +1936,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>63.43991196954502</v>
+        <v>50.75192957563601</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1944,22 +1944,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.07991132384310751</v>
+        <v>0.07976905396196005</v>
       </c>
       <c r="C7">
-        <v>2057.476605660921</v>
+        <v>2038.136500520773</v>
       </c>
       <c r="D7">
-        <v>1088.98160566092</v>
+        <v>1093.542500520773</v>
       </c>
       <c r="E7">
-        <v>-1337.295</v>
+        <v>-1313.394</v>
       </c>
       <c r="F7">
-        <v>119.505</v>
+        <v>143.406</v>
       </c>
       <c r="G7">
         <v>1088</v>
@@ -1980,28 +1980,28 @@
         <v>305.075</v>
       </c>
       <c r="M7">
-        <v>6.0111015</v>
+        <v>7.2133218</v>
       </c>
       <c r="N7">
-        <v>299.0638985</v>
+        <v>297.8616782</v>
       </c>
       <c r="O7">
-        <v>65.79405767</v>
+        <v>65.529569204</v>
       </c>
       <c r="P7">
-        <v>233.26984083</v>
+        <v>232.332108996</v>
       </c>
       <c r="Q7">
-        <v>347.56984083</v>
+        <v>346.632108996</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.0820522356243237</v>
+        <v>0.08235639783187239</v>
       </c>
       <c r="T7">
-        <v>0.8372340790836883</v>
+        <v>0.8442586104358522</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2018,7 +2018,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>50.75192957563601</v>
+        <v>42.29327464636334</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2026,22 +2026,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07976905396196005</v>
+        <v>0.07962678408081258</v>
       </c>
       <c r="C8">
-        <v>2038.136500520773</v>
+        <v>2018.834760125443</v>
       </c>
       <c r="D8">
-        <v>1093.542500520773</v>
+        <v>1098.141760125443</v>
       </c>
       <c r="E8">
-        <v>-1313.394</v>
+        <v>-1289.493</v>
       </c>
       <c r="F8">
-        <v>143.406</v>
+        <v>167.307</v>
       </c>
       <c r="G8">
         <v>1088</v>
@@ -2062,28 +2062,28 @@
         <v>305.075</v>
       </c>
       <c r="M8">
-        <v>7.213321799999998</v>
+        <v>8.4155421</v>
       </c>
       <c r="N8">
-        <v>297.8616782</v>
+        <v>296.6594579</v>
       </c>
       <c r="O8">
-        <v>65.529569204</v>
+        <v>65.26508073800001</v>
       </c>
       <c r="P8">
-        <v>232.332108996</v>
+        <v>231.394377162</v>
       </c>
       <c r="Q8">
-        <v>346.632108996</v>
+        <v>345.694377162</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08235639783187239</v>
+        <v>0.08266710116216407</v>
       </c>
       <c r="T8">
-        <v>0.8442586104358522</v>
+        <v>0.8514342069783851</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2100,7 +2100,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>42.29327464636335</v>
+        <v>36.25137826831144</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2108,22 +2108,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.0796267840808126</v>
+        <v>0.07948451419966512</v>
       </c>
       <c r="C9">
-        <v>2018.834760125442</v>
+        <v>1999.571870586827</v>
       </c>
       <c r="D9">
-        <v>1098.141760125442</v>
+        <v>1102.779870586827</v>
       </c>
       <c r="E9">
-        <v>-1289.493</v>
+        <v>-1265.592</v>
       </c>
       <c r="F9">
-        <v>167.307</v>
+        <v>191.208</v>
       </c>
       <c r="G9">
         <v>1088</v>
@@ -2144,28 +2144,28 @@
         <v>305.075</v>
       </c>
       <c r="M9">
-        <v>8.4155421</v>
+        <v>9.6177624</v>
       </c>
       <c r="N9">
-        <v>296.6594579</v>
+        <v>295.4572376</v>
       </c>
       <c r="O9">
-        <v>65.26508073800001</v>
+        <v>65.00059227199999</v>
       </c>
       <c r="P9">
-        <v>231.394377162</v>
+        <v>230.456645328</v>
       </c>
       <c r="Q9">
-        <v>345.694377162</v>
+        <v>344.756645328</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08266710116216408</v>
+        <v>0.08298455891267949</v>
       </c>
       <c r="T9">
-        <v>0.8514342069783853</v>
+        <v>0.8587657947501038</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2182,7 +2182,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>36.25137826831144</v>
+        <v>31.71995598477251</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2190,22 +2190,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07948451419966512</v>
+        <v>0.07934224431851768</v>
       </c>
       <c r="C10">
-        <v>1999.571870586827</v>
+        <v>1980.348326264221</v>
       </c>
       <c r="D10">
-        <v>1102.779870586827</v>
+        <v>1107.457326264221</v>
       </c>
       <c r="E10">
-        <v>-1265.592</v>
+        <v>-1241.691</v>
       </c>
       <c r="F10">
-        <v>191.208</v>
+        <v>215.109</v>
       </c>
       <c r="G10">
         <v>1088</v>
@@ -2226,28 +2226,28 @@
         <v>305.075</v>
       </c>
       <c r="M10">
-        <v>9.6177624</v>
+        <v>10.8199827</v>
       </c>
       <c r="N10">
-        <v>295.4572376</v>
+        <v>294.2550173</v>
       </c>
       <c r="O10">
-        <v>65.00059227199999</v>
+        <v>64.73610380599999</v>
       </c>
       <c r="P10">
-        <v>230.456645328</v>
+        <v>229.518913494</v>
       </c>
       <c r="Q10">
-        <v>344.756645328</v>
+        <v>343.818913494</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08298455891267949</v>
+        <v>0.08330899375661283</v>
       </c>
       <c r="T10">
-        <v>0.8587657947501038</v>
+        <v>0.8662585163190031</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2264,7 +2264,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>31.71995598477251</v>
+        <v>28.1955164309089</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2272,22 +2272,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.07934224431851768</v>
+        <v>0.07919997443737022</v>
       </c>
       <c r="C11">
-        <v>1980.348326264221</v>
+        <v>1961.164629939975</v>
       </c>
       <c r="D11">
-        <v>1107.457326264221</v>
+        <v>1112.174629939975</v>
       </c>
       <c r="E11">
-        <v>-1241.691</v>
+        <v>-1217.79</v>
       </c>
       <c r="F11">
-        <v>215.109</v>
+        <v>239.01</v>
       </c>
       <c r="G11">
         <v>1088</v>
@@ -2308,28 +2308,28 @@
         <v>305.075</v>
       </c>
       <c r="M11">
-        <v>10.8199827</v>
+        <v>12.022203</v>
       </c>
       <c r="N11">
-        <v>294.2550173</v>
+        <v>293.052797</v>
       </c>
       <c r="O11">
-        <v>64.73610380599999</v>
+        <v>64.47161534</v>
       </c>
       <c r="P11">
-        <v>229.518913494</v>
+        <v>228.58118166</v>
       </c>
       <c r="Q11">
-        <v>343.818913494</v>
+        <v>342.88118166</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08330899375661283</v>
+        <v>0.08364063826374468</v>
       </c>
       <c r="T11">
-        <v>0.8662585163190031</v>
+        <v>0.8739177428116557</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2346,7 +2346,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>28.1955164309089</v>
+        <v>25.37596478781801</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2354,22 +2354,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.07919997443737022</v>
+        <v>0.07905770455622275</v>
       </c>
       <c r="C12">
-        <v>1961.164629939975</v>
+        <v>1942.021292999651</v>
       </c>
       <c r="D12">
-        <v>1112.174629939975</v>
+        <v>1116.932292999652</v>
       </c>
       <c r="E12">
-        <v>-1217.79</v>
+        <v>-1193.889</v>
       </c>
       <c r="F12">
-        <v>239.01</v>
+        <v>262.911</v>
       </c>
       <c r="G12">
         <v>1088</v>
@@ -2390,28 +2390,28 @@
         <v>305.075</v>
       </c>
       <c r="M12">
-        <v>12.022203</v>
+        <v>13.2244233</v>
       </c>
       <c r="N12">
-        <v>293.052797</v>
+        <v>291.8505767</v>
       </c>
       <c r="O12">
-        <v>64.47161534</v>
+        <v>64.207126874</v>
       </c>
       <c r="P12">
-        <v>228.58118166</v>
+        <v>227.643449826</v>
       </c>
       <c r="Q12">
-        <v>342.88118166</v>
+        <v>341.943449826</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08364063826374468</v>
+        <v>0.08397973545643006</v>
       </c>
       <c r="T12">
-        <v>0.8739177428116557</v>
+        <v>0.8817490867535813</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2428,7 +2428,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>25.37596478781801</v>
+        <v>23.06905889801637</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2436,22 +2436,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07905770455622275</v>
+        <v>0.07891543467507531</v>
       </c>
       <c r="C13">
-        <v>1942.021292999651</v>
+        <v>1922.918835616832</v>
       </c>
       <c r="D13">
-        <v>1116.932292999652</v>
+        <v>1121.730835616832</v>
       </c>
       <c r="E13">
-        <v>-1193.889</v>
+        <v>-1169.988</v>
       </c>
       <c r="F13">
-        <v>262.911</v>
+        <v>286.812</v>
       </c>
       <c r="G13">
         <v>1088</v>
@@ -2472,28 +2472,28 @@
         <v>305.075</v>
       </c>
       <c r="M13">
-        <v>13.2244233</v>
+        <v>14.4266436</v>
       </c>
       <c r="N13">
-        <v>291.8505767</v>
+        <v>290.6483564</v>
       </c>
       <c r="O13">
-        <v>64.207126874</v>
+        <v>63.942638408</v>
       </c>
       <c r="P13">
-        <v>227.643449826</v>
+        <v>226.705717992</v>
       </c>
       <c r="Q13">
-        <v>341.943449826</v>
+        <v>341.005717992</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08397973545643006</v>
+        <v>0.08432653940349466</v>
       </c>
       <c r="T13">
-        <v>0.8817490867535813</v>
+        <v>0.8897584157850962</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2510,7 +2510,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>23.06905889801637</v>
+        <v>21.14663732318168</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2518,22 +2518,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.07891543467507531</v>
+        <v>0.07877316479392785</v>
       </c>
       <c r="C14">
-        <v>1922.918835616832</v>
+        <v>1903.857786942707</v>
       </c>
       <c r="D14">
-        <v>1121.730835616832</v>
+        <v>1126.570786942707</v>
       </c>
       <c r="E14">
-        <v>-1169.988</v>
+        <v>-1146.087</v>
       </c>
       <c r="F14">
-        <v>286.812</v>
+        <v>310.713</v>
       </c>
       <c r="G14">
         <v>1088</v>
@@ -2554,28 +2554,28 @@
         <v>305.075</v>
       </c>
       <c r="M14">
-        <v>14.4266436</v>
+        <v>15.6288639</v>
       </c>
       <c r="N14">
-        <v>290.6483564</v>
+        <v>289.4461361</v>
       </c>
       <c r="O14">
-        <v>63.942638408</v>
+        <v>63.678149942</v>
       </c>
       <c r="P14">
-        <v>226.705717992</v>
+        <v>225.767986158</v>
       </c>
       <c r="Q14">
-        <v>341.005717992</v>
+        <v>340.067986158</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.08432653940349466</v>
+        <v>0.08468131585508948</v>
       </c>
       <c r="T14">
-        <v>0.8897584157850962</v>
+        <v>0.8979518673230826</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2592,7 +2592,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>21.14663732318168</v>
+        <v>19.51997291370616</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2600,22 +2600,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07877316479392785</v>
+        <v>0.07863089491278039</v>
       </c>
       <c r="C15">
-        <v>1903.857786942707</v>
+        <v>1884.83868530059</v>
       </c>
       <c r="D15">
-        <v>1126.570786942707</v>
+        <v>1131.45268530059</v>
       </c>
       <c r="E15">
-        <v>-1146.087</v>
+        <v>-1122.186</v>
       </c>
       <c r="F15">
-        <v>310.713</v>
+        <v>334.614</v>
       </c>
       <c r="G15">
         <v>1088</v>
@@ -2636,28 +2636,28 @@
         <v>305.075</v>
       </c>
       <c r="M15">
-        <v>15.6288639</v>
+        <v>16.8310842</v>
       </c>
       <c r="N15">
-        <v>289.4461361</v>
+        <v>288.2439158</v>
       </c>
       <c r="O15">
-        <v>63.678149942</v>
+        <v>63.41366147599999</v>
       </c>
       <c r="P15">
-        <v>225.767986158</v>
+        <v>224.830254324</v>
       </c>
       <c r="Q15">
-        <v>340.067986158</v>
+        <v>339.130254324</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08468131585508948</v>
+        <v>0.08504434292183766</v>
       </c>
       <c r="T15">
-        <v>0.8979518673230826</v>
+        <v>0.9063358642456735</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2674,7 +2674,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>19.51997291370616</v>
+        <v>18.12568913415572</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2682,22 +2682,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.07863089491278039</v>
+        <v>0.07848862503163294</v>
       </c>
       <c r="C16">
-        <v>1884.83868530059</v>
+        <v>1865.862078385521</v>
       </c>
       <c r="D16">
-        <v>1131.45268530059</v>
+        <v>1136.377078385521</v>
       </c>
       <c r="E16">
-        <v>-1122.186</v>
+        <v>-1098.285</v>
       </c>
       <c r="F16">
-        <v>334.614</v>
+        <v>358.515</v>
       </c>
       <c r="G16">
         <v>1088</v>
@@ -2718,28 +2718,28 @@
         <v>305.075</v>
       </c>
       <c r="M16">
-        <v>16.8310842</v>
+        <v>18.0333045</v>
       </c>
       <c r="N16">
-        <v>288.2439158</v>
+        <v>287.0416955</v>
       </c>
       <c r="O16">
-        <v>63.41366147599999</v>
+        <v>63.14917301</v>
       </c>
       <c r="P16">
-        <v>224.830254324</v>
+        <v>223.89252249</v>
       </c>
       <c r="Q16">
-        <v>339.130254324</v>
+        <v>338.19252249</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.08504434292183766</v>
+        <v>0.0854159118019211</v>
       </c>
       <c r="T16">
-        <v>0.9063358642456735</v>
+        <v>0.9149171316840899</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2756,7 +2756,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>18.12568913415572</v>
+        <v>16.91730985854534</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2764,22 +2764,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.07848862503163294</v>
+        <v>0.07834635515048546</v>
       </c>
       <c r="C17">
-        <v>1865.862078385521</v>
+        <v>1846.928523469098</v>
       </c>
       <c r="D17">
-        <v>1136.377078385521</v>
+        <v>1141.344523469098</v>
       </c>
       <c r="E17">
-        <v>-1098.285</v>
+        <v>-1074.384</v>
       </c>
       <c r="F17">
-        <v>358.515</v>
+        <v>382.416</v>
       </c>
       <c r="G17">
         <v>1088</v>
@@ -2800,28 +2800,28 @@
         <v>305.075</v>
       </c>
       <c r="M17">
-        <v>18.0333045</v>
+        <v>19.2355248</v>
       </c>
       <c r="N17">
-        <v>287.0416955</v>
+        <v>285.8394752</v>
       </c>
       <c r="O17">
-        <v>63.14917301</v>
+        <v>62.884684544</v>
       </c>
       <c r="P17">
-        <v>223.89252249</v>
+        <v>222.954790656</v>
       </c>
       <c r="Q17">
-        <v>338.19252249</v>
+        <v>337.254790656</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.0854159118019211</v>
+        <v>0.08579632756010175</v>
       </c>
       <c r="T17">
-        <v>0.9149171316840899</v>
+        <v>0.9237027150138972</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2838,7 +2838,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>16.91730985854534</v>
+        <v>15.85997799238625</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2846,22 +2846,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.07834635515048546</v>
+        <v>0.078204085269338</v>
       </c>
       <c r="C18">
-        <v>1846.928523469098</v>
+        <v>1828.038587609702</v>
       </c>
       <c r="D18">
-        <v>1141.344523469098</v>
+        <v>1146.355587609702</v>
       </c>
       <c r="E18">
-        <v>-1074.384</v>
+        <v>-1050.483</v>
       </c>
       <c r="F18">
-        <v>382.416</v>
+        <v>406.317</v>
       </c>
       <c r="G18">
         <v>1088</v>
@@ -2882,28 +2882,28 @@
         <v>305.075</v>
       </c>
       <c r="M18">
-        <v>19.2355248</v>
+        <v>20.4377451</v>
       </c>
       <c r="N18">
-        <v>285.8394752</v>
+        <v>284.6372549</v>
       </c>
       <c r="O18">
-        <v>62.884684544</v>
+        <v>62.62019607800001</v>
       </c>
       <c r="P18">
-        <v>222.954790656</v>
+        <v>222.017058822</v>
       </c>
       <c r="Q18">
-        <v>337.254790656</v>
+        <v>336.317058822</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.08579632756010175</v>
+        <v>0.08618590996305783</v>
       </c>
       <c r="T18">
-        <v>0.9237027150138972</v>
+        <v>0.9326999991468325</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2920,7 +2920,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>15.85997799238625</v>
+        <v>14.92703811048118</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2928,22 +2928,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.078204085269338</v>
+        <v>0.07806181538819056</v>
       </c>
       <c r="C19">
-        <v>1828.038587609702</v>
+        <v>1809.192847868294</v>
       </c>
       <c r="D19">
-        <v>1146.355587609702</v>
+        <v>1151.410847868294</v>
       </c>
       <c r="E19">
-        <v>-1050.483</v>
+        <v>-1026.582</v>
       </c>
       <c r="F19">
-        <v>406.317</v>
+        <v>430.218</v>
       </c>
       <c r="G19">
         <v>1088</v>
@@ -2964,28 +2964,28 @@
         <v>305.075</v>
       </c>
       <c r="M19">
-        <v>20.4377451</v>
+        <v>21.6399654</v>
       </c>
       <c r="N19">
-        <v>284.6372549</v>
+        <v>283.4350346</v>
       </c>
       <c r="O19">
-        <v>62.62019607800001</v>
+        <v>62.355707612</v>
       </c>
       <c r="P19">
-        <v>222.017058822</v>
+        <v>221.079326988</v>
       </c>
       <c r="Q19">
-        <v>336.317058822</v>
+        <v>335.379326988</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.08618590996305783</v>
+        <v>0.08658499437584213</v>
       </c>
       <c r="T19">
-        <v>0.9326999991468325</v>
+        <v>0.9419167292342296</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -3002,7 +3002,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>14.92703811048118</v>
+        <v>14.09775821545445</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3010,22 +3010,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.07806181538819056</v>
+        <v>0.07791954550704309</v>
       </c>
       <c r="C20">
-        <v>1809.192847868294</v>
+        <v>1790.391891529939</v>
       </c>
       <c r="D20">
-        <v>1151.410847868294</v>
+        <v>1156.510891529939</v>
       </c>
       <c r="E20">
-        <v>-1026.582</v>
+        <v>-1002.681</v>
       </c>
       <c r="F20">
-        <v>430.218</v>
+        <v>454.119</v>
       </c>
       <c r="G20">
         <v>1088</v>
@@ -3046,28 +3046,28 @@
         <v>305.075</v>
       </c>
       <c r="M20">
-        <v>21.6399654</v>
+        <v>22.8421857</v>
       </c>
       <c r="N20">
-        <v>283.4350346</v>
+        <v>282.2328143</v>
       </c>
       <c r="O20">
-        <v>62.355707612</v>
+        <v>62.09121914599999</v>
       </c>
       <c r="P20">
-        <v>221.079326988</v>
+        <v>220.141595154</v>
       </c>
       <c r="Q20">
-        <v>335.379326988</v>
+        <v>334.441595154</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.08658499437584213</v>
+        <v>0.08699393272474455</v>
       </c>
       <c r="T20">
-        <v>0.9419167292342294</v>
+        <v>0.9513610329040314</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -3084,7 +3084,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>14.09775821545445</v>
+        <v>13.35577094095684</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3092,22 +3092,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.07791954550704309</v>
+        <v>0.07801127562589563</v>
       </c>
       <c r="C21">
-        <v>1790.391891529939</v>
+        <v>1763.197421169858</v>
       </c>
       <c r="D21">
-        <v>1156.510891529939</v>
+        <v>1153.217421169858</v>
       </c>
       <c r="E21">
-        <v>-1002.681</v>
+        <v>-978.78</v>
       </c>
       <c r="F21">
-        <v>454.119</v>
+        <v>478.02</v>
       </c>
       <c r="G21">
         <v>1088</v>
@@ -3128,45 +3128,45 @@
         <v>305.075</v>
       </c>
       <c r="M21">
-        <v>22.8421857</v>
+        <v>24.761436</v>
       </c>
       <c r="N21">
-        <v>282.2328143</v>
+        <v>280.313564</v>
       </c>
       <c r="O21">
-        <v>62.09121914599999</v>
+        <v>61.66898407999999</v>
       </c>
       <c r="P21">
-        <v>220.141595154</v>
+        <v>218.64457992</v>
       </c>
       <c r="Q21">
-        <v>334.441595154</v>
+        <v>332.94457992</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.08699393272474455</v>
+        <v>0.08741309453236953</v>
       </c>
       <c r="T21">
-        <v>0.9513610329040314</v>
+        <v>0.9610414441655785</v>
       </c>
       <c r="U21">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V21">
         <v>0.22</v>
       </c>
       <c r="W21">
-        <v>0.039234</v>
+        <v>0.040404</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y21">
-        <v>13.35577094095684</v>
+        <v>12.32056977632477</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3174,22 +3174,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.07801127562589563</v>
+        <v>0.07788070574474817</v>
       </c>
       <c r="C22">
-        <v>1763.197421169858</v>
+        <v>1743.990066715482</v>
       </c>
       <c r="D22">
-        <v>1153.217421169858</v>
+        <v>1157.911066715482</v>
       </c>
       <c r="E22">
-        <v>-978.78</v>
+        <v>-954.8789999999999</v>
       </c>
       <c r="F22">
-        <v>478.02</v>
+        <v>501.921</v>
       </c>
       <c r="G22">
         <v>1088</v>
@@ -3210,28 +3210,28 @@
         <v>305.075</v>
       </c>
       <c r="M22">
-        <v>24.761436</v>
+        <v>25.9995078</v>
       </c>
       <c r="N22">
-        <v>280.313564</v>
+        <v>279.0754922</v>
       </c>
       <c r="O22">
-        <v>61.66898407999999</v>
+        <v>61.396608284</v>
       </c>
       <c r="P22">
-        <v>218.64457992</v>
+        <v>217.678883916</v>
       </c>
       <c r="Q22">
-        <v>332.94457992</v>
+        <v>331.978883916</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.08741309453236953</v>
+        <v>0.08784286803132679</v>
       </c>
       <c r="T22">
-        <v>0.9610414441655785</v>
+        <v>0.9709669291299494</v>
       </c>
       <c r="U22">
         <v>0.0518</v>
@@ -3248,7 +3248,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>12.32056977632477</v>
+        <v>11.73387597745216</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3256,22 +3256,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.07788070574474817</v>
+        <v>0.0777501358636007</v>
       </c>
       <c r="C23">
-        <v>1743.990066715482</v>
+        <v>1724.821075086458</v>
       </c>
       <c r="D23">
-        <v>1157.911066715482</v>
+        <v>1162.643075086458</v>
       </c>
       <c r="E23">
-        <v>-954.879</v>
+        <v>-930.978</v>
       </c>
       <c r="F23">
-        <v>501.9209999999999</v>
+        <v>525.822</v>
       </c>
       <c r="G23">
         <v>1088</v>
@@ -3292,28 +3292,28 @@
         <v>305.075</v>
       </c>
       <c r="M23">
-        <v>25.9995078</v>
+        <v>27.2375796</v>
       </c>
       <c r="N23">
-        <v>279.0754922</v>
+        <v>277.8374204</v>
       </c>
       <c r="O23">
-        <v>61.396608284</v>
+        <v>61.124232488</v>
       </c>
       <c r="P23">
-        <v>217.678883916</v>
+        <v>216.713187912</v>
       </c>
       <c r="Q23">
-        <v>331.978883916</v>
+        <v>331.013187912</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.08784286803132679</v>
+        <v>0.08828366136359064</v>
       </c>
       <c r="T23">
-        <v>0.9709669291299492</v>
+        <v>0.9811469137087913</v>
       </c>
       <c r="U23">
         <v>0.0518</v>
@@ -3330,7 +3330,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>11.73387597745216</v>
+        <v>11.20051797847706</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3338,22 +3338,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.0777501358636007</v>
+        <v>0.07761956598245326</v>
       </c>
       <c r="C24">
-        <v>1724.821075086458</v>
+        <v>1705.690918542169</v>
       </c>
       <c r="D24">
-        <v>1162.643075086458</v>
+        <v>1167.413918542169</v>
       </c>
       <c r="E24">
-        <v>-930.978</v>
+        <v>-907.077</v>
       </c>
       <c r="F24">
-        <v>525.822</v>
+        <v>549.723</v>
       </c>
       <c r="G24">
         <v>1088</v>
@@ -3374,28 +3374,28 @@
         <v>305.075</v>
       </c>
       <c r="M24">
-        <v>27.2375796</v>
+        <v>28.4756514</v>
       </c>
       <c r="N24">
-        <v>277.8374204</v>
+        <v>276.5993486</v>
       </c>
       <c r="O24">
-        <v>61.124232488</v>
+        <v>60.851856692</v>
       </c>
       <c r="P24">
-        <v>216.713187912</v>
+        <v>215.747491908</v>
       </c>
       <c r="Q24">
-        <v>331.013187912</v>
+        <v>330.047491908</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.08828366136359064</v>
+        <v>0.08873590387331592</v>
       </c>
       <c r="T24">
-        <v>0.9811469137087913</v>
+        <v>0.9915913134714994</v>
       </c>
       <c r="U24">
         <v>0.0518</v>
@@ -3412,7 +3412,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>11.20051797847706</v>
+        <v>10.71353893593458</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3420,22 +3420,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.07761956598245326</v>
+        <v>0.07748899610130579</v>
       </c>
       <c r="C25">
-        <v>1705.690918542169</v>
+        <v>1686.600077125503</v>
       </c>
       <c r="D25">
-        <v>1167.413918542169</v>
+        <v>1172.224077125503</v>
       </c>
       <c r="E25">
-        <v>-907.077</v>
+        <v>-883.1759999999999</v>
       </c>
       <c r="F25">
-        <v>549.723</v>
+        <v>573.624</v>
       </c>
       <c r="G25">
         <v>1088</v>
@@ -3456,28 +3456,28 @@
         <v>305.075</v>
       </c>
       <c r="M25">
-        <v>28.4756514</v>
+        <v>29.7137232</v>
       </c>
       <c r="N25">
-        <v>276.5993486</v>
+        <v>275.3612768</v>
       </c>
       <c r="O25">
-        <v>60.851856692</v>
+        <v>60.579480896</v>
       </c>
       <c r="P25">
-        <v>215.747491908</v>
+        <v>214.781795904</v>
       </c>
       <c r="Q25">
-        <v>330.047491908</v>
+        <v>329.081795904</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.08873590387331592</v>
+        <v>0.08920004750171814</v>
       </c>
       <c r="T25">
-        <v>0.9915913134714994</v>
+        <v>1.002310565859542</v>
       </c>
       <c r="U25">
         <v>0.0518</v>
@@ -3494,7 +3494,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>10.71353893593458</v>
+        <v>10.26714148027064</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3502,22 +3502,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.07748899610130579</v>
+        <v>0.07735842622015834</v>
       </c>
       <c r="C26">
-        <v>1686.600077125504</v>
+        <v>1667.549038823868</v>
       </c>
       <c r="D26">
-        <v>1172.224077125503</v>
+        <v>1177.074038823868</v>
       </c>
       <c r="E26">
-        <v>-883.176</v>
+        <v>-859.275</v>
       </c>
       <c r="F26">
-        <v>573.6239999999999</v>
+        <v>597.525</v>
       </c>
       <c r="G26">
         <v>1088</v>
@@ -3538,28 +3538,28 @@
         <v>305.075</v>
       </c>
       <c r="M26">
-        <v>29.71372319999999</v>
+        <v>30.951795</v>
       </c>
       <c r="N26">
-        <v>275.3612768</v>
+        <v>274.123205</v>
       </c>
       <c r="O26">
-        <v>60.579480896</v>
+        <v>60.30710509999999</v>
       </c>
       <c r="P26">
-        <v>214.781795904</v>
+        <v>213.8160999</v>
       </c>
       <c r="Q26">
-        <v>329.081795904</v>
+        <v>328.1160999</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.08920004750171814</v>
+        <v>0.08967656829354445</v>
       </c>
       <c r="T26">
-        <v>1.002310565859542</v>
+        <v>1.013315664977932</v>
       </c>
       <c r="U26">
         <v>0.0518</v>
@@ -3576,7 +3576,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>10.26714148027064</v>
+        <v>9.856455821059813</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3584,22 +3584,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.07735842622015834</v>
+        <v>0.07757261633901089</v>
       </c>
       <c r="C27">
-        <v>1667.549038823868</v>
+        <v>1635.712978469258</v>
       </c>
       <c r="D27">
-        <v>1177.074038823868</v>
+        <v>1169.138978469258</v>
       </c>
       <c r="E27">
-        <v>-859.275</v>
+        <v>-835.3739999999999</v>
       </c>
       <c r="F27">
-        <v>597.525</v>
+        <v>621.426</v>
       </c>
       <c r="G27">
         <v>1088</v>
@@ -3620,45 +3620,45 @@
         <v>305.075</v>
       </c>
       <c r="M27">
-        <v>30.951795</v>
+        <v>33.246291</v>
       </c>
       <c r="N27">
-        <v>274.123205</v>
+        <v>271.828709</v>
       </c>
       <c r="O27">
-        <v>60.30710509999999</v>
+        <v>59.80231598</v>
       </c>
       <c r="P27">
-        <v>213.8160999</v>
+        <v>212.02639302</v>
       </c>
       <c r="Q27">
-        <v>328.1160999</v>
+        <v>326.32639302</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.08967656829354445</v>
+        <v>0.09016596802569038</v>
       </c>
       <c r="T27">
-        <v>1.013315664977932</v>
+        <v>1.02461819920763</v>
       </c>
       <c r="U27">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V27">
         <v>0.22</v>
       </c>
       <c r="W27">
-        <v>0.040404</v>
+        <v>0.04173</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y27">
-        <v>9.856455821059813</v>
+        <v>9.176211565975887</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3666,22 +3666,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.07757261633901089</v>
+        <v>0.07745530645786342</v>
       </c>
       <c r="C28">
-        <v>1635.712978469258</v>
+        <v>1616.14463450567</v>
       </c>
       <c r="D28">
-        <v>1169.138978469258</v>
+        <v>1173.471634505669</v>
       </c>
       <c r="E28">
-        <v>-835.3739999999999</v>
+        <v>-811.473</v>
       </c>
       <c r="F28">
-        <v>621.426</v>
+        <v>645.327</v>
       </c>
       <c r="G28">
         <v>1088</v>
@@ -3702,28 +3702,28 @@
         <v>305.075</v>
       </c>
       <c r="M28">
-        <v>33.246291</v>
+        <v>34.5249945</v>
       </c>
       <c r="N28">
-        <v>271.828709</v>
+        <v>270.5500055</v>
       </c>
       <c r="O28">
-        <v>59.80231598</v>
+        <v>59.52100121</v>
       </c>
       <c r="P28">
-        <v>212.02639302</v>
+        <v>211.02900429</v>
       </c>
       <c r="Q28">
-        <v>326.32639302</v>
+        <v>325.32900429</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09016596802569038</v>
+        <v>0.09066877596967592</v>
       </c>
       <c r="T28">
-        <v>1.02461819920763</v>
+        <v>1.036230391909375</v>
       </c>
       <c r="U28">
         <v>0.0535</v>
@@ -3740,7 +3740,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>9.176211565975887</v>
+        <v>8.836351878347148</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3748,22 +3748,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.07745530645786342</v>
+        <v>0.07733799657671596</v>
       </c>
       <c r="C29">
-        <v>1616.14463450567</v>
+        <v>1596.608522352585</v>
       </c>
       <c r="D29">
-        <v>1173.471634505669</v>
+        <v>1177.836522352585</v>
       </c>
       <c r="E29">
-        <v>-811.473</v>
+        <v>-787.5719999999999</v>
       </c>
       <c r="F29">
-        <v>645.327</v>
+        <v>669.2280000000001</v>
       </c>
       <c r="G29">
         <v>1088</v>
@@ -3784,28 +3784,28 @@
         <v>305.075</v>
       </c>
       <c r="M29">
-        <v>34.5249945</v>
+        <v>35.803698</v>
       </c>
       <c r="N29">
-        <v>270.5500055</v>
+        <v>269.271302</v>
       </c>
       <c r="O29">
-        <v>59.52100121</v>
+        <v>59.23968644</v>
       </c>
       <c r="P29">
-        <v>211.02900429</v>
+        <v>210.03161556</v>
       </c>
       <c r="Q29">
-        <v>325.32900429</v>
+        <v>324.33161556</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09066877596967592</v>
+        <v>0.09118555080099439</v>
       </c>
       <c r="T29">
-        <v>1.036230391909375</v>
+        <v>1.048165145519501</v>
       </c>
       <c r="U29">
         <v>0.0535</v>
@@ -3822,7 +3822,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>8.836351878347148</v>
+        <v>8.520767882691892</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3830,22 +3830,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.07733799657671596</v>
+        <v>0.0772206866955685</v>
       </c>
       <c r="C30">
-        <v>1596.608522352585</v>
+        <v>1577.105003024699</v>
       </c>
       <c r="D30">
-        <v>1177.836522352585</v>
+        <v>1182.234003024699</v>
       </c>
       <c r="E30">
-        <v>-787.5719999999999</v>
+        <v>-763.6709999999999</v>
       </c>
       <c r="F30">
-        <v>669.2280000000001</v>
+        <v>693.129</v>
       </c>
       <c r="G30">
         <v>1088</v>
@@ -3866,28 +3866,28 @@
         <v>305.075</v>
       </c>
       <c r="M30">
-        <v>35.803698</v>
+        <v>37.0824015</v>
       </c>
       <c r="N30">
-        <v>269.271302</v>
+        <v>267.9925985</v>
       </c>
       <c r="O30">
-        <v>59.23968644</v>
+        <v>58.95837167</v>
       </c>
       <c r="P30">
-        <v>210.03161556</v>
+        <v>209.03422683</v>
       </c>
       <c r="Q30">
-        <v>324.33161556</v>
+        <v>323.33422683</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.09118555080099439</v>
+        <v>0.09171688266981479</v>
       </c>
       <c r="T30">
-        <v>1.048165145519501</v>
+        <v>1.060436089372166</v>
       </c>
       <c r="U30">
         <v>0.0535</v>
@@ -3904,7 +3904,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>8.520767882691892</v>
+        <v>8.226948300530104</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3912,22 +3912,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.0772206866955685</v>
+        <v>0.07710337681442105</v>
       </c>
       <c r="C31">
-        <v>1577.105003024699</v>
+        <v>1557.634442948338</v>
       </c>
       <c r="D31">
-        <v>1182.234003024699</v>
+        <v>1186.664442948337</v>
       </c>
       <c r="E31">
-        <v>-763.671</v>
+        <v>-739.77</v>
       </c>
       <c r="F31">
-        <v>693.1289999999999</v>
+        <v>717.03</v>
       </c>
       <c r="G31">
         <v>1088</v>
@@ -3948,28 +3948,28 @@
         <v>305.075</v>
       </c>
       <c r="M31">
-        <v>37.0824015</v>
+        <v>38.36110499999999</v>
       </c>
       <c r="N31">
-        <v>267.9925985</v>
+        <v>266.713895</v>
       </c>
       <c r="O31">
-        <v>58.95837167</v>
+        <v>58.6770569</v>
       </c>
       <c r="P31">
-        <v>209.03422683</v>
+        <v>208.0368381</v>
       </c>
       <c r="Q31">
-        <v>323.33422683</v>
+        <v>322.3368381</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.09171688266981479</v>
+        <v>0.09226339544917292</v>
       </c>
       <c r="T31">
-        <v>1.060436089372166</v>
+        <v>1.073057631620622</v>
       </c>
       <c r="U31">
         <v>0.0535</v>
@@ -3986,7 +3986,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>8.226948300530104</v>
+        <v>7.952716690512434</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3994,22 +3994,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.07710337681442105</v>
+        <v>0.07698606693327358</v>
       </c>
       <c r="C32">
-        <v>1557.634442948338</v>
+        <v>1538.197214063241</v>
       </c>
       <c r="D32">
-        <v>1186.664442948337</v>
+        <v>1191.128214063241</v>
       </c>
       <c r="E32">
-        <v>-739.77</v>
+        <v>-715.869</v>
       </c>
       <c r="F32">
-        <v>717.03</v>
+        <v>740.9309999999999</v>
       </c>
       <c r="G32">
         <v>1088</v>
@@ -4030,28 +4030,28 @@
         <v>305.075</v>
       </c>
       <c r="M32">
-        <v>38.36110499999999</v>
+        <v>39.63980849999999</v>
       </c>
       <c r="N32">
-        <v>266.713895</v>
+        <v>265.4351915</v>
       </c>
       <c r="O32">
-        <v>58.6770569</v>
+        <v>58.39574213</v>
       </c>
       <c r="P32">
-        <v>208.0368381</v>
+        <v>207.03944937</v>
       </c>
       <c r="Q32">
-        <v>322.3368381</v>
+        <v>321.33944937</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.09226339544917292</v>
+        <v>0.09282574917865737</v>
       </c>
       <c r="T32">
-        <v>1.073057631620622</v>
+        <v>1.086045015673381</v>
       </c>
       <c r="U32">
         <v>0.0535</v>
@@ -4068,7 +4068,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>7.952716690512434</v>
+        <v>7.696177442431389</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4076,22 +4076,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.07698606693327358</v>
+        <v>0.07706843705212613</v>
       </c>
       <c r="C33">
-        <v>1538.197214063241</v>
+        <v>1511.158437384559</v>
       </c>
       <c r="D33">
-        <v>1191.128214063241</v>
+        <v>1187.990437384558</v>
       </c>
       <c r="E33">
-        <v>-715.869</v>
+        <v>-691.968</v>
       </c>
       <c r="F33">
-        <v>740.9309999999999</v>
+        <v>764.832</v>
       </c>
       <c r="G33">
         <v>1088</v>
@@ -4112,45 +4112,45 @@
         <v>305.075</v>
       </c>
       <c r="M33">
-        <v>39.63980849999999</v>
+        <v>41.5303776</v>
       </c>
       <c r="N33">
-        <v>265.4351915</v>
+        <v>263.5446224</v>
       </c>
       <c r="O33">
-        <v>58.39574213</v>
+        <v>57.979816928</v>
       </c>
       <c r="P33">
-        <v>207.03944937</v>
+        <v>205.564805472</v>
       </c>
       <c r="Q33">
-        <v>321.33944937</v>
+        <v>319.864805472</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.09282574917865737</v>
+        <v>0.09340464272371489</v>
       </c>
       <c r="T33">
-        <v>1.086045015673381</v>
+        <v>1.099414381610044</v>
       </c>
       <c r="U33">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V33">
         <v>0.22</v>
       </c>
       <c r="W33">
-        <v>0.04173</v>
+        <v>0.042354</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y33">
-        <v>7.696177442431389</v>
+        <v>7.345827744171533</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4158,22 +4158,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.07706843705212613</v>
+        <v>0.07695736717097866</v>
       </c>
       <c r="C34">
-        <v>1511.158437384559</v>
+        <v>1491.492389457387</v>
       </c>
       <c r="D34">
-        <v>1187.990437384558</v>
+        <v>1192.225389457387</v>
       </c>
       <c r="E34">
-        <v>-691.968</v>
+        <v>-668.0669999999999</v>
       </c>
       <c r="F34">
-        <v>764.832</v>
+        <v>788.7330000000001</v>
       </c>
       <c r="G34">
         <v>1088</v>
@@ -4194,28 +4194,28 @@
         <v>305.075</v>
       </c>
       <c r="M34">
-        <v>41.5303776</v>
+        <v>42.8282019</v>
       </c>
       <c r="N34">
-        <v>263.5446224</v>
+        <v>262.2467981</v>
       </c>
       <c r="O34">
-        <v>57.979816928</v>
+        <v>57.694295582</v>
       </c>
       <c r="P34">
-        <v>205.564805472</v>
+        <v>204.552502518</v>
       </c>
       <c r="Q34">
-        <v>319.864805472</v>
+        <v>318.852502518</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.09340464272371489</v>
+        <v>0.09400081667310249</v>
       </c>
       <c r="T34">
-        <v>1.099414381610044</v>
+        <v>1.113182833097055</v>
       </c>
       <c r="U34">
         <v>0.0543</v>
@@ -4232,7 +4232,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>7.345827744171533</v>
+        <v>7.123226903439062</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4240,22 +4240,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.07695736717097866</v>
+        <v>0.07684629728983119</v>
       </c>
       <c r="C35">
-        <v>1491.492389457387</v>
+        <v>1471.856643090432</v>
       </c>
       <c r="D35">
-        <v>1192.225389457387</v>
+        <v>1196.490643090432</v>
       </c>
       <c r="E35">
-        <v>-668.0669999999999</v>
+        <v>-644.1659999999999</v>
       </c>
       <c r="F35">
-        <v>788.7330000000001</v>
+        <v>812.634</v>
       </c>
       <c r="G35">
         <v>1088</v>
@@ -4276,28 +4276,28 @@
         <v>305.075</v>
       </c>
       <c r="M35">
-        <v>42.8282019</v>
+        <v>44.1260262</v>
       </c>
       <c r="N35">
-        <v>262.2467981</v>
+        <v>260.9489738</v>
       </c>
       <c r="O35">
-        <v>57.694295582</v>
+        <v>57.40877423599999</v>
       </c>
       <c r="P35">
-        <v>204.552502518</v>
+        <v>203.540199564</v>
       </c>
       <c r="Q35">
-        <v>318.852502518</v>
+        <v>317.840199564</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.09400081667310249</v>
+        <v>0.09461505649974425</v>
       </c>
       <c r="T35">
-        <v>1.113182833097055</v>
+        <v>1.127368510386703</v>
       </c>
       <c r="U35">
         <v>0.0543</v>
@@ -4314,7 +4314,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>7.123226903439062</v>
+        <v>6.913720229808503</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4322,22 +4322,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.07684629728983119</v>
+        <v>0.07673522740868376</v>
       </c>
       <c r="C36">
-        <v>1471.856643090432</v>
+        <v>1452.251524667975</v>
       </c>
       <c r="D36">
-        <v>1196.490643090432</v>
+        <v>1200.786524667975</v>
       </c>
       <c r="E36">
-        <v>-644.1659999999999</v>
+        <v>-620.2649999999999</v>
       </c>
       <c r="F36">
-        <v>812.634</v>
+        <v>836.5350000000001</v>
       </c>
       <c r="G36">
         <v>1088</v>
@@ -4358,28 +4358,28 @@
         <v>305.075</v>
       </c>
       <c r="M36">
-        <v>44.1260262</v>
+        <v>45.42385050000001</v>
       </c>
       <c r="N36">
-        <v>260.9489738</v>
+        <v>259.6511495</v>
       </c>
       <c r="O36">
-        <v>57.40877423599999</v>
+        <v>57.12325289</v>
       </c>
       <c r="P36">
-        <v>203.540199564</v>
+        <v>202.52789661</v>
       </c>
       <c r="Q36">
-        <v>317.840199564</v>
+        <v>316.82789661</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.09461505649974425</v>
+        <v>0.09524819601335963</v>
       </c>
       <c r="T36">
-        <v>1.127368510386703</v>
+        <v>1.141990670054495</v>
       </c>
       <c r="U36">
         <v>0.0543</v>
@@ -4396,7 +4396,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>6.913720229808503</v>
+        <v>6.716185366099687</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4404,22 +4404,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.07673522740868376</v>
+        <v>0.07662415752753629</v>
       </c>
       <c r="C37">
-        <v>1452.251524667975</v>
+        <v>1432.677365278596</v>
       </c>
       <c r="D37">
-        <v>1200.786524667975</v>
+        <v>1205.113365278597</v>
       </c>
       <c r="E37">
-        <v>-620.2649999999999</v>
+        <v>-596.3639999999999</v>
       </c>
       <c r="F37">
-        <v>836.5350000000001</v>
+        <v>860.436</v>
       </c>
       <c r="G37">
         <v>1088</v>
@@ -4440,28 +4440,28 @@
         <v>305.075</v>
       </c>
       <c r="M37">
-        <v>45.42385050000001</v>
+        <v>46.7216748</v>
       </c>
       <c r="N37">
-        <v>259.6511495</v>
+        <v>258.3533252</v>
       </c>
       <c r="O37">
-        <v>57.12325289</v>
+        <v>56.83773154399999</v>
       </c>
       <c r="P37">
-        <v>202.52789661</v>
+        <v>201.515593656</v>
       </c>
       <c r="Q37">
-        <v>316.82789661</v>
+        <v>315.815593656</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.09524819601335963</v>
+        <v>0.09590112113677546</v>
       </c>
       <c r="T37">
-        <v>1.141990670054495</v>
+        <v>1.157069772211905</v>
       </c>
       <c r="U37">
         <v>0.0543</v>
@@ -4478,7 +4478,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>6.716185366099687</v>
+        <v>6.529624661485807</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4486,22 +4486,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.07662415752753629</v>
+        <v>0.07651308764638884</v>
       </c>
       <c r="C38">
-        <v>1432.677365278597</v>
+        <v>1413.134500800228</v>
       </c>
       <c r="D38">
-        <v>1205.113365278597</v>
+        <v>1209.471500800228</v>
       </c>
       <c r="E38">
-        <v>-596.364</v>
+        <v>-572.463</v>
       </c>
       <c r="F38">
-        <v>860.4359999999999</v>
+        <v>884.337</v>
       </c>
       <c r="G38">
         <v>1088</v>
@@ -4522,28 +4522,28 @@
         <v>305.075</v>
       </c>
       <c r="M38">
-        <v>46.7216748</v>
+        <v>48.0194991</v>
       </c>
       <c r="N38">
-        <v>258.3533252</v>
+        <v>257.0555009</v>
       </c>
       <c r="O38">
-        <v>56.83773154399999</v>
+        <v>56.55221019799999</v>
       </c>
       <c r="P38">
-        <v>201.515593656</v>
+        <v>200.503290702</v>
       </c>
       <c r="Q38">
-        <v>315.815593656</v>
+        <v>314.803290702</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.09590112113677546</v>
+        <v>0.09657477404188704</v>
       </c>
       <c r="T38">
-        <v>1.157069772211905</v>
+        <v>1.172627576025105</v>
       </c>
       <c r="U38">
         <v>0.0543</v>
@@ -4560,7 +4560,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>6.529624661485808</v>
+        <v>6.353148319283489</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4568,22 +4568,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.07651308764638884</v>
+        <v>0.07640201776524139</v>
       </c>
       <c r="C39">
-        <v>1413.134500800228</v>
+        <v>1393.623271987071</v>
       </c>
       <c r="D39">
-        <v>1209.471500800228</v>
+        <v>1213.861271987071</v>
       </c>
       <c r="E39">
-        <v>-572.463</v>
+        <v>-548.562</v>
       </c>
       <c r="F39">
-        <v>884.337</v>
+        <v>908.2379999999999</v>
       </c>
       <c r="G39">
         <v>1088</v>
@@ -4604,28 +4604,28 @@
         <v>305.075</v>
       </c>
       <c r="M39">
-        <v>48.0194991</v>
+        <v>49.3173234</v>
       </c>
       <c r="N39">
-        <v>257.0555009</v>
+        <v>255.7576766</v>
       </c>
       <c r="O39">
-        <v>56.55221019799999</v>
+        <v>56.266688852</v>
       </c>
       <c r="P39">
-        <v>200.503290702</v>
+        <v>199.490987748</v>
       </c>
       <c r="Q39">
-        <v>314.803290702</v>
+        <v>313.790987748</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.09657477404188704</v>
+        <v>0.09727015768587319</v>
       </c>
       <c r="T39">
-        <v>1.172627576025105</v>
+        <v>1.188687244477441</v>
       </c>
       <c r="U39">
         <v>0.0543</v>
@@ -4642,7 +4642,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>6.353148319283489</v>
+        <v>6.185960205618134</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4650,22 +4650,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.07640201776524139</v>
+        <v>0.07659514788409391</v>
       </c>
       <c r="C40">
-        <v>1393.623271987071</v>
+        <v>1362.109606101792</v>
       </c>
       <c r="D40">
-        <v>1213.861271987071</v>
+        <v>1206.248606101793</v>
       </c>
       <c r="E40">
-        <v>-548.562</v>
+        <v>-524.6609999999999</v>
       </c>
       <c r="F40">
-        <v>908.2379999999999</v>
+        <v>932.139</v>
       </c>
       <c r="G40">
         <v>1088</v>
@@ -4686,45 +4686,45 @@
         <v>305.075</v>
       </c>
       <c r="M40">
-        <v>49.3173234</v>
+        <v>51.5472867</v>
       </c>
       <c r="N40">
-        <v>255.7576766</v>
+        <v>253.5277133</v>
       </c>
       <c r="O40">
-        <v>56.266688852</v>
+        <v>55.776096926</v>
       </c>
       <c r="P40">
-        <v>199.490987748</v>
+        <v>197.751616374</v>
       </c>
       <c r="Q40">
-        <v>313.790987748</v>
+        <v>312.051616374</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.09727015768587319</v>
+        <v>0.09798834079359658</v>
       </c>
       <c r="T40">
-        <v>1.188687244477441</v>
+        <v>1.205273459436411</v>
       </c>
       <c r="U40">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V40">
         <v>0.22</v>
       </c>
       <c r="W40">
-        <v>0.042354</v>
+        <v>0.04313400000000001</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y40">
-        <v>6.185960205618134</v>
+        <v>5.918352245686677</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4732,22 +4732,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.07659514788409391</v>
+        <v>0.07649187800294646</v>
       </c>
       <c r="C41">
-        <v>1362.109606101792</v>
+        <v>1342.26730691425</v>
       </c>
       <c r="D41">
-        <v>1206.248606101793</v>
+        <v>1210.30730691425</v>
       </c>
       <c r="E41">
-        <v>-524.6609999999999</v>
+        <v>-500.76</v>
       </c>
       <c r="F41">
-        <v>932.139</v>
+        <v>956.04</v>
       </c>
       <c r="G41">
         <v>1088</v>
@@ -4768,28 +4768,28 @@
         <v>305.075</v>
       </c>
       <c r="M41">
-        <v>51.5472867</v>
+        <v>52.869012</v>
       </c>
       <c r="N41">
-        <v>253.5277133</v>
+        <v>252.205988</v>
       </c>
       <c r="O41">
-        <v>55.776096926</v>
+        <v>55.48531736</v>
       </c>
       <c r="P41">
-        <v>197.751616374</v>
+        <v>196.72067064</v>
       </c>
       <c r="Q41">
-        <v>312.051616374</v>
+        <v>311.02067064</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.09798834079359658</v>
+        <v>0.09873046333824409</v>
       </c>
       <c r="T41">
-        <v>1.205273459436411</v>
+        <v>1.222412548227346</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4806,7 +4806,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>5.918352245686677</v>
+        <v>5.77039343954451</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4814,22 +4814,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.07649187800294646</v>
+        <v>0.07638860812179901</v>
       </c>
       <c r="C42">
-        <v>1342.26730691425</v>
+        <v>1322.452412801751</v>
       </c>
       <c r="D42">
-        <v>1210.30730691425</v>
+        <v>1214.393412801751</v>
       </c>
       <c r="E42">
-        <v>-500.76</v>
+        <v>-476.8589999999999</v>
       </c>
       <c r="F42">
-        <v>956.04</v>
+        <v>979.941</v>
       </c>
       <c r="G42">
         <v>1088</v>
@@ -4850,28 +4850,28 @@
         <v>305.075</v>
       </c>
       <c r="M42">
-        <v>52.869012</v>
+        <v>54.1907373</v>
       </c>
       <c r="N42">
-        <v>252.205988</v>
+        <v>250.8842627</v>
       </c>
       <c r="O42">
-        <v>55.48531736</v>
+        <v>55.194537794</v>
       </c>
       <c r="P42">
-        <v>196.72067064</v>
+        <v>195.689724906</v>
       </c>
       <c r="Q42">
-        <v>311.02067064</v>
+        <v>309.989724906</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.09873046333824409</v>
+        <v>0.09949774257932034</v>
       </c>
       <c r="T42">
-        <v>1.222412548227346</v>
+        <v>1.240132623078992</v>
       </c>
       <c r="U42">
         <v>0.0553</v>
@@ -4888,7 +4888,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>5.77039343954451</v>
+        <v>5.629652136140986</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4896,22 +4896,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.07638860812179901</v>
+        <v>0.07628533824065153</v>
       </c>
       <c r="C43">
-        <v>1322.452412801751</v>
+        <v>1302.665202270522</v>
       </c>
       <c r="D43">
-        <v>1214.393412801751</v>
+        <v>1218.507202270522</v>
       </c>
       <c r="E43">
-        <v>-476.8589999999999</v>
+        <v>-452.9579999999999</v>
       </c>
       <c r="F43">
-        <v>979.941</v>
+        <v>1003.842</v>
       </c>
       <c r="G43">
         <v>1088</v>
@@ -4932,28 +4932,28 @@
         <v>305.075</v>
       </c>
       <c r="M43">
-        <v>54.1907373</v>
+        <v>55.51246260000001</v>
       </c>
       <c r="N43">
-        <v>250.8842627</v>
+        <v>249.5625374</v>
       </c>
       <c r="O43">
-        <v>55.194537794</v>
+        <v>54.903758228</v>
       </c>
       <c r="P43">
-        <v>195.689724906</v>
+        <v>194.658779172</v>
       </c>
       <c r="Q43">
-        <v>309.989724906</v>
+        <v>308.958779172</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.09949774257932034</v>
+        <v>0.1002914797252613</v>
       </c>
       <c r="T43">
-        <v>1.240132623078992</v>
+        <v>1.258463734994487</v>
       </c>
       <c r="U43">
         <v>0.0553</v>
@@ -4970,7 +4970,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>5.629652136140986</v>
+        <v>5.4956127995662</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4978,22 +4978,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.07628533824065155</v>
+        <v>0.07618206835950408</v>
       </c>
       <c r="C44">
-        <v>1302.665202270521</v>
+        <v>1282.905957613404</v>
       </c>
       <c r="D44">
-        <v>1218.507202270521</v>
+        <v>1222.648957613404</v>
       </c>
       <c r="E44">
-        <v>-452.9580000000001</v>
+        <v>-429.057</v>
       </c>
       <c r="F44">
-        <v>1003.842</v>
+        <v>1027.743</v>
       </c>
       <c r="G44">
         <v>1088</v>
@@ -5014,28 +5014,28 @@
         <v>305.075</v>
       </c>
       <c r="M44">
-        <v>55.51246259999999</v>
+        <v>56.8341879</v>
       </c>
       <c r="N44">
-        <v>249.5625374</v>
+        <v>248.2408121</v>
       </c>
       <c r="O44">
-        <v>54.903758228</v>
+        <v>54.612978662</v>
       </c>
       <c r="P44">
-        <v>194.658779172</v>
+        <v>193.627833438</v>
       </c>
       <c r="Q44">
-        <v>308.958779172</v>
+        <v>307.927833438</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1002914797252613</v>
+        <v>0.1011130672973756</v>
       </c>
       <c r="T44">
-        <v>1.258463734994487</v>
+        <v>1.277438043819298</v>
       </c>
       <c r="U44">
         <v>0.0553</v>
@@ -5052,7 +5052,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>5.495612799566201</v>
+        <v>5.36780785073908</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5060,22 +5060,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.07618206835950408</v>
+        <v>0.07607879847835664</v>
       </c>
       <c r="C45">
-        <v>1282.905957613404</v>
+        <v>1263.174964974431</v>
       </c>
       <c r="D45">
-        <v>1222.648957613404</v>
+        <v>1226.818964974431</v>
       </c>
       <c r="E45">
-        <v>-429.057</v>
+        <v>-405.1559999999999</v>
       </c>
       <c r="F45">
-        <v>1027.743</v>
+        <v>1051.644</v>
       </c>
       <c r="G45">
         <v>1088</v>
@@ -5096,28 +5096,28 @@
         <v>305.075</v>
       </c>
       <c r="M45">
-        <v>56.8341879</v>
+        <v>58.1559132</v>
       </c>
       <c r="N45">
-        <v>248.2408121</v>
+        <v>246.9190868</v>
       </c>
       <c r="O45">
-        <v>54.612978662</v>
+        <v>54.322199096</v>
       </c>
       <c r="P45">
-        <v>193.627833438</v>
+        <v>192.596887704</v>
       </c>
       <c r="Q45">
-        <v>307.927833438</v>
+        <v>306.8968877040001</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1011130672973756</v>
+        <v>0.1019639972827797</v>
       </c>
       <c r="T45">
-        <v>1.277438043819298</v>
+        <v>1.297090006530709</v>
       </c>
       <c r="U45">
         <v>0.0553</v>
@@ -5134,7 +5134,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>5.36780785073908</v>
+        <v>5.245812217767737</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5142,22 +5142,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.07607879847835664</v>
+        <v>0.07597552859720917</v>
       </c>
       <c r="C46">
-        <v>1263.174964974431</v>
+        <v>1243.472514414724</v>
       </c>
       <c r="D46">
-        <v>1226.818964974431</v>
+        <v>1231.017514414724</v>
       </c>
       <c r="E46">
-        <v>-405.1559999999999</v>
+        <v>-381.2549999999999</v>
       </c>
       <c r="F46">
-        <v>1051.644</v>
+        <v>1075.545</v>
       </c>
       <c r="G46">
         <v>1088</v>
@@ -5178,28 +5178,28 @@
         <v>305.075</v>
       </c>
       <c r="M46">
-        <v>58.1559132</v>
+        <v>59.4776385</v>
       </c>
       <c r="N46">
-        <v>246.9190868</v>
+        <v>245.5973615</v>
       </c>
       <c r="O46">
-        <v>54.322199096</v>
+        <v>54.03141952999999</v>
       </c>
       <c r="P46">
-        <v>192.596887704</v>
+        <v>191.56594197</v>
       </c>
       <c r="Q46">
-        <v>306.8968877040001</v>
+        <v>305.86594197</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1019639972827797</v>
+        <v>0.1028458701767439</v>
       </c>
       <c r="T46">
-        <v>1.297090006530709</v>
+        <v>1.317456586067989</v>
       </c>
       <c r="U46">
         <v>0.0553</v>
@@ -5216,7 +5216,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>5.245812217767737</v>
+        <v>5.129238612928453</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5224,22 +5224,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.07597552859720917</v>
+        <v>0.07587225871606171</v>
       </c>
       <c r="C47">
-        <v>1243.472514414724</v>
+        <v>1223.798899979751</v>
       </c>
       <c r="D47">
-        <v>1231.017514414724</v>
+        <v>1235.244899979751</v>
       </c>
       <c r="E47">
-        <v>-381.2549999999999</v>
+        <v>-357.354</v>
       </c>
       <c r="F47">
-        <v>1075.545</v>
+        <v>1099.446</v>
       </c>
       <c r="G47">
         <v>1088</v>
@@ -5260,28 +5260,28 @@
         <v>305.075</v>
       </c>
       <c r="M47">
-        <v>59.4776385</v>
+        <v>60.79936379999999</v>
       </c>
       <c r="N47">
-        <v>245.5973615</v>
+        <v>244.2756362</v>
       </c>
       <c r="O47">
-        <v>54.03141952999999</v>
+        <v>53.740639964</v>
       </c>
       <c r="P47">
-        <v>191.56594197</v>
+        <v>190.534996236</v>
       </c>
       <c r="Q47">
-        <v>305.86594197</v>
+        <v>304.8349962360001</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1028458701767439</v>
+        <v>0.1037604050297439</v>
       </c>
       <c r="T47">
-        <v>1.317456586067989</v>
+        <v>1.33857748336591</v>
       </c>
       <c r="U47">
         <v>0.0553</v>
@@ -5298,7 +5298,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>5.129238612928453</v>
+        <v>5.017733425690879</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5306,22 +5306,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.07587225871606171</v>
+        <v>0.07576898883491426</v>
       </c>
       <c r="C48">
-        <v>1223.798899979751</v>
+        <v>1204.154419767976</v>
       </c>
       <c r="D48">
-        <v>1235.244899979751</v>
+        <v>1239.501419767976</v>
       </c>
       <c r="E48">
-        <v>-357.354</v>
+        <v>-333.453</v>
       </c>
       <c r="F48">
-        <v>1099.446</v>
+        <v>1123.347</v>
       </c>
       <c r="G48">
         <v>1088</v>
@@ -5342,28 +5342,28 @@
         <v>305.075</v>
       </c>
       <c r="M48">
-        <v>60.79936379999999</v>
+        <v>62.1210891</v>
       </c>
       <c r="N48">
-        <v>244.2756362</v>
+        <v>242.9539109</v>
       </c>
       <c r="O48">
-        <v>53.740639964</v>
+        <v>53.449860398</v>
       </c>
       <c r="P48">
-        <v>190.534996236</v>
+        <v>189.504050502</v>
       </c>
       <c r="Q48">
-        <v>304.8349962360001</v>
+        <v>303.804050502</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1037604050297439</v>
+        <v>0.1047094506319137</v>
       </c>
       <c r="T48">
-        <v>1.33857748336591</v>
+        <v>1.360495395656205</v>
       </c>
       <c r="U48">
         <v>0.0553</v>
@@ -5380,7 +5380,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>5.017733425690879</v>
+        <v>4.910973140037881</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5388,22 +5388,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.07576898883491426</v>
+        <v>0.07566571895376679</v>
       </c>
       <c r="C49">
-        <v>1204.154419767976</v>
+        <v>1184.53937600093</v>
       </c>
       <c r="D49">
-        <v>1239.501419767976</v>
+        <v>1243.78737600093</v>
       </c>
       <c r="E49">
-        <v>-333.453</v>
+        <v>-309.5519999999999</v>
       </c>
       <c r="F49">
-        <v>1123.347</v>
+        <v>1147.248</v>
       </c>
       <c r="G49">
         <v>1088</v>
@@ -5424,28 +5424,28 @@
         <v>305.075</v>
       </c>
       <c r="M49">
-        <v>62.1210891</v>
+        <v>63.4428144</v>
       </c>
       <c r="N49">
-        <v>242.9539109</v>
+        <v>241.6321856</v>
       </c>
       <c r="O49">
-        <v>53.449860398</v>
+        <v>53.15908083199999</v>
       </c>
       <c r="P49">
-        <v>189.504050502</v>
+        <v>188.473104768</v>
       </c>
       <c r="Q49">
-        <v>303.804050502</v>
+        <v>302.773104768</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1047094506319137</v>
+        <v>0.1056949979880131</v>
       </c>
       <c r="T49">
-        <v>1.360495395656205</v>
+        <v>1.38325630457305</v>
       </c>
       <c r="U49">
         <v>0.0553</v>
@@ -5462,7 +5462,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>4.910973140037881</v>
+        <v>4.808661199620425</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5470,22 +5470,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.07566571895376678</v>
+        <v>0.07556244907261933</v>
       </c>
       <c r="C50">
-        <v>1184.539376000931</v>
+        <v>1164.954075094742</v>
       </c>
       <c r="D50">
-        <v>1243.787376000931</v>
+        <v>1248.103075094742</v>
       </c>
       <c r="E50">
-        <v>-309.5520000000001</v>
+        <v>-285.6510000000001</v>
       </c>
       <c r="F50">
-        <v>1147.248</v>
+        <v>1171.149</v>
       </c>
       <c r="G50">
         <v>1088</v>
@@ -5506,28 +5506,28 @@
         <v>305.075</v>
       </c>
       <c r="M50">
-        <v>63.44281439999999</v>
+        <v>64.7645397</v>
       </c>
       <c r="N50">
-        <v>241.6321856</v>
+        <v>240.3104603</v>
       </c>
       <c r="O50">
-        <v>53.159080832</v>
+        <v>52.868301266</v>
       </c>
       <c r="P50">
-        <v>188.473104768</v>
+        <v>187.442159034</v>
       </c>
       <c r="Q50">
-        <v>302.7731047680001</v>
+        <v>301.742159034</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.105694997988013</v>
+        <v>0.1067191942600379</v>
       </c>
       <c r="T50">
-        <v>1.38325630457305</v>
+        <v>1.406909798153301</v>
       </c>
       <c r="U50">
         <v>0.0553</v>
@@ -5544,7 +5544,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>4.808661199620426</v>
+        <v>4.710525256771029</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5552,22 +5552,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.07556244907261933</v>
+        <v>0.07545917919147188</v>
       </c>
       <c r="C51">
-        <v>1164.954075094742</v>
+        <v>1145.398827733166</v>
       </c>
       <c r="D51">
-        <v>1248.103075094742</v>
+        <v>1252.448827733165</v>
       </c>
       <c r="E51">
-        <v>-285.6510000000001</v>
+        <v>-261.75</v>
       </c>
       <c r="F51">
-        <v>1171.149</v>
+        <v>1195.05</v>
       </c>
       <c r="G51">
         <v>1088</v>
@@ -5588,28 +5588,28 @@
         <v>305.075</v>
       </c>
       <c r="M51">
-        <v>64.7645397</v>
+        <v>66.086265</v>
       </c>
       <c r="N51">
-        <v>240.3104603</v>
+        <v>238.988735</v>
       </c>
       <c r="O51">
-        <v>52.868301266</v>
+        <v>52.5775217</v>
       </c>
       <c r="P51">
-        <v>187.442159034</v>
+        <v>186.4112133</v>
       </c>
       <c r="Q51">
-        <v>301.742159034</v>
+        <v>300.7112133</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1067191942600379</v>
+        <v>0.1077843583829437</v>
       </c>
       <c r="T51">
-        <v>1.406909798153301</v>
+        <v>1.431509431476761</v>
       </c>
       <c r="U51">
         <v>0.0553</v>
@@ -5626,7 +5626,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>4.710525256771029</v>
+        <v>4.616314751635608</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5634,22 +5634,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.07545917919147188</v>
+        <v>0.0753559093103244</v>
       </c>
       <c r="C52">
-        <v>1145.398827733166</v>
+        <v>1125.873948942135</v>
       </c>
       <c r="D52">
-        <v>1252.448827733165</v>
+        <v>1256.824948942135</v>
       </c>
       <c r="E52">
-        <v>-261.75</v>
+        <v>-237.8489999999999</v>
       </c>
       <c r="F52">
-        <v>1195.05</v>
+        <v>1218.951</v>
       </c>
       <c r="G52">
         <v>1088</v>
@@ -5670,28 +5670,28 @@
         <v>305.075</v>
       </c>
       <c r="M52">
-        <v>66.086265</v>
+        <v>67.40799030000001</v>
       </c>
       <c r="N52">
-        <v>238.988735</v>
+        <v>237.6670097</v>
       </c>
       <c r="O52">
-        <v>52.5775217</v>
+        <v>52.286742134</v>
       </c>
       <c r="P52">
-        <v>186.4112133</v>
+        <v>185.380267566</v>
       </c>
       <c r="Q52">
-        <v>300.7112133</v>
+        <v>299.680267566</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1077843583829437</v>
+        <v>0.1088929985924988</v>
       </c>
       <c r="T52">
-        <v>1.431509431476761</v>
+        <v>1.457113131466485</v>
       </c>
       <c r="U52">
         <v>0.0553</v>
@@ -5708,7 +5708,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>4.616314751635608</v>
+        <v>4.525798776113341</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5716,22 +5716,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.0753559093103244</v>
+        <v>0.07626663942917696</v>
       </c>
       <c r="C53">
-        <v>1125.873948942135</v>
+        <v>1064.403057527372</v>
       </c>
       <c r="D53">
-        <v>1256.824948942135</v>
+        <v>1219.255057527372</v>
       </c>
       <c r="E53">
-        <v>-237.8489999999999</v>
+        <v>-213.9479999999999</v>
       </c>
       <c r="F53">
-        <v>1218.951</v>
+        <v>1242.852</v>
       </c>
       <c r="G53">
         <v>1088</v>
@@ -5752,45 +5752,45 @@
         <v>305.075</v>
       </c>
       <c r="M53">
-        <v>67.40799030000001</v>
+        <v>71.8368456</v>
       </c>
       <c r="N53">
-        <v>237.6670097</v>
+        <v>233.2381544</v>
       </c>
       <c r="O53">
-        <v>52.286742134</v>
+        <v>51.31239396799999</v>
       </c>
       <c r="P53">
-        <v>185.380267566</v>
+        <v>181.925760432</v>
       </c>
       <c r="Q53">
-        <v>299.680267566</v>
+        <v>296.225760432</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1088929985924988</v>
+        <v>0.1100478321441186</v>
       </c>
       <c r="T53">
-        <v>1.457113131466485</v>
+        <v>1.483783652289115</v>
       </c>
       <c r="U53">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V53">
         <v>0.22</v>
       </c>
       <c r="W53">
-        <v>0.04313400000000001</v>
+        <v>0.04508400000000001</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y53">
-        <v>4.525798776113341</v>
+        <v>4.246776114011331</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5798,22 +5798,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.07626663942917696</v>
+        <v>0.0761828695480295</v>
       </c>
       <c r="C54">
-        <v>1064.403057527372</v>
+        <v>1043.863716672044</v>
       </c>
       <c r="D54">
-        <v>1219.255057527372</v>
+        <v>1222.616716672044</v>
       </c>
       <c r="E54">
-        <v>-213.9479999999999</v>
+        <v>-190.047</v>
       </c>
       <c r="F54">
-        <v>1242.852</v>
+        <v>1266.753</v>
       </c>
       <c r="G54">
         <v>1088</v>
@@ -5834,28 +5834,28 @@
         <v>305.075</v>
       </c>
       <c r="M54">
-        <v>71.8368456</v>
+        <v>73.2183234</v>
       </c>
       <c r="N54">
-        <v>233.2381544</v>
+        <v>231.8566766</v>
       </c>
       <c r="O54">
-        <v>51.31239396799999</v>
+        <v>51.008468852</v>
       </c>
       <c r="P54">
-        <v>181.925760432</v>
+        <v>180.848207748</v>
       </c>
       <c r="Q54">
-        <v>296.225760432</v>
+        <v>295.148207748</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1100478321441186</v>
+        <v>0.1112518075489989</v>
       </c>
       <c r="T54">
-        <v>1.483783652289115</v>
+        <v>1.511589088891431</v>
       </c>
       <c r="U54">
         <v>0.0578</v>
@@ -5872,7 +5872,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>4.246776114011331</v>
+        <v>4.166648262803569</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5880,22 +5880,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.0761828695480295</v>
+        <v>0.07609909966688204</v>
       </c>
       <c r="C55">
-        <v>1043.863716672044</v>
+        <v>1023.342964209777</v>
       </c>
       <c r="D55">
-        <v>1222.616716672044</v>
+        <v>1225.996964209777</v>
       </c>
       <c r="E55">
-        <v>-190.047</v>
+        <v>-166.146</v>
       </c>
       <c r="F55">
-        <v>1266.753</v>
+        <v>1290.654</v>
       </c>
       <c r="G55">
         <v>1088</v>
@@ -5916,28 +5916,28 @@
         <v>305.075</v>
       </c>
       <c r="M55">
-        <v>73.2183234</v>
+        <v>74.5998012</v>
       </c>
       <c r="N55">
-        <v>231.8566766</v>
+        <v>230.4751988</v>
       </c>
       <c r="O55">
-        <v>51.008468852</v>
+        <v>50.704543736</v>
       </c>
       <c r="P55">
-        <v>180.848207748</v>
+        <v>179.770655064</v>
       </c>
       <c r="Q55">
-        <v>295.148207748</v>
+        <v>294.070655064</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1112518075489989</v>
+        <v>0.1125081297106131</v>
       </c>
       <c r="T55">
-        <v>1.511589088891431</v>
+        <v>1.540603457519934</v>
       </c>
       <c r="U55">
         <v>0.0578</v>
@@ -5954,7 +5954,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>4.166648262803569</v>
+        <v>4.089488109788689</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5962,22 +5962,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.07609909966688204</v>
+        <v>0.07601532978573458</v>
       </c>
       <c r="C56">
-        <v>1023.342964209777</v>
+        <v>1002.840954745617</v>
       </c>
       <c r="D56">
-        <v>1225.996964209777</v>
+        <v>1229.395954745617</v>
       </c>
       <c r="E56">
-        <v>-166.146</v>
+        <v>-142.2449999999999</v>
       </c>
       <c r="F56">
-        <v>1290.654</v>
+        <v>1314.555</v>
       </c>
       <c r="G56">
         <v>1088</v>
@@ -5998,28 +5998,28 @@
         <v>305.075</v>
       </c>
       <c r="M56">
-        <v>74.5998012</v>
+        <v>75.98127900000001</v>
       </c>
       <c r="N56">
-        <v>230.4751988</v>
+        <v>229.093721</v>
       </c>
       <c r="O56">
-        <v>50.704543736</v>
+        <v>50.40061861999999</v>
       </c>
       <c r="P56">
-        <v>179.770655064</v>
+        <v>178.69310238</v>
       </c>
       <c r="Q56">
-        <v>294.070655064</v>
+        <v>292.99310238</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1125081297106131</v>
+        <v>0.1138202884127435</v>
       </c>
       <c r="T56">
-        <v>1.540603457519934</v>
+        <v>1.570907353643038</v>
       </c>
       <c r="U56">
         <v>0.0578</v>
@@ -6036,7 +6036,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>4.089488109788689</v>
+        <v>4.015133780519803</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6044,22 +6044,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.07601532978573458</v>
+        <v>0.07746035990458711</v>
       </c>
       <c r="C57">
-        <v>1002.840954745617</v>
+        <v>922.8283316321513</v>
       </c>
       <c r="D57">
-        <v>1229.395954745617</v>
+        <v>1173.284331632151</v>
       </c>
       <c r="E57">
-        <v>-142.2449999999999</v>
+        <v>-118.3439999999998</v>
       </c>
       <c r="F57">
-        <v>1314.555</v>
+        <v>1338.456</v>
       </c>
       <c r="G57">
         <v>1088</v>
@@ -6080,45 +6080,45 @@
         <v>305.075</v>
       </c>
       <c r="M57">
-        <v>75.98127900000001</v>
+        <v>82.04735280000001</v>
       </c>
       <c r="N57">
-        <v>229.093721</v>
+        <v>223.0276472</v>
       </c>
       <c r="O57">
-        <v>50.40061861999999</v>
+        <v>49.066082384</v>
       </c>
       <c r="P57">
-        <v>178.69310238</v>
+        <v>173.961564816</v>
       </c>
       <c r="Q57">
-        <v>292.99310238</v>
+        <v>288.261564816</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1138202884127435</v>
+        <v>0.1151920906922435</v>
       </c>
       <c r="T57">
-        <v>1.570907353643038</v>
+        <v>1.602588699589919</v>
       </c>
       <c r="U57">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V57">
         <v>0.22</v>
       </c>
       <c r="W57">
-        <v>0.04508400000000001</v>
+        <v>0.047814</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y57">
-        <v>4.015133780519803</v>
+        <v>3.718279622544994</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6126,22 +6126,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.07746035990458711</v>
+        <v>0.07740389002343966</v>
       </c>
       <c r="C58">
-        <v>922.8283316321513</v>
+        <v>901.0237579489842</v>
       </c>
       <c r="D58">
-        <v>1173.284331632151</v>
+        <v>1175.380757948984</v>
       </c>
       <c r="E58">
-        <v>-118.3439999999998</v>
+        <v>-94.44299999999976</v>
       </c>
       <c r="F58">
-        <v>1338.456</v>
+        <v>1362.357</v>
       </c>
       <c r="G58">
         <v>1088</v>
@@ -6162,28 +6162,28 @@
         <v>305.075</v>
       </c>
       <c r="M58">
-        <v>82.04735280000001</v>
+        <v>83.51248410000001</v>
       </c>
       <c r="N58">
-        <v>223.0276472</v>
+        <v>221.5625159</v>
       </c>
       <c r="O58">
-        <v>49.066082384</v>
+        <v>48.743753498</v>
       </c>
       <c r="P58">
-        <v>173.961564816</v>
+        <v>172.818762402</v>
       </c>
       <c r="Q58">
-        <v>288.261564816</v>
+        <v>287.118762402</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1151920906922435</v>
+        <v>0.1166276977289294</v>
       </c>
       <c r="T58">
-        <v>1.602588699589919</v>
+        <v>1.635743596511073</v>
       </c>
       <c r="U58">
         <v>0.0613</v>
@@ -6200,7 +6200,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>3.718279622544994</v>
+        <v>3.653046646710871</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6208,22 +6208,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.07740389002343966</v>
+        <v>0.07734742014229221</v>
       </c>
       <c r="C59">
-        <v>901.0237579489842</v>
+        <v>879.2266894719112</v>
       </c>
       <c r="D59">
-        <v>1175.380757948984</v>
+        <v>1177.484689471911</v>
       </c>
       <c r="E59">
-        <v>-94.44299999999976</v>
+        <v>-70.54199999999992</v>
       </c>
       <c r="F59">
-        <v>1362.357</v>
+        <v>1386.258</v>
       </c>
       <c r="G59">
         <v>1088</v>
@@ -6244,28 +6244,28 @@
         <v>305.075</v>
       </c>
       <c r="M59">
-        <v>83.51248410000001</v>
+        <v>84.9776154</v>
       </c>
       <c r="N59">
-        <v>221.5625159</v>
+        <v>220.0973846</v>
       </c>
       <c r="O59">
-        <v>48.743753498</v>
+        <v>48.421424612</v>
       </c>
       <c r="P59">
-        <v>172.818762402</v>
+        <v>171.675959988</v>
       </c>
       <c r="Q59">
-        <v>287.118762402</v>
+        <v>285.975959988</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1166276977289294</v>
+        <v>0.1181316670054576</v>
       </c>
       <c r="T59">
-        <v>1.635743596511073</v>
+        <v>1.670477298047521</v>
       </c>
       <c r="U59">
         <v>0.0613</v>
@@ -6282,7 +6282,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>3.653046646710871</v>
+        <v>3.590063083836546</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6290,22 +6290,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.07734742014229221</v>
+        <v>0.07729095026114474</v>
       </c>
       <c r="C60">
-        <v>879.2266894719114</v>
+        <v>857.4371665761598</v>
       </c>
       <c r="D60">
-        <v>1177.484689471911</v>
+        <v>1179.596166576159</v>
       </c>
       <c r="E60">
-        <v>-70.54200000000014</v>
+        <v>-46.64100000000008</v>
       </c>
       <c r="F60">
-        <v>1386.258</v>
+        <v>1410.159</v>
       </c>
       <c r="G60">
         <v>1088</v>
@@ -6326,28 +6326,28 @@
         <v>305.075</v>
       </c>
       <c r="M60">
-        <v>84.97761539999999</v>
+        <v>86.44274669999999</v>
       </c>
       <c r="N60">
-        <v>220.0973846</v>
+        <v>218.6322533</v>
       </c>
       <c r="O60">
-        <v>48.421424612</v>
+        <v>48.099095726</v>
       </c>
       <c r="P60">
-        <v>171.675959988</v>
+        <v>170.533157574</v>
       </c>
       <c r="Q60">
-        <v>285.975959988</v>
+        <v>284.833157574</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1181316670054576</v>
+        <v>0.1197090006369384</v>
       </c>
       <c r="T60">
-        <v>1.67047729804752</v>
+        <v>1.706905326488185</v>
       </c>
       <c r="U60">
         <v>0.0613</v>
@@ -6364,7 +6364,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>3.590063083836547</v>
+        <v>3.52921455699186</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6372,22 +6372,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.07729095026114474</v>
+        <v>0.07854488037999728</v>
       </c>
       <c r="C61">
-        <v>857.4371665761598</v>
+        <v>788.3647949239244</v>
       </c>
       <c r="D61">
-        <v>1179.596166576159</v>
+        <v>1134.424794923924</v>
       </c>
       <c r="E61">
-        <v>-46.64100000000008</v>
+        <v>-22.74000000000001</v>
       </c>
       <c r="F61">
-        <v>1410.159</v>
+        <v>1434.06</v>
       </c>
       <c r="G61">
         <v>1088</v>
@@ -6408,45 +6408,45 @@
         <v>305.075</v>
       </c>
       <c r="M61">
-        <v>86.44274669999999</v>
+        <v>91.92324600000001</v>
       </c>
       <c r="N61">
-        <v>218.6322533</v>
+        <v>213.151754</v>
       </c>
       <c r="O61">
-        <v>48.099095726</v>
+        <v>46.89338588</v>
       </c>
       <c r="P61">
-        <v>170.533157574</v>
+        <v>166.25836812</v>
       </c>
       <c r="Q61">
-        <v>284.833157574</v>
+        <v>280.55836812</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1197090006369384</v>
+        <v>0.1213652009499932</v>
       </c>
       <c r="T61">
-        <v>1.706905326488185</v>
+        <v>1.745154756350883</v>
       </c>
       <c r="U61">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V61">
         <v>0.22</v>
       </c>
       <c r="W61">
-        <v>0.047814</v>
+        <v>0.04999800000000001</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y61">
-        <v>3.52921455699186</v>
+        <v>3.318801427007919</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6454,22 +6454,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.07854488037999728</v>
+        <v>0.07851025049884983</v>
       </c>
       <c r="C62">
-        <v>788.3647949239244</v>
+        <v>765.6647944644299</v>
       </c>
       <c r="D62">
-        <v>1134.424794923924</v>
+        <v>1135.62579446443</v>
       </c>
       <c r="E62">
-        <v>-22.74000000000001</v>
+        <v>1.161000000000058</v>
       </c>
       <c r="F62">
-        <v>1434.06</v>
+        <v>1457.961</v>
       </c>
       <c r="G62">
         <v>1088</v>
@@ -6490,28 +6490,28 @@
         <v>305.075</v>
       </c>
       <c r="M62">
-        <v>91.92324600000001</v>
+        <v>93.4553001</v>
       </c>
       <c r="N62">
-        <v>213.151754</v>
+        <v>211.6196999</v>
       </c>
       <c r="O62">
-        <v>46.89338588</v>
+        <v>46.556333978</v>
       </c>
       <c r="P62">
-        <v>166.25836812</v>
+        <v>165.063365922</v>
       </c>
       <c r="Q62">
-        <v>280.55836812</v>
+        <v>279.363365922</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1213652009499932</v>
+        <v>0.1231063346124354</v>
       </c>
       <c r="T62">
-        <v>1.745154756350883</v>
+        <v>1.785365695437308</v>
       </c>
       <c r="U62">
         <v>0.0641</v>
@@ -6528,7 +6528,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>3.318801427007919</v>
+        <v>3.264394846237297</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6536,22 +6536,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.07851025049884983</v>
+        <v>0.07847562061770237</v>
       </c>
       <c r="C63">
-        <v>765.6647944644299</v>
+        <v>742.9673396625578</v>
       </c>
       <c r="D63">
-        <v>1135.62579446443</v>
+        <v>1136.829339662558</v>
       </c>
       <c r="E63">
-        <v>1.161000000000058</v>
+        <v>25.0619999999999</v>
       </c>
       <c r="F63">
-        <v>1457.961</v>
+        <v>1481.862</v>
       </c>
       <c r="G63">
         <v>1088</v>
@@ -6572,28 +6572,28 @@
         <v>305.075</v>
       </c>
       <c r="M63">
-        <v>93.4553001</v>
+        <v>94.9873542</v>
       </c>
       <c r="N63">
-        <v>211.6196999</v>
+        <v>210.0876458</v>
       </c>
       <c r="O63">
-        <v>46.556333978</v>
+        <v>46.219282076</v>
       </c>
       <c r="P63">
-        <v>165.063365922</v>
+        <v>163.868363724</v>
       </c>
       <c r="Q63">
-        <v>279.363365922</v>
+        <v>278.168363724</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1231063346124354</v>
+        <v>0.1249391068886904</v>
       </c>
       <c r="T63">
-        <v>1.785365695437308</v>
+        <v>1.82769299973881</v>
       </c>
       <c r="U63">
         <v>0.0641</v>
@@ -6610,7 +6610,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>3.264394846237297</v>
+        <v>3.211743316459276</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6618,22 +6618,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.07847562061770237</v>
+        <v>0.07844099073655492</v>
       </c>
       <c r="C64">
-        <v>742.9673396625578</v>
+        <v>720.2724386206196</v>
       </c>
       <c r="D64">
-        <v>1136.829339662558</v>
+        <v>1138.03543862062</v>
       </c>
       <c r="E64">
-        <v>25.0619999999999</v>
+        <v>48.96299999999997</v>
       </c>
       <c r="F64">
-        <v>1481.862</v>
+        <v>1505.763</v>
       </c>
       <c r="G64">
         <v>1088</v>
@@ -6654,28 +6654,28 @@
         <v>305.075</v>
       </c>
       <c r="M64">
-        <v>94.9873542</v>
+        <v>96.51940829999999</v>
       </c>
       <c r="N64">
-        <v>210.0876458</v>
+        <v>208.5555917</v>
       </c>
       <c r="O64">
-        <v>46.219282076</v>
+        <v>45.88223017399999</v>
       </c>
       <c r="P64">
-        <v>163.868363724</v>
+        <v>162.673361526</v>
       </c>
       <c r="Q64">
-        <v>278.168363724</v>
+        <v>276.973361526</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1249391068886904</v>
+        <v>0.1268709479366349</v>
       </c>
       <c r="T64">
-        <v>1.82769299973881</v>
+        <v>1.872308266434986</v>
       </c>
       <c r="U64">
         <v>0.0641</v>
@@ -6692,7 +6692,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>3.211743316459276</v>
+        <v>3.160763263817066</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6700,22 +6700,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.07844099073655492</v>
+        <v>0.07840636085540746</v>
       </c>
       <c r="C65">
-        <v>720.2724386206196</v>
+        <v>697.5800994753461</v>
       </c>
       <c r="D65">
-        <v>1138.03543862062</v>
+        <v>1139.244099475346</v>
       </c>
       <c r="E65">
-        <v>48.96299999999997</v>
+        <v>72.86400000000003</v>
       </c>
       <c r="F65">
-        <v>1505.763</v>
+        <v>1529.664</v>
       </c>
       <c r="G65">
         <v>1088</v>
@@ -6736,28 +6736,28 @@
         <v>305.075</v>
       </c>
       <c r="M65">
-        <v>96.51940829999999</v>
+        <v>98.05146240000001</v>
       </c>
       <c r="N65">
-        <v>208.5555917</v>
+        <v>207.0235376</v>
       </c>
       <c r="O65">
-        <v>45.88223017399999</v>
+        <v>45.545178272</v>
       </c>
       <c r="P65">
-        <v>162.673361526</v>
+        <v>161.478359328</v>
       </c>
       <c r="Q65">
-        <v>276.973361526</v>
+        <v>275.778359328</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1268709479366349</v>
+        <v>0.1289101134872429</v>
       </c>
       <c r="T65">
-        <v>1.872308266434986</v>
+        <v>1.919402159058728</v>
       </c>
       <c r="U65">
         <v>0.0641</v>
@@ -6774,7 +6774,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>3.160763263817066</v>
+        <v>3.111376337819924</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6782,22 +6782,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.07840636085540746</v>
+        <v>0.07837173097426001</v>
       </c>
       <c r="C66">
-        <v>697.5800994753461</v>
+        <v>674.8903303980728</v>
       </c>
       <c r="D66">
-        <v>1139.244099475346</v>
+        <v>1140.455330398073</v>
       </c>
       <c r="E66">
-        <v>72.86400000000003</v>
+        <v>96.7650000000001</v>
       </c>
       <c r="F66">
-        <v>1529.664</v>
+        <v>1553.565</v>
       </c>
       <c r="G66">
         <v>1088</v>
@@ -6818,28 +6818,28 @@
         <v>305.075</v>
       </c>
       <c r="M66">
-        <v>98.05146240000001</v>
+        <v>99.58351650000002</v>
       </c>
       <c r="N66">
-        <v>207.0235376</v>
+        <v>205.4914835</v>
       </c>
       <c r="O66">
-        <v>45.545178272</v>
+        <v>45.20812636999999</v>
       </c>
       <c r="P66">
-        <v>161.478359328</v>
+        <v>160.28335713</v>
       </c>
       <c r="Q66">
-        <v>275.778359328</v>
+        <v>274.58335713</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1289101134872429</v>
+        <v>0.1310658027836</v>
       </c>
       <c r="T66">
-        <v>1.919402159058728</v>
+        <v>1.96918713126097</v>
       </c>
       <c r="U66">
         <v>0.0641</v>
@@ -6856,7 +6856,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>3.111376337819924</v>
+        <v>3.063509009545771</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6864,22 +6864,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.07837173097426001</v>
+        <v>0.07833710109311254</v>
       </c>
       <c r="C67">
-        <v>674.8903303980728</v>
+        <v>652.2031395949236</v>
       </c>
       <c r="D67">
-        <v>1140.455330398073</v>
+        <v>1141.669139594924</v>
       </c>
       <c r="E67">
-        <v>96.7650000000001</v>
+        <v>120.6660000000002</v>
       </c>
       <c r="F67">
-        <v>1553.565</v>
+        <v>1577.466</v>
       </c>
       <c r="G67">
         <v>1088</v>
@@ -6900,28 +6900,28 @@
         <v>305.075</v>
       </c>
       <c r="M67">
-        <v>99.58351650000002</v>
+        <v>101.1155706</v>
       </c>
       <c r="N67">
-        <v>205.4914835</v>
+        <v>203.9594294</v>
       </c>
       <c r="O67">
-        <v>45.20812636999999</v>
+        <v>44.871074468</v>
       </c>
       <c r="P67">
-        <v>160.28335713</v>
+        <v>159.088354932</v>
       </c>
       <c r="Q67">
-        <v>274.58335713</v>
+        <v>273.388354932</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1310658027836</v>
+        <v>0.1333482973326839</v>
       </c>
       <c r="T67">
-        <v>1.96918713126097</v>
+        <v>2.021900631239814</v>
       </c>
       <c r="U67">
         <v>0.0641</v>
@@ -6938,7 +6938,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>3.063509009545771</v>
+        <v>3.017092206370835</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6946,22 +6946,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.07833710109311254</v>
+        <v>0.08237875121196508</v>
       </c>
       <c r="C68">
-        <v>652.2031395949236</v>
+        <v>502.1571220409958</v>
       </c>
       <c r="D68">
-        <v>1141.669139594924</v>
+        <v>1015.524122040996</v>
       </c>
       <c r="E68">
-        <v>120.6660000000002</v>
+        <v>144.567</v>
       </c>
       <c r="F68">
-        <v>1577.466</v>
+        <v>1601.367</v>
       </c>
       <c r="G68">
         <v>1088</v>
@@ -6982,45 +6982,45 @@
         <v>305.075</v>
       </c>
       <c r="M68">
-        <v>101.1155706</v>
+        <v>115.1382873</v>
       </c>
       <c r="N68">
-        <v>203.9594294</v>
+        <v>189.9367127</v>
       </c>
       <c r="O68">
-        <v>44.871074468</v>
+        <v>41.786076794</v>
       </c>
       <c r="P68">
-        <v>159.088354932</v>
+        <v>148.150635906</v>
       </c>
       <c r="Q68">
-        <v>273.388354932</v>
+        <v>262.450635906</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1333482973326839</v>
+        <v>0.1357691248847427</v>
       </c>
       <c r="T68">
-        <v>2.021900631239814</v>
+        <v>2.077808888793133</v>
       </c>
       <c r="U68">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V68">
         <v>0.22</v>
       </c>
       <c r="W68">
-        <v>0.04999800000000001</v>
+        <v>0.05608200000000001</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y68">
-        <v>3.017092206370835</v>
+        <v>2.64963989958534</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7028,22 +7028,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.08237875121196508</v>
+        <v>0.08240496133081762</v>
       </c>
       <c r="C69">
-        <v>502.1571220409958</v>
+        <v>477.5289799550974</v>
       </c>
       <c r="D69">
-        <v>1015.524122040996</v>
+        <v>1014.796979955097</v>
       </c>
       <c r="E69">
-        <v>144.567</v>
+        <v>168.4680000000001</v>
       </c>
       <c r="F69">
-        <v>1601.367</v>
+        <v>1625.268</v>
       </c>
       <c r="G69">
         <v>1088</v>
@@ -7064,28 +7064,28 @@
         <v>305.075</v>
       </c>
       <c r="M69">
-        <v>115.1382873</v>
+        <v>116.8567692</v>
       </c>
       <c r="N69">
-        <v>189.9367127</v>
+        <v>188.2182308</v>
       </c>
       <c r="O69">
-        <v>41.786076794</v>
+        <v>41.40801077599999</v>
       </c>
       <c r="P69">
-        <v>148.150635906</v>
+        <v>146.810220024</v>
       </c>
       <c r="Q69">
-        <v>262.450635906</v>
+        <v>261.110220024</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1357691248847427</v>
+        <v>0.1383412541588051</v>
       </c>
       <c r="T69">
-        <v>2.077808888793133</v>
+        <v>2.137211412443536</v>
       </c>
       <c r="U69">
         <v>0.07190000000000001</v>
@@ -7102,7 +7102,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.64963989958534</v>
+        <v>2.610674606944378</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7110,22 +7110,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.08240496133081762</v>
+        <v>0.08243117144967016</v>
       </c>
       <c r="C70">
-        <v>477.5289799550974</v>
+        <v>452.9018784299967</v>
       </c>
       <c r="D70">
-        <v>1014.796979955097</v>
+        <v>1014.070878429997</v>
       </c>
       <c r="E70">
-        <v>168.4680000000001</v>
+        <v>192.3690000000001</v>
       </c>
       <c r="F70">
-        <v>1625.268</v>
+        <v>1649.169</v>
       </c>
       <c r="G70">
         <v>1088</v>
@@ -7146,28 +7146,28 @@
         <v>305.075</v>
       </c>
       <c r="M70">
-        <v>116.8567692</v>
+        <v>118.5752511</v>
       </c>
       <c r="N70">
-        <v>188.2182308</v>
+        <v>186.4997489</v>
       </c>
       <c r="O70">
-        <v>41.40801077599999</v>
+        <v>41.029944758</v>
       </c>
       <c r="P70">
-        <v>146.810220024</v>
+        <v>145.469804142</v>
       </c>
       <c r="Q70">
-        <v>261.110220024</v>
+        <v>259.769804142</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1383412541588051</v>
+        <v>0.1410793272570005</v>
       </c>
       <c r="T70">
-        <v>2.137211412443536</v>
+        <v>2.200446356974608</v>
       </c>
       <c r="U70">
         <v>0.07190000000000001</v>
@@ -7184,7 +7184,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.610674606944378</v>
+        <v>2.57283874307562</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7192,22 +7192,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.08243117144967016</v>
+        <v>0.0824573815685227</v>
       </c>
       <c r="C71">
-        <v>452.9018784299967</v>
+        <v>428.2758152336837</v>
       </c>
       <c r="D71">
-        <v>1014.070878429997</v>
+        <v>1013.345815233684</v>
       </c>
       <c r="E71">
-        <v>192.3690000000001</v>
+        <v>216.2700000000002</v>
       </c>
       <c r="F71">
-        <v>1649.169</v>
+        <v>1673.07</v>
       </c>
       <c r="G71">
         <v>1088</v>
@@ -7228,28 +7228,28 @@
         <v>305.075</v>
       </c>
       <c r="M71">
-        <v>118.5752511</v>
+        <v>120.293733</v>
       </c>
       <c r="N71">
-        <v>186.4997489</v>
+        <v>184.781267</v>
       </c>
       <c r="O71">
-        <v>41.029944758</v>
+        <v>40.65187873999999</v>
       </c>
       <c r="P71">
-        <v>145.469804142</v>
+        <v>144.12938826</v>
       </c>
       <c r="Q71">
-        <v>259.769804142</v>
+        <v>258.42938826</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1410793272570005</v>
+        <v>0.1439999385617423</v>
       </c>
       <c r="T71">
-        <v>2.200446356974608</v>
+        <v>2.267896964474419</v>
       </c>
       <c r="U71">
         <v>0.07190000000000001</v>
@@ -7266,7 +7266,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>2.57283874307562</v>
+        <v>2.536083903888825</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7274,22 +7274,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.0824573815685227</v>
+        <v>0.08248359168737525</v>
       </c>
       <c r="C72">
-        <v>428.2758152336837</v>
+        <v>403.6507881405255</v>
       </c>
       <c r="D72">
-        <v>1013.345815233684</v>
+        <v>1012.621788140526</v>
       </c>
       <c r="E72">
-        <v>216.2700000000002</v>
+        <v>240.171</v>
       </c>
       <c r="F72">
-        <v>1673.07</v>
+        <v>1696.971</v>
       </c>
       <c r="G72">
         <v>1088</v>
@@ -7310,28 +7310,28 @@
         <v>305.075</v>
       </c>
       <c r="M72">
-        <v>120.293733</v>
+        <v>122.0122149</v>
       </c>
       <c r="N72">
-        <v>184.781267</v>
+        <v>183.0627851</v>
       </c>
       <c r="O72">
-        <v>40.65187873999999</v>
+        <v>40.273812722</v>
       </c>
       <c r="P72">
-        <v>144.12938826</v>
+        <v>142.788972378</v>
       </c>
       <c r="Q72">
-        <v>258.42938826</v>
+        <v>257.088972378</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1439999385617423</v>
+        <v>0.1471219713357767</v>
       </c>
       <c r="T72">
-        <v>2.267896964474419</v>
+        <v>2.339999338008701</v>
       </c>
       <c r="U72">
         <v>0.07190000000000001</v>
@@ -7348,7 +7348,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>2.536083903888825</v>
+        <v>2.500364412284757</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7356,22 +7356,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.08248359168737524</v>
+        <v>0.0847000418062278</v>
       </c>
       <c r="C73">
-        <v>403.6507881405262</v>
+        <v>322.0525318276182</v>
       </c>
       <c r="D73">
-        <v>1012.621788140526</v>
+        <v>954.9245318276181</v>
       </c>
       <c r="E73">
-        <v>240.1709999999998</v>
+        <v>264.0719999999999</v>
       </c>
       <c r="F73">
-        <v>1696.971</v>
+        <v>1720.872</v>
       </c>
       <c r="G73">
         <v>1088</v>
@@ -7392,45 +7392,45 @@
         <v>305.075</v>
       </c>
       <c r="M73">
-        <v>122.0122149</v>
+        <v>130.4420976</v>
       </c>
       <c r="N73">
-        <v>183.0627851</v>
+        <v>174.6329024</v>
       </c>
       <c r="O73">
-        <v>40.273812722</v>
+        <v>38.41923852799999</v>
       </c>
       <c r="P73">
-        <v>142.788972378</v>
+        <v>136.213663872</v>
       </c>
       <c r="Q73">
-        <v>257.088972378</v>
+        <v>250.513663872</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1471219713357767</v>
+        <v>0.1504670064508135</v>
       </c>
       <c r="T73">
-        <v>2.3399993380087</v>
+        <v>2.417251881081144</v>
       </c>
       <c r="U73">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V73">
         <v>0.22</v>
       </c>
       <c r="W73">
-        <v>0.05608200000000001</v>
+        <v>0.05912400000000001</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y73">
-        <v>2.500364412284757</v>
+        <v>2.338777170967542</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7438,22 +7438,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.0847000418062278</v>
+        <v>0.08475667192508032</v>
       </c>
       <c r="C74">
-        <v>322.0525318276182</v>
+        <v>296.7633873311736</v>
       </c>
       <c r="D74">
-        <v>954.9245318276181</v>
+        <v>953.5363873311736</v>
       </c>
       <c r="E74">
-        <v>264.0719999999999</v>
+        <v>287.973</v>
       </c>
       <c r="F74">
-        <v>1720.872</v>
+        <v>1744.773</v>
       </c>
       <c r="G74">
         <v>1088</v>
@@ -7474,28 +7474,28 @@
         <v>305.075</v>
       </c>
       <c r="M74">
-        <v>130.4420976</v>
+        <v>132.2537934</v>
       </c>
       <c r="N74">
-        <v>174.6329024</v>
+        <v>172.8212066</v>
       </c>
       <c r="O74">
-        <v>38.41923852799999</v>
+        <v>38.020665452</v>
       </c>
       <c r="P74">
-        <v>136.213663872</v>
+        <v>134.800541148</v>
       </c>
       <c r="Q74">
-        <v>250.513663872</v>
+        <v>249.100541148</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1504670064508135</v>
+        <v>0.1540598219447419</v>
       </c>
       <c r="T74">
-        <v>2.417251881081144</v>
+        <v>2.500226834751546</v>
       </c>
       <c r="U74">
         <v>0.07580000000000001</v>
@@ -7512,7 +7512,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>2.338777170967542</v>
+        <v>2.30673912752963</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7520,22 +7520,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.08475667192508032</v>
+        <v>0.08481330204393286</v>
       </c>
       <c r="C75">
-        <v>296.7633873311736</v>
+        <v>271.4782727826541</v>
       </c>
       <c r="D75">
-        <v>953.5363873311736</v>
+        <v>952.1522727826542</v>
       </c>
       <c r="E75">
-        <v>287.973</v>
+        <v>311.874</v>
       </c>
       <c r="F75">
-        <v>1744.773</v>
+        <v>1768.674</v>
       </c>
       <c r="G75">
         <v>1088</v>
@@ -7556,28 +7556,28 @@
         <v>305.075</v>
       </c>
       <c r="M75">
-        <v>132.2537934</v>
+        <v>134.0654892</v>
       </c>
       <c r="N75">
-        <v>172.8212066</v>
+        <v>171.0095108</v>
       </c>
       <c r="O75">
-        <v>38.020665452</v>
+        <v>37.622092376</v>
       </c>
       <c r="P75">
-        <v>134.800541148</v>
+        <v>133.387418424</v>
       </c>
       <c r="Q75">
-        <v>249.100541148</v>
+        <v>247.687418424</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1540598219447419</v>
+        <v>0.1579290078612802</v>
       </c>
       <c r="T75">
-        <v>2.500226834751546</v>
+        <v>2.589584477165826</v>
       </c>
       <c r="U75">
         <v>0.07580000000000001</v>
@@ -7594,7 +7594,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>2.30673912752963</v>
+        <v>2.275566977157609</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7602,22 +7602,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.08481330204393286</v>
+        <v>0.08486993216278541</v>
       </c>
       <c r="C76">
-        <v>271.4782727826541</v>
+        <v>246.1971706583729</v>
       </c>
       <c r="D76">
-        <v>952.1522727826542</v>
+        <v>950.7721706583727</v>
       </c>
       <c r="E76">
-        <v>311.874</v>
+        <v>335.7749999999999</v>
       </c>
       <c r="F76">
-        <v>1768.674</v>
+        <v>1792.575</v>
       </c>
       <c r="G76">
         <v>1088</v>
@@ -7638,28 +7638,28 @@
         <v>305.075</v>
       </c>
       <c r="M76">
-        <v>134.0654892</v>
+        <v>135.877185</v>
       </c>
       <c r="N76">
-        <v>171.0095108</v>
+        <v>169.197815</v>
       </c>
       <c r="O76">
-        <v>37.622092376</v>
+        <v>37.2235193</v>
       </c>
       <c r="P76">
-        <v>133.387418424</v>
+        <v>131.9742957</v>
       </c>
       <c r="Q76">
-        <v>247.687418424</v>
+        <v>246.2742957</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1579290078612802</v>
+        <v>0.1621077286511416</v>
       </c>
       <c r="T76">
-        <v>2.589584477165826</v>
+        <v>2.686090730973248</v>
       </c>
       <c r="U76">
         <v>0.07580000000000001</v>
@@ -7676,7 +7676,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>2.275566977157609</v>
+        <v>2.245226084128841</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7684,22 +7684,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.08486993216278541</v>
+        <v>0.08492656228163795</v>
       </c>
       <c r="C77">
-        <v>246.1971706583729</v>
+        <v>220.9200635360933</v>
       </c>
       <c r="D77">
-        <v>950.7721706583727</v>
+        <v>949.3960635360933</v>
       </c>
       <c r="E77">
-        <v>335.7749999999999</v>
+        <v>359.6759999999999</v>
       </c>
       <c r="F77">
-        <v>1792.575</v>
+        <v>1816.476</v>
       </c>
       <c r="G77">
         <v>1088</v>
@@ -7720,28 +7720,28 @@
         <v>305.075</v>
       </c>
       <c r="M77">
-        <v>135.877185</v>
+        <v>137.6888808</v>
       </c>
       <c r="N77">
-        <v>169.197815</v>
+        <v>167.3861192</v>
       </c>
       <c r="O77">
-        <v>37.2235193</v>
+        <v>36.824946224</v>
       </c>
       <c r="P77">
-        <v>131.9742957</v>
+        <v>130.561172976</v>
       </c>
       <c r="Q77">
-        <v>246.2742957</v>
+        <v>244.861172976</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1621077286511416</v>
+        <v>0.1666346761734915</v>
       </c>
       <c r="T77">
-        <v>2.686090730973248</v>
+        <v>2.790639172597956</v>
       </c>
       <c r="U77">
         <v>0.07580000000000001</v>
@@ -7758,7 +7758,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>2.245226084128841</v>
+        <v>2.215683635653461</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7766,22 +7766,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.08492656228163795</v>
+        <v>0.08498319240049049</v>
       </c>
       <c r="C78">
-        <v>220.9200635360933</v>
+        <v>195.6469340942995</v>
       </c>
       <c r="D78">
-        <v>949.3960635360933</v>
+        <v>948.0239340942993</v>
       </c>
       <c r="E78">
-        <v>359.6759999999999</v>
+        <v>383.577</v>
       </c>
       <c r="F78">
-        <v>1816.476</v>
+        <v>1840.377</v>
       </c>
       <c r="G78">
         <v>1088</v>
@@ -7802,28 +7802,28 @@
         <v>305.075</v>
       </c>
       <c r="M78">
-        <v>137.6888808</v>
+        <v>139.5005766</v>
       </c>
       <c r="N78">
-        <v>167.3861192</v>
+        <v>165.5744234</v>
       </c>
       <c r="O78">
-        <v>36.824946224</v>
+        <v>36.426373148</v>
       </c>
       <c r="P78">
-        <v>130.561172976</v>
+        <v>129.148050252</v>
       </c>
       <c r="Q78">
-        <v>244.861172976</v>
+        <v>243.448050252</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1666346761734915</v>
+        <v>0.1715552713064804</v>
       </c>
       <c r="T78">
-        <v>2.790639172597956</v>
+        <v>2.904278783059594</v>
       </c>
       <c r="U78">
         <v>0.07580000000000001</v>
@@ -7840,7 +7840,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>2.215683635653461</v>
+        <v>2.186908523502117</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7848,22 +7848,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.08498319240049049</v>
+        <v>0.08503982251934303</v>
       </c>
       <c r="C79">
-        <v>195.6469340942995</v>
+        <v>170.3777651114672</v>
       </c>
       <c r="D79">
-        <v>948.0239340942993</v>
+        <v>946.6557651114671</v>
       </c>
       <c r="E79">
-        <v>383.577</v>
+        <v>407.4780000000001</v>
       </c>
       <c r="F79">
-        <v>1840.377</v>
+        <v>1864.278</v>
       </c>
       <c r="G79">
         <v>1088</v>
@@ -7884,28 +7884,28 @@
         <v>305.075</v>
       </c>
       <c r="M79">
-        <v>139.5005766</v>
+        <v>141.3122724</v>
       </c>
       <c r="N79">
-        <v>165.5744234</v>
+        <v>163.7627276</v>
       </c>
       <c r="O79">
-        <v>36.426373148</v>
+        <v>36.027800072</v>
       </c>
       <c r="P79">
-        <v>129.148050252</v>
+        <v>127.734927528</v>
       </c>
       <c r="Q79">
-        <v>243.448050252</v>
+        <v>242.034927528</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1715552713064804</v>
+        <v>0.1769231932697411</v>
       </c>
       <c r="T79">
-        <v>2.904278783059594</v>
+        <v>3.028249267199564</v>
       </c>
       <c r="U79">
         <v>0.07580000000000001</v>
@@ -7922,7 +7922,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>2.186908523502117</v>
+        <v>2.158871234739269</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7930,22 +7930,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.08503982251934303</v>
+        <v>0.08509645263819557</v>
       </c>
       <c r="C80">
-        <v>170.3777651114672</v>
+        <v>145.1125394653436</v>
       </c>
       <c r="D80">
-        <v>946.6557651114671</v>
+        <v>945.2915394653436</v>
       </c>
       <c r="E80">
-        <v>407.4780000000001</v>
+        <v>431.3790000000001</v>
       </c>
       <c r="F80">
-        <v>1864.278</v>
+        <v>1888.179</v>
       </c>
       <c r="G80">
         <v>1088</v>
@@ -7966,28 +7966,28 @@
         <v>305.075</v>
       </c>
       <c r="M80">
-        <v>141.3122724</v>
+        <v>143.1239682</v>
       </c>
       <c r="N80">
-        <v>163.7627276</v>
+        <v>161.9510318</v>
       </c>
       <c r="O80">
-        <v>36.027800072</v>
+        <v>35.62922699599999</v>
       </c>
       <c r="P80">
-        <v>127.734927528</v>
+        <v>126.321804804</v>
       </c>
       <c r="Q80">
-        <v>242.034927528</v>
+        <v>240.621804804</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1769231932697411</v>
+        <v>0.1828023458961694</v>
       </c>
       <c r="T80">
-        <v>3.028249267199564</v>
+        <v>3.164026464114768</v>
       </c>
       <c r="U80">
         <v>0.07580000000000001</v>
@@ -8004,7 +8004,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>2.158871234739269</v>
+        <v>2.131543750755228</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8012,22 +8012,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.08509645263819557</v>
+        <v>0.08515308275704814</v>
       </c>
       <c r="C81">
-        <v>145.1125394653436</v>
+        <v>119.8512401322332</v>
       </c>
       <c r="D81">
-        <v>945.2915394653436</v>
+        <v>943.9312401322331</v>
       </c>
       <c r="E81">
-        <v>431.3790000000001</v>
+        <v>455.28</v>
       </c>
       <c r="F81">
-        <v>1888.179</v>
+        <v>1912.08</v>
       </c>
       <c r="G81">
         <v>1088</v>
@@ -8048,28 +8048,28 @@
         <v>305.075</v>
       </c>
       <c r="M81">
-        <v>143.1239682</v>
+        <v>144.935664</v>
       </c>
       <c r="N81">
-        <v>161.9510318</v>
+        <v>160.139336</v>
       </c>
       <c r="O81">
-        <v>35.62922699599999</v>
+        <v>35.23065391999999</v>
       </c>
       <c r="P81">
-        <v>126.321804804</v>
+        <v>124.90868208</v>
       </c>
       <c r="Q81">
-        <v>240.621804804</v>
+        <v>239.20868208</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1828023458961694</v>
+        <v>0.1892694137852406</v>
       </c>
       <c r="T81">
-        <v>3.164026464114768</v>
+        <v>3.313381380721493</v>
       </c>
       <c r="U81">
         <v>0.07580000000000001</v>
@@ -8086,7 +8086,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>2.131543750755228</v>
+        <v>2.104899453870788</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8094,22 +8094,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.08515308275704814</v>
+        <v>0.08520971287590066</v>
       </c>
       <c r="C82">
-        <v>119.8512401322332</v>
+        <v>94.59385018629177</v>
       </c>
       <c r="D82">
-        <v>943.9312401322331</v>
+        <v>942.5748501862919</v>
       </c>
       <c r="E82">
-        <v>455.28</v>
+        <v>479.181</v>
       </c>
       <c r="F82">
-        <v>1912.08</v>
+        <v>1935.981</v>
       </c>
       <c r="G82">
         <v>1088</v>
@@ -8130,28 +8130,28 @@
         <v>305.075</v>
       </c>
       <c r="M82">
-        <v>144.935664</v>
+        <v>146.7473598</v>
       </c>
       <c r="N82">
-        <v>160.139336</v>
+        <v>158.3276402</v>
       </c>
       <c r="O82">
-        <v>35.23065391999999</v>
+        <v>34.832080844</v>
       </c>
       <c r="P82">
-        <v>124.90868208</v>
+        <v>123.495559356</v>
       </c>
       <c r="Q82">
-        <v>239.20868208</v>
+        <v>237.795559356</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1892694137852406</v>
+        <v>0.1964172256626351</v>
       </c>
       <c r="T82">
-        <v>3.313381380721493</v>
+        <v>3.478457867497346</v>
       </c>
       <c r="U82">
         <v>0.07580000000000001</v>
@@ -8168,7 +8168,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>2.104899453870788</v>
+        <v>2.078913040860037</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8176,22 +8176,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.08520971287590066</v>
+        <v>0.08526634299475321</v>
       </c>
       <c r="C83">
-        <v>94.59385018629177</v>
+        <v>69.34035279882028</v>
       </c>
       <c r="D83">
-        <v>942.5748501862919</v>
+        <v>941.2223527988202</v>
       </c>
       <c r="E83">
-        <v>479.181</v>
+        <v>503.0820000000001</v>
       </c>
       <c r="F83">
-        <v>1935.981</v>
+        <v>1959.882</v>
       </c>
       <c r="G83">
         <v>1088</v>
@@ -8212,28 +8212,28 @@
         <v>305.075</v>
       </c>
       <c r="M83">
-        <v>146.7473598</v>
+        <v>148.5590556</v>
       </c>
       <c r="N83">
-        <v>158.3276402</v>
+        <v>156.5159444</v>
       </c>
       <c r="O83">
-        <v>34.832080844</v>
+        <v>34.43350776799999</v>
       </c>
       <c r="P83">
-        <v>123.495559356</v>
+        <v>122.082436632</v>
       </c>
       <c r="Q83">
-        <v>237.795559356</v>
+        <v>236.382436632</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1964172256626351</v>
+        <v>0.20435923885974</v>
       </c>
       <c r="T83">
-        <v>3.478457867497346</v>
+        <v>3.661876186137184</v>
       </c>
       <c r="U83">
         <v>0.07580000000000001</v>
@@ -8250,7 +8250,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>2.078913040860037</v>
+        <v>2.053560442800768</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8258,22 +8258,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.08526634299475321</v>
+        <v>0.08532297311360575</v>
       </c>
       <c r="C84">
-        <v>69.34035279882028</v>
+        <v>44.09073123757139</v>
       </c>
       <c r="D84">
-        <v>941.2223527988202</v>
+        <v>939.8737312375714</v>
       </c>
       <c r="E84">
-        <v>503.0820000000001</v>
+        <v>526.9830000000002</v>
       </c>
       <c r="F84">
-        <v>1959.882</v>
+        <v>1983.783</v>
       </c>
       <c r="G84">
         <v>1088</v>
@@ -8294,28 +8294,28 @@
         <v>305.075</v>
       </c>
       <c r="M84">
-        <v>148.5590556</v>
+        <v>150.3707514</v>
       </c>
       <c r="N84">
-        <v>156.5159444</v>
+        <v>154.7042486</v>
       </c>
       <c r="O84">
-        <v>34.43350776799999</v>
+        <v>34.03493469199999</v>
       </c>
       <c r="P84">
-        <v>122.082436632</v>
+        <v>120.669313908</v>
       </c>
       <c r="Q84">
-        <v>236.382436632</v>
+        <v>234.969313908</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.20435923885974</v>
+        <v>0.2132356065506221</v>
       </c>
       <c r="T84">
-        <v>3.661876186137184</v>
+        <v>3.866873130499356</v>
       </c>
       <c r="U84">
         <v>0.07580000000000001</v>
@@ -8332,7 +8332,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>2.053560442800768</v>
+        <v>2.028818750718831</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8340,22 +8340,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.08532297311360575</v>
+        <v>0.0853796032324583</v>
       </c>
       <c r="C85">
-        <v>44.09073123757139</v>
+        <v>18.84496886605939</v>
       </c>
       <c r="D85">
-        <v>939.8737312375714</v>
+        <v>938.5289688660595</v>
       </c>
       <c r="E85">
-        <v>526.9830000000002</v>
+        <v>550.8840000000002</v>
       </c>
       <c r="F85">
-        <v>1983.783</v>
+        <v>2007.684</v>
       </c>
       <c r="G85">
         <v>1088</v>
@@ -8376,28 +8376,28 @@
         <v>305.075</v>
       </c>
       <c r="M85">
-        <v>150.3707514</v>
+        <v>152.1824472</v>
       </c>
       <c r="N85">
-        <v>154.7042486</v>
+        <v>152.8925527999999</v>
       </c>
       <c r="O85">
-        <v>34.03493469199999</v>
+        <v>33.63636161599999</v>
       </c>
       <c r="P85">
-        <v>120.669313908</v>
+        <v>119.256191184</v>
       </c>
       <c r="Q85">
-        <v>234.969313908</v>
+        <v>233.556191184</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2132356065506221</v>
+        <v>0.2232215202028644</v>
       </c>
       <c r="T85">
-        <v>3.866873130499356</v>
+        <v>4.097494692906799</v>
       </c>
       <c r="U85">
         <v>0.07580000000000001</v>
@@ -8414,7 +8414,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>2.028818750718831</v>
+        <v>2.004666146543607</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8422,22 +8422,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.08537960323245829</v>
+        <v>0.09485083335131082</v>
       </c>
       <c r="C86">
-        <v>18.8449688660603</v>
+        <v>-186.2766797960139</v>
       </c>
       <c r="D86">
-        <v>938.5289688660599</v>
+        <v>757.3083202039859</v>
       </c>
       <c r="E86">
-        <v>550.8839999999998</v>
+        <v>574.7849999999999</v>
       </c>
       <c r="F86">
-        <v>2007.684</v>
+        <v>2031.585</v>
       </c>
       <c r="G86">
         <v>1088</v>
@@ -8458,45 +8458,45 @@
         <v>305.075</v>
       </c>
       <c r="M86">
-        <v>152.1824472</v>
+        <v>182.84265</v>
       </c>
       <c r="N86">
-        <v>152.8925528</v>
+        <v>122.23235</v>
       </c>
       <c r="O86">
-        <v>33.636361616</v>
+        <v>26.891117</v>
       </c>
       <c r="P86">
-        <v>119.256191184</v>
+        <v>95.34123300000002</v>
       </c>
       <c r="Q86">
-        <v>233.556191184</v>
+        <v>209.641233</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2232215202028642</v>
+        <v>0.2345388890087388</v>
       </c>
       <c r="T86">
-        <v>4.097494692906796</v>
+        <v>4.358865796968565</v>
       </c>
       <c r="U86">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V86">
         <v>0.22</v>
       </c>
       <c r="W86">
-        <v>0.05912400000000001</v>
+        <v>0.0702</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y86">
-        <v>2.004666146543608</v>
+        <v>1.668511148793785</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8504,22 +8504,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.09485083335131082</v>
+        <v>0.09501822347016337</v>
       </c>
       <c r="C87">
-        <v>-186.2766797960139</v>
+        <v>-212.7532690958556</v>
       </c>
       <c r="D87">
-        <v>757.3083202039859</v>
+        <v>754.7327309041443</v>
       </c>
       <c r="E87">
-        <v>574.7849999999999</v>
+        <v>598.6859999999999</v>
       </c>
       <c r="F87">
-        <v>2031.585</v>
+        <v>2055.486</v>
       </c>
       <c r="G87">
         <v>1088</v>
@@ -8540,28 +8540,28 @@
         <v>305.075</v>
       </c>
       <c r="M87">
-        <v>182.84265</v>
+        <v>184.99374</v>
       </c>
       <c r="N87">
-        <v>122.23235</v>
+        <v>120.08126</v>
       </c>
       <c r="O87">
-        <v>26.891117</v>
+        <v>26.4178772</v>
       </c>
       <c r="P87">
-        <v>95.34123300000002</v>
+        <v>93.66338280000001</v>
       </c>
       <c r="Q87">
-        <v>209.641233</v>
+        <v>207.9633828</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2345388890087388</v>
+        <v>0.2474730247868812</v>
       </c>
       <c r="T87">
-        <v>4.358865796968565</v>
+        <v>4.657575630182014</v>
       </c>
       <c r="U87">
         <v>0.09</v>
@@ -8578,7 +8578,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>1.668511148793785</v>
+        <v>1.649109856365951</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8586,22 +8586,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.09501822347016337</v>
+        <v>0.09518561358901589</v>
       </c>
       <c r="C88">
-        <v>-212.7532690958556</v>
+        <v>-239.2123987280856</v>
       </c>
       <c r="D88">
-        <v>754.7327309041443</v>
+        <v>752.1746012719141</v>
       </c>
       <c r="E88">
-        <v>598.6859999999999</v>
+        <v>622.5869999999998</v>
       </c>
       <c r="F88">
-        <v>2055.486</v>
+        <v>2079.387</v>
       </c>
       <c r="G88">
         <v>1088</v>
@@ -8622,28 +8622,28 @@
         <v>305.075</v>
       </c>
       <c r="M88">
-        <v>184.99374</v>
+        <v>187.14483</v>
       </c>
       <c r="N88">
-        <v>120.08126</v>
+        <v>117.93017</v>
       </c>
       <c r="O88">
-        <v>26.4178772</v>
+        <v>25.94463740000001</v>
       </c>
       <c r="P88">
-        <v>93.66338280000001</v>
+        <v>91.98553260000003</v>
       </c>
       <c r="Q88">
-        <v>207.9633828</v>
+        <v>206.2855326</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2474730247868812</v>
+        <v>0.2623970276078146</v>
       </c>
       <c r="T88">
-        <v>4.657575630182014</v>
+        <v>5.002240822351379</v>
       </c>
       <c r="U88">
         <v>0.09</v>
@@ -8660,7 +8660,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>1.649109856365951</v>
+        <v>1.630154570660595</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8668,22 +8668,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.09518561358901589</v>
+        <v>0.09535300370786845</v>
       </c>
       <c r="C89">
-        <v>-239.2123987280856</v>
+        <v>-265.6542456290535</v>
       </c>
       <c r="D89">
-        <v>752.1746012719141</v>
+        <v>749.6337543709463</v>
       </c>
       <c r="E89">
-        <v>622.5869999999998</v>
+        <v>646.4880000000001</v>
       </c>
       <c r="F89">
-        <v>2079.387</v>
+        <v>2103.288</v>
       </c>
       <c r="G89">
         <v>1088</v>
@@ -8704,28 +8704,28 @@
         <v>305.075</v>
       </c>
       <c r="M89">
-        <v>187.14483</v>
+        <v>189.29592</v>
       </c>
       <c r="N89">
-        <v>117.93017</v>
+        <v>115.77908</v>
       </c>
       <c r="O89">
-        <v>25.94463740000001</v>
+        <v>25.4713976</v>
       </c>
       <c r="P89">
-        <v>91.98553260000003</v>
+        <v>90.30768239999999</v>
       </c>
       <c r="Q89">
-        <v>206.2855326</v>
+        <v>204.6076824</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2623970276078146</v>
+        <v>0.2798083642322371</v>
       </c>
       <c r="T89">
-        <v>5.002240822351379</v>
+        <v>5.404350213215638</v>
       </c>
       <c r="U89">
         <v>0.09</v>
@@ -8742,7 +8742,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>1.630154570660595</v>
+        <v>1.611630086903088</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8750,22 +8750,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.09535300370786845</v>
+        <v>0.09552039382672098</v>
       </c>
       <c r="C90">
-        <v>-265.6542456290535</v>
+        <v>-292.0789843523899</v>
       </c>
       <c r="D90">
-        <v>749.6337543709463</v>
+        <v>747.1100156476101</v>
       </c>
       <c r="E90">
-        <v>646.4880000000001</v>
+        <v>670.3889999999999</v>
       </c>
       <c r="F90">
-        <v>2103.288</v>
+        <v>2127.189</v>
       </c>
       <c r="G90">
         <v>1088</v>
@@ -8786,28 +8786,28 @@
         <v>305.075</v>
       </c>
       <c r="M90">
-        <v>189.29592</v>
+        <v>191.44701</v>
       </c>
       <c r="N90">
-        <v>115.77908</v>
+        <v>113.62799</v>
       </c>
       <c r="O90">
-        <v>25.4713976</v>
+        <v>24.9981578</v>
       </c>
       <c r="P90">
-        <v>90.30768239999999</v>
+        <v>88.62983220000001</v>
       </c>
       <c r="Q90">
-        <v>204.6076824</v>
+        <v>202.9298322</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2798083642322371</v>
+        <v>0.3003853984247363</v>
       </c>
       <c r="T90">
-        <v>5.404350213215638</v>
+        <v>5.879570402418853</v>
       </c>
       <c r="U90">
         <v>0.09</v>
@@ -8824,7 +8824,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>1.611630086903088</v>
+        <v>1.593521883679458</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8832,22 +8832,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.09552039382672098</v>
+        <v>0.09568778394557353</v>
       </c>
       <c r="C91">
-        <v>-292.0789843523899</v>
+        <v>-318.4867871089853</v>
       </c>
       <c r="D91">
-        <v>747.1100156476101</v>
+        <v>744.6032128910149</v>
       </c>
       <c r="E91">
-        <v>670.3889999999999</v>
+        <v>694.2900000000002</v>
       </c>
       <c r="F91">
-        <v>2127.189</v>
+        <v>2151.09</v>
       </c>
       <c r="G91">
         <v>1088</v>
@@ -8868,28 +8868,28 @@
         <v>305.075</v>
       </c>
       <c r="M91">
-        <v>191.44701</v>
+        <v>193.5981</v>
       </c>
       <c r="N91">
-        <v>113.62799</v>
+        <v>111.4769</v>
       </c>
       <c r="O91">
-        <v>24.9981578</v>
+        <v>24.52491799999999</v>
       </c>
       <c r="P91">
-        <v>88.62983220000001</v>
+        <v>86.95198199999999</v>
       </c>
       <c r="Q91">
-        <v>202.9298322</v>
+        <v>201.251982</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3003853984247363</v>
+        <v>0.3250778394557354</v>
       </c>
       <c r="T91">
-        <v>5.879570402418853</v>
+        <v>6.449834629462711</v>
       </c>
       <c r="U91">
         <v>0.09</v>
@@ -8906,7 +8906,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>1.593521883679458</v>
+        <v>1.575816084971908</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8914,22 +8914,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.09568778394557353</v>
+        <v>0.09585517406442606</v>
       </c>
       <c r="C92">
-        <v>-318.4867871089853</v>
+        <v>-344.8778238061579</v>
       </c>
       <c r="D92">
-        <v>744.6032128910149</v>
+        <v>742.113176193842</v>
       </c>
       <c r="E92">
-        <v>694.2900000000002</v>
+        <v>718.191</v>
       </c>
       <c r="F92">
-        <v>2151.09</v>
+        <v>2174.991</v>
       </c>
       <c r="G92">
         <v>1088</v>
@@ -8950,28 +8950,28 @@
         <v>305.075</v>
       </c>
       <c r="M92">
-        <v>193.5981</v>
+        <v>195.74919</v>
       </c>
       <c r="N92">
-        <v>111.4769</v>
+        <v>109.32581</v>
       </c>
       <c r="O92">
-        <v>24.52491799999999</v>
+        <v>24.0516782</v>
       </c>
       <c r="P92">
-        <v>86.95198199999999</v>
+        <v>85.27413179999999</v>
       </c>
       <c r="Q92">
-        <v>201.251982</v>
+        <v>199.5741318</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3250778394557354</v>
+        <v>0.3552574896047342</v>
       </c>
       <c r="T92">
-        <v>6.449834629462711</v>
+        <v>7.146824240294094</v>
       </c>
       <c r="U92">
         <v>0.09</v>
@@ -8988,7 +8988,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>1.575816084971908</v>
+        <v>1.558499424697492</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8996,22 +8996,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.09585517406442606</v>
+        <v>0.09602256418327862</v>
       </c>
       <c r="C93">
-        <v>-344.8778238061579</v>
+        <v>-371.2522620860475</v>
       </c>
       <c r="D93">
-        <v>742.113176193842</v>
+        <v>739.6397379139523</v>
       </c>
       <c r="E93">
-        <v>718.191</v>
+        <v>742.0919999999999</v>
       </c>
       <c r="F93">
-        <v>2174.991</v>
+        <v>2198.892</v>
       </c>
       <c r="G93">
         <v>1088</v>
@@ -9032,28 +9032,28 @@
         <v>305.075</v>
       </c>
       <c r="M93">
-        <v>195.74919</v>
+        <v>197.90028</v>
       </c>
       <c r="N93">
-        <v>109.32581</v>
+        <v>107.17472</v>
       </c>
       <c r="O93">
-        <v>24.0516782</v>
+        <v>23.5784384</v>
       </c>
       <c r="P93">
-        <v>85.27413179999999</v>
+        <v>83.5962816</v>
       </c>
       <c r="Q93">
-        <v>199.5741318</v>
+        <v>197.8962816</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3552574896047342</v>
+        <v>0.3929820522909829</v>
       </c>
       <c r="T93">
-        <v>7.146824240294094</v>
+        <v>8.018061253833324</v>
       </c>
       <c r="U93">
         <v>0.09</v>
@@ -9070,7 +9070,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>1.558499424697492</v>
+        <v>1.541559213559476</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9078,22 +9078,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.09602256418327862</v>
+        <v>0.09618995430213115</v>
       </c>
       <c r="C94">
-        <v>-371.2522620860475</v>
+        <v>-397.6102673632331</v>
       </c>
       <c r="D94">
-        <v>739.6397379139523</v>
+        <v>737.1827326367669</v>
       </c>
       <c r="E94">
-        <v>742.0919999999999</v>
+        <v>765.9930000000002</v>
       </c>
       <c r="F94">
-        <v>2198.892</v>
+        <v>2222.793</v>
       </c>
       <c r="G94">
         <v>1088</v>
@@ -9114,28 +9114,28 @@
         <v>305.075</v>
       </c>
       <c r="M94">
-        <v>197.90028</v>
+        <v>200.05137</v>
       </c>
       <c r="N94">
-        <v>107.17472</v>
+        <v>105.02363</v>
       </c>
       <c r="O94">
-        <v>23.5784384</v>
+        <v>23.1051986</v>
       </c>
       <c r="P94">
-        <v>83.5962816</v>
+        <v>81.9184314</v>
       </c>
       <c r="Q94">
-        <v>197.8962816</v>
+        <v>196.2184314</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.3929820522909829</v>
+        <v>0.4414850614590168</v>
       </c>
       <c r="T94">
-        <v>8.018061253833324</v>
+        <v>9.13822312838376</v>
       </c>
       <c r="U94">
         <v>0.09</v>
@@ -9152,7 +9152,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>1.541559213559476</v>
+        <v>1.524983308037331</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9160,22 +9160,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.09618995430213115</v>
+        <v>0.09635734442098369</v>
       </c>
       <c r="C95">
-        <v>-397.6102673632331</v>
+        <v>-423.952002861613</v>
       </c>
       <c r="D95">
-        <v>737.1827326367669</v>
+        <v>734.7419971383871</v>
       </c>
       <c r="E95">
-        <v>765.9930000000002</v>
+        <v>789.894</v>
       </c>
       <c r="F95">
-        <v>2222.793</v>
+        <v>2246.694</v>
       </c>
       <c r="G95">
         <v>1088</v>
@@ -9196,28 +9196,28 @@
         <v>305.075</v>
       </c>
       <c r="M95">
-        <v>200.05137</v>
+        <v>202.20246</v>
       </c>
       <c r="N95">
-        <v>105.02363</v>
+        <v>102.87254</v>
       </c>
       <c r="O95">
-        <v>23.1051986</v>
+        <v>22.6319588</v>
       </c>
       <c r="P95">
-        <v>81.9184314</v>
+        <v>80.24058119999999</v>
       </c>
       <c r="Q95">
-        <v>196.2184314</v>
+        <v>194.5405812</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.4414850614590168</v>
+        <v>0.5061557403497287</v>
       </c>
       <c r="T95">
-        <v>9.13822312838376</v>
+        <v>10.63177229445101</v>
       </c>
       <c r="U95">
         <v>0.09</v>
@@ -9234,7 +9234,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>1.524983308037331</v>
+        <v>1.508760081356082</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9242,22 +9242,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.09635734442098369</v>
+        <v>0.1418304795782857</v>
       </c>
       <c r="C96">
-        <v>-423.952002861613</v>
+        <v>-795.7740201088784</v>
       </c>
       <c r="D96">
-        <v>734.7419971383871</v>
+        <v>386.8209798911218</v>
       </c>
       <c r="E96">
-        <v>789.894</v>
+        <v>813.7950000000003</v>
       </c>
       <c r="F96">
-        <v>2246.694</v>
+        <v>2270.595</v>
       </c>
       <c r="G96">
         <v>1088</v>
@@ -9278,45 +9278,45 @@
         <v>305.075</v>
       </c>
       <c r="M96">
-        <v>202.20246</v>
+        <v>333.3233460000001</v>
       </c>
       <c r="N96">
-        <v>102.87254</v>
+        <v>-28.24834600000008</v>
       </c>
       <c r="O96">
-        <v>22.6319588</v>
+        <v>-6.214636120000018</v>
       </c>
       <c r="P96">
-        <v>80.24058119999999</v>
+        <v>-22.03370988000006</v>
       </c>
       <c r="Q96">
-        <v>194.5405812</v>
+        <v>92.26629011999995</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.5061557403497287</v>
+        <v>0.6090304442497024</v>
       </c>
       <c r="T96">
-        <v>10.63177229445101</v>
+        <v>13.00763150692154</v>
       </c>
       <c r="U96">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V96">
-        <v>0.22</v>
+        <v>0.2013555330144801</v>
       </c>
       <c r="W96">
-        <v>0.0702</v>
+        <v>0.1172410077534743</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y96">
-        <v>1.508760081356082</v>
+        <v>0.9152524227930915</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9324,22 +9324,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1418304795782857</v>
+        <v>0.1428404795782857</v>
       </c>
       <c r="C97">
-        <v>-795.7740201088784</v>
+        <v>-823.7010635846304</v>
       </c>
       <c r="D97">
-        <v>386.8209798911218</v>
+        <v>382.7949364153696</v>
       </c>
       <c r="E97">
-        <v>813.7950000000003</v>
+        <v>837.6960000000001</v>
       </c>
       <c r="F97">
-        <v>2270.595</v>
+        <v>2294.496</v>
       </c>
       <c r="G97">
         <v>1088</v>
@@ -9360,37 +9360,37 @@
         <v>305.075</v>
       </c>
       <c r="M97">
-        <v>333.3233460000001</v>
+        <v>336.8320128</v>
       </c>
       <c r="N97">
-        <v>-28.24834600000008</v>
+        <v>-31.75701280000004</v>
       </c>
       <c r="O97">
-        <v>-6.214636120000018</v>
+        <v>-6.986542816000009</v>
       </c>
       <c r="P97">
-        <v>-22.03370988000006</v>
+        <v>-24.77046998400003</v>
       </c>
       <c r="Q97">
-        <v>92.26629011999995</v>
+        <v>89.52953001599998</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.6090304442497024</v>
+        <v>0.7498380553121282</v>
       </c>
       <c r="T97">
-        <v>13.00763150692154</v>
+        <v>16.25953938365193</v>
       </c>
       <c r="U97">
         <v>0.1468</v>
       </c>
       <c r="V97">
-        <v>0.2013555330144801</v>
+        <v>0.1992580795455793</v>
       </c>
       <c r="W97">
-        <v>0.1172410077534743</v>
+        <v>0.117548913922709</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9398,7 +9398,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.9152524227930915</v>
+        <v>0.9057185433889969</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9406,22 +9406,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1428404795782857</v>
+        <v>0.1438504795782857</v>
       </c>
       <c r="C98">
-        <v>-823.70106358463</v>
+        <v>-851.5451639900784</v>
       </c>
       <c r="D98">
-        <v>382.7949364153696</v>
+        <v>378.8518360099214</v>
       </c>
       <c r="E98">
-        <v>837.6959999999997</v>
+        <v>861.597</v>
       </c>
       <c r="F98">
-        <v>2294.496</v>
+        <v>2318.397</v>
       </c>
       <c r="G98">
         <v>1088</v>
@@ -9442,37 +9442,37 @@
         <v>305.075</v>
       </c>
       <c r="M98">
-        <v>336.8320128</v>
+        <v>340.3406796</v>
       </c>
       <c r="N98">
-        <v>-31.75701279999998</v>
+        <v>-35.26567960000006</v>
       </c>
       <c r="O98">
-        <v>-6.986542815999996</v>
+        <v>-7.758449512000012</v>
       </c>
       <c r="P98">
-        <v>-24.77046998399999</v>
+        <v>-27.50723008800004</v>
       </c>
       <c r="Q98">
-        <v>89.52953001600002</v>
+        <v>86.79276991199997</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.7498380553121263</v>
+        <v>0.9845174070828354</v>
       </c>
       <c r="T98">
-        <v>16.25953938365188</v>
+        <v>21.67938584486918</v>
       </c>
       <c r="U98">
         <v>0.1468</v>
       </c>
       <c r="V98">
-        <v>0.1992580795455794</v>
+        <v>0.1972038725399548</v>
       </c>
       <c r="W98">
-        <v>0.117548913922709</v>
+        <v>0.1178504715111347</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9480,7 +9480,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.905718543388997</v>
+        <v>0.8963812388179763</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9488,22 +9488,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1438504795782857</v>
+        <v>0.1448604795782857</v>
       </c>
       <c r="C99">
-        <v>-851.5451639900784</v>
+        <v>-879.3088583359868</v>
       </c>
       <c r="D99">
-        <v>378.8518360099214</v>
+        <v>374.989141664013</v>
       </c>
       <c r="E99">
-        <v>861.597</v>
+        <v>885.4979999999998</v>
       </c>
       <c r="F99">
-        <v>2318.397</v>
+        <v>2342.298</v>
       </c>
       <c r="G99">
         <v>1088</v>
@@ -9524,37 +9524,37 @@
         <v>305.075</v>
       </c>
       <c r="M99">
-        <v>340.3406796</v>
+        <v>343.8493464</v>
       </c>
       <c r="N99">
-        <v>-35.26567960000006</v>
+        <v>-38.77434640000001</v>
       </c>
       <c r="O99">
-        <v>-7.758449512000012</v>
+        <v>-8.530356208000002</v>
       </c>
       <c r="P99">
-        <v>-27.50723008800004</v>
+        <v>-30.24399019200001</v>
       </c>
       <c r="Q99">
-        <v>86.79276991199997</v>
+        <v>84.056009808</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.9845174070828354</v>
+        <v>1.453876110624253</v>
       </c>
       <c r="T99">
-        <v>21.67938584486918</v>
+        <v>32.51907876730377</v>
       </c>
       <c r="U99">
         <v>0.1468</v>
       </c>
       <c r="V99">
-        <v>0.1972038725399548</v>
+        <v>0.1951915881262818</v>
       </c>
       <c r="W99">
-        <v>0.1178504715111347</v>
+        <v>0.1181458748630618</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9562,7 +9562,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.8963812388179763</v>
+        <v>0.8872344914830991</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9570,22 +9570,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1448604795782857</v>
+        <v>0.1458704795782857</v>
       </c>
       <c r="C100">
-        <v>-879.3088583359868</v>
+        <v>-906.9945812100727</v>
       </c>
       <c r="D100">
-        <v>374.989141664013</v>
+        <v>371.2044187899274</v>
       </c>
       <c r="E100">
-        <v>885.4979999999998</v>
+        <v>909.3990000000001</v>
       </c>
       <c r="F100">
-        <v>2342.298</v>
+        <v>2366.199</v>
       </c>
       <c r="G100">
         <v>1088</v>
@@ -9606,37 +9606,37 @@
         <v>305.075</v>
       </c>
       <c r="M100">
-        <v>343.8493464</v>
+        <v>347.3580132</v>
       </c>
       <c r="N100">
-        <v>-38.77434640000001</v>
+        <v>-42.28301320000003</v>
       </c>
       <c r="O100">
-        <v>-8.530356208000002</v>
+        <v>-9.302262904000006</v>
       </c>
       <c r="P100">
-        <v>-30.24399019200001</v>
+        <v>-32.98075029600002</v>
       </c>
       <c r="Q100">
-        <v>84.056009808</v>
+        <v>81.31924970399999</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.453876110624253</v>
+        <v>2.861952221248506</v>
       </c>
       <c r="T100">
-        <v>32.51907876730377</v>
+        <v>65.03815753460755</v>
       </c>
       <c r="U100">
         <v>0.1468</v>
       </c>
       <c r="V100">
-        <v>0.1951915881262818</v>
+        <v>0.193219955922986</v>
       </c>
       <c r="W100">
-        <v>0.1181458748630618</v>
+        <v>0.1184353104705057</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9644,91 +9644,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.8872344914830991</v>
+        <v>0.8782725269226637</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1458704795782857</v>
-      </c>
-      <c r="C101">
-        <v>-906.9945812100727</v>
-      </c>
-      <c r="D101">
-        <v>371.2044187899274</v>
-      </c>
-      <c r="E101">
-        <v>909.3990000000001</v>
-      </c>
-      <c r="F101">
-        <v>2366.199</v>
-      </c>
-      <c r="G101">
-        <v>1088</v>
-      </c>
-      <c r="H101">
-        <v>933.3</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>419.375</v>
-      </c>
-      <c r="K101">
-        <v>114.3</v>
-      </c>
-      <c r="L101">
-        <v>305.075</v>
-      </c>
-      <c r="M101">
-        <v>347.3580132</v>
-      </c>
-      <c r="N101">
-        <v>-42.28301320000003</v>
-      </c>
-      <c r="O101">
-        <v>-9.302262904000006</v>
-      </c>
-      <c r="P101">
-        <v>-32.98075029600002</v>
-      </c>
-      <c r="Q101">
-        <v>81.31924970399999</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.861952221248506</v>
-      </c>
-      <c r="T101">
-        <v>65.03815753460755</v>
-      </c>
-      <c r="U101">
-        <v>0.1468</v>
-      </c>
-      <c r="V101">
-        <v>0.193219955922986</v>
-      </c>
-      <c r="W101">
-        <v>0.1184353104705057</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Ca2/CC</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.8782725269226637</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
